--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -5675,52 +5675,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129223986</v>
+        <v>129231240</v>
       </c>
       <c r="B38" t="n">
-        <v>98659</v>
+        <v>80169</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5729,13 +5715,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490070</v>
+        <v>490033</v>
       </c>
       <c r="R38" t="n">
-        <v>7004763</v>
+        <v>7004823</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5764,7 +5750,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5774,12 +5760,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 22 plantor inom ca 1 m2 yta.</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5794,6 +5775,26 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5811,38 +5812,52 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129231240</v>
+        <v>129223986</v>
       </c>
       <c r="B39" t="n">
-        <v>80169</v>
+        <v>98659</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5851,13 +5866,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490033</v>
+        <v>490070</v>
       </c>
       <c r="R39" t="n">
-        <v>7004823</v>
+        <v>7004763</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5886,7 +5901,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5896,7 +5911,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Minst 22 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5911,26 +5931,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -6651,47 +6651,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129225914</v>
+        <v>129226789</v>
       </c>
       <c r="B45" t="n">
-        <v>57883</v>
+        <v>92464</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>4769</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6700,13 +6691,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490106</v>
+        <v>490174</v>
       </c>
       <c r="R45" t="n">
-        <v>7004828</v>
+        <v>7004879</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6735,7 +6726,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6745,12 +6736,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Synobservation av minst 2 livliga talltitor i flerskiktad äldre granskog.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6764,7 +6750,7 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6782,38 +6768,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129226789</v>
+        <v>129224339</v>
       </c>
       <c r="B46" t="n">
-        <v>92464</v>
+        <v>98659</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6822,13 +6818,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490174</v>
+        <v>490008</v>
       </c>
       <c r="R46" t="n">
-        <v>7004879</v>
+        <v>7004696</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6857,7 +6853,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6867,7 +6863,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6881,7 +6882,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6899,63 +6900,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129224339</v>
+        <v>129229015</v>
       </c>
       <c r="B47" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490008</v>
+        <v>490105</v>
       </c>
       <c r="R47" t="n">
-        <v>7004696</v>
+        <v>7004966</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6984,7 +6970,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6994,12 +6980,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7013,7 +6994,27 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7031,10 +7032,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129229015</v>
+        <v>129230332</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7042,37 +7043,47 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490105</v>
+        <v>490052</v>
       </c>
       <c r="R48" t="n">
-        <v>7004966</v>
+        <v>7004901</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7101,7 +7112,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7111,7 +7122,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7125,7 +7141,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -7140,12 +7156,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7163,7 +7179,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129230332</v>
+        <v>129230142</v>
       </c>
       <c r="B49" t="n">
         <v>57723</v>
@@ -7208,13 +7224,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490052</v>
+        <v>490056</v>
       </c>
       <c r="R49" t="n">
-        <v>7004901</v>
+        <v>7004912</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7243,7 +7259,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7253,7 +7269,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7310,10 +7326,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129230142</v>
+        <v>129223439</v>
       </c>
       <c r="B50" t="n">
-        <v>57723</v>
+        <v>57883</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7321,27 +7337,36 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7355,13 +7380,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490056</v>
+        <v>490044</v>
       </c>
       <c r="R50" t="n">
-        <v>7004912</v>
+        <v>7004789</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7390,7 +7415,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7400,12 +7425,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7420,26 +7445,6 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7457,47 +7462,47 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129223439</v>
+        <v>129223831</v>
       </c>
       <c r="B51" t="n">
-        <v>57883</v>
+        <v>98659</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7511,13 +7516,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490044</v>
+        <v>490057</v>
       </c>
       <c r="R51" t="n">
-        <v>7004789</v>
+        <v>7004780</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7546,7 +7551,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7556,12 +7561,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
+          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7593,47 +7598,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129223831</v>
+        <v>129230834</v>
       </c>
       <c r="B52" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7647,13 +7643,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490057</v>
+        <v>490020</v>
       </c>
       <c r="R52" t="n">
-        <v>7004780</v>
+        <v>7004888</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7682,7 +7678,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7692,12 +7688,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7712,6 +7708,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7729,43 +7745,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129230834</v>
+        <v>129226046</v>
       </c>
       <c r="B53" t="n">
-        <v>57723</v>
+        <v>80176</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7774,13 +7785,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490020</v>
+        <v>490078</v>
       </c>
       <c r="R53" t="n">
-        <v>7004888</v>
+        <v>7004812</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7809,7 +7820,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7819,12 +7830,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
+          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7843,22 +7854,22 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7876,10 +7887,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129226046</v>
+        <v>129231961</v>
       </c>
       <c r="B54" t="n">
-        <v>80176</v>
+        <v>98576</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7887,27 +7898,32 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7916,13 +7932,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490078</v>
+        <v>489928</v>
       </c>
       <c r="R54" t="n">
-        <v>7004812</v>
+        <v>7004745</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7951,7 +7967,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7961,12 +7977,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7981,26 +7992,6 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -8018,38 +8009,47 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129231961</v>
+        <v>129226468</v>
       </c>
       <c r="B55" t="n">
-        <v>98576</v>
+        <v>98659</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -8063,13 +8063,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489928</v>
+        <v>490119</v>
       </c>
       <c r="R55" t="n">
-        <v>7004745</v>
+        <v>7004845</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8108,7 +8108,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8140,47 +8145,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129226468</v>
+        <v>129230183</v>
       </c>
       <c r="B56" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -8194,13 +8190,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490119</v>
+        <v>490060</v>
       </c>
       <c r="R56" t="n">
-        <v>7004845</v>
+        <v>7004914</v>
       </c>
       <c r="S56" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8229,7 +8225,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8239,12 +8235,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8259,6 +8255,26 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8423,38 +8439,47 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129230183</v>
+        <v>129225550</v>
       </c>
       <c r="B58" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8468,13 +8493,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490060</v>
+        <v>490157</v>
       </c>
       <c r="R58" t="n">
-        <v>7004914</v>
+        <v>7004793</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8503,7 +8528,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8513,12 +8538,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8533,26 +8558,6 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8570,67 +8575,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129225550</v>
+        <v>129223232</v>
       </c>
       <c r="B59" t="n">
-        <v>98659</v>
+        <v>79035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490157</v>
+        <v>490017</v>
       </c>
       <c r="R59" t="n">
-        <v>7004793</v>
+        <v>7004780</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8659,7 +8645,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8669,12 +8655,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8689,6 +8670,26 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8706,10 +8707,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129223232</v>
+        <v>129225914</v>
       </c>
       <c r="B60" t="n">
-        <v>79035</v>
+        <v>57885</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8717,37 +8718,57 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490017</v>
+        <v>490106</v>
       </c>
       <c r="R60" t="n">
-        <v>7004780</v>
+        <v>7004828</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8776,7 +8797,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8786,7 +8807,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Synobservation av minst 2 livliga talltitor i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8801,26 +8827,6 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129227061</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>129230577</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -954,38 +954,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129230003</v>
+        <v>129228951</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -999,13 +1008,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490061</v>
+        <v>490119</v>
       </c>
       <c r="R4" t="n">
-        <v>7004922</v>
+        <v>7004879</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,7 +1043,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1053,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
+          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,26 +1073,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1101,10 +1090,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129230622</v>
+        <v>129230003</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1121,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1146,13 +1135,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490077</v>
+        <v>490061</v>
       </c>
       <c r="R5" t="n">
-        <v>7004897</v>
+        <v>7004922</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1181,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1191,12 +1180,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1248,47 +1237,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129228951</v>
+        <v>129230622</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1302,13 +1282,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490119</v>
+        <v>490077</v>
       </c>
       <c r="R6" t="n">
-        <v>7004879</v>
+        <v>7004897</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1337,7 +1317,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1347,12 +1327,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1367,6 +1347,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1384,64 +1384,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129226982</v>
+        <v>129224447</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490196</v>
+        <v>490020</v>
       </c>
       <c r="R7" t="n">
-        <v>7004884</v>
+        <v>7004694</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1473,7 +1454,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1483,12 +1464,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1503,6 +1479,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1520,10 +1516,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129224447</v>
+        <v>129223103</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,37 +1527,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490020</v>
+        <v>489959</v>
       </c>
       <c r="R8" t="n">
-        <v>7004694</v>
+        <v>7004819</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1590,7 +1596,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1600,7 +1606,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1629,12 +1640,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1652,38 +1663,47 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129223103</v>
+        <v>129226982</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1697,13 +1717,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489959</v>
+        <v>490196</v>
       </c>
       <c r="R9" t="n">
-        <v>7004819</v>
+        <v>7004884</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1732,7 +1752,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1742,12 +1762,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1762,26 +1782,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1802,7 +1802,7 @@
         <v>129226861</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>129231117</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129231914</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2203,43 +2203,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129231535</v>
+        <v>129224667</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2248,10 +2252,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489991</v>
+        <v>490027</v>
       </c>
       <c r="R13" t="n">
-        <v>7004843</v>
+        <v>7004700</v>
       </c>
       <c r="S13" t="n">
         <v>8</v>
@@ -2283,7 +2287,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2293,12 +2297,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 250 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2313,26 +2317,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2350,10 +2334,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129230279</v>
+        <v>129231535</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2395,13 +2379,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490064</v>
+        <v>489991</v>
       </c>
       <c r="R14" t="n">
-        <v>7004903</v>
+        <v>7004843</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2430,7 +2414,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2440,7 +2424,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2497,10 +2481,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129230462</v>
+        <v>129230279</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2542,13 +2526,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490066</v>
+        <v>490064</v>
       </c>
       <c r="R15" t="n">
-        <v>7004896</v>
+        <v>7004903</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2577,7 +2561,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2587,12 +2571,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2644,47 +2628,43 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129224667</v>
+        <v>129230462</v>
       </c>
       <c r="B16" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2693,10 +2673,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490027</v>
+        <v>490066</v>
       </c>
       <c r="R16" t="n">
-        <v>7004700</v>
+        <v>7004896</v>
       </c>
       <c r="S16" t="n">
         <v>8</v>
@@ -2728,7 +2708,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2738,12 +2718,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minst 250 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2758,6 +2738,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2778,7 +2778,7 @@
         <v>129230594</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>129225817</v>
       </c>
       <c r="B18" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>129230997</v>
       </c>
       <c r="B19" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>129229350</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>129225796</v>
       </c>
       <c r="B21" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3490,64 +3490,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129225751</v>
+        <v>129230877</v>
       </c>
       <c r="B22" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490094</v>
+        <v>490026</v>
       </c>
       <c r="R22" t="n">
-        <v>7004803</v>
+        <v>7004861</v>
       </c>
       <c r="S22" t="n">
         <v>11</v>
@@ -3579,7 +3560,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3589,12 +3570,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3609,6 +3585,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3626,10 +3622,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129230745</v>
+        <v>129225751</v>
       </c>
       <c r="B23" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3656,7 +3652,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3680,10 +3676,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490076</v>
+        <v>490094</v>
       </c>
       <c r="R23" t="n">
-        <v>7004871</v>
+        <v>7004803</v>
       </c>
       <c r="S23" t="n">
         <v>11</v>
@@ -3715,7 +3711,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3725,12 +3721,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3762,45 +3758,64 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129230877</v>
+        <v>129230745</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490026</v>
+        <v>490076</v>
       </c>
       <c r="R24" t="n">
-        <v>7004861</v>
+        <v>7004871</v>
       </c>
       <c r="S24" t="n">
         <v>11</v>
@@ -3832,7 +3847,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3842,7 +3857,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3857,26 +3877,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3894,38 +3894,47 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129230367</v>
+        <v>129226592</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3939,13 +3948,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490063</v>
+        <v>490132</v>
       </c>
       <c r="R25" t="n">
-        <v>7004901</v>
+        <v>7004833</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3974,7 +3983,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3984,12 +3993,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4004,26 +4013,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4041,48 +4030,67 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129229156</v>
+        <v>129225418</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490069</v>
+        <v>490122</v>
       </c>
       <c r="R26" t="n">
-        <v>7004928</v>
+        <v>7004771</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4111,7 +4119,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4121,7 +4129,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4136,26 +4149,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4173,10 +4166,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129226592</v>
+        <v>129225602</v>
       </c>
       <c r="B27" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4203,7 +4196,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4213,7 +4206,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4227,13 +4220,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490132</v>
+        <v>490142</v>
       </c>
       <c r="R27" t="n">
-        <v>7004833</v>
+        <v>7004806</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4262,7 +4255,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4272,12 +4265,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4309,45 +4302,64 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129227087</v>
+        <v>129225165</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490187</v>
+        <v>490124</v>
       </c>
       <c r="R28" t="n">
-        <v>7004903</v>
+        <v>7004767</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -4379,7 +4391,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4389,7 +4401,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4404,26 +4421,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4441,10 +4438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129230525</v>
+        <v>129229156</v>
       </c>
       <c r="B29" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4452,47 +4449,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490071</v>
+        <v>490069</v>
       </c>
       <c r="R29" t="n">
-        <v>7004894</v>
+        <v>7004928</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4521,7 +4508,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4531,12 +4518,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4565,12 +4547,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4588,67 +4570,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129225418</v>
+        <v>129227087</v>
       </c>
       <c r="B30" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490122</v>
+        <v>490187</v>
       </c>
       <c r="R30" t="n">
-        <v>7004771</v>
+        <v>7004903</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4677,7 +4640,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4687,12 +4650,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4707,6 +4665,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4724,67 +4702,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129225602</v>
+        <v>129225967</v>
       </c>
       <c r="B31" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490142</v>
+        <v>490095</v>
       </c>
       <c r="R31" t="n">
-        <v>7004806</v>
+        <v>7004830</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4813,7 +4772,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4823,12 +4782,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4843,6 +4797,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4860,47 +4834,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129225165</v>
+        <v>129230367</v>
       </c>
       <c r="B32" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4914,10 +4879,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490124</v>
+        <v>490063</v>
       </c>
       <c r="R32" t="n">
-        <v>7004767</v>
+        <v>7004901</v>
       </c>
       <c r="S32" t="n">
         <v>9</v>
@@ -4949,7 +4914,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4959,12 +4924,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4979,6 +4944,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4996,10 +4981,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129225967</v>
+        <v>129230525</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5007,37 +4992,47 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490095</v>
+        <v>490071</v>
       </c>
       <c r="R33" t="n">
-        <v>7004830</v>
+        <v>7004894</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5066,7 +5061,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5076,7 +5071,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5131,7 +5131,7 @@
         <v>129224808</v>
       </c>
       <c r="B34" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5265,52 +5265,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129228038</v>
+        <v>129223375</v>
       </c>
       <c r="B35" t="n">
-        <v>98659</v>
+        <v>80173</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5319,13 +5305,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490161</v>
+        <v>490028</v>
       </c>
       <c r="R35" t="n">
-        <v>7004940</v>
+        <v>7004796</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5354,7 +5340,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5364,12 +5350,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5383,7 +5364,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5401,53 +5402,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129223375</v>
+        <v>129227795</v>
       </c>
       <c r="B36" t="n">
-        <v>80169</v>
+        <v>79039</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490028</v>
+        <v>490175</v>
       </c>
       <c r="R36" t="n">
-        <v>7004796</v>
+        <v>7004918</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5476,7 +5472,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5486,7 +5482,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5505,22 +5506,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5538,48 +5539,67 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129227795</v>
+        <v>129228038</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490175</v>
+        <v>490161</v>
       </c>
       <c r="R37" t="n">
-        <v>7004918</v>
+        <v>7004940</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5608,7 +5628,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5618,12 +5638,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5637,27 +5657,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5678,7 +5678,7 @@
         <v>129231240</v>
       </c>
       <c r="B38" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>129223986</v>
       </c>
       <c r="B39" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5948,52 +5948,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129223203</v>
+        <v>129230966</v>
       </c>
       <c r="B40" t="n">
-        <v>98659</v>
+        <v>80144</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -6002,10 +5988,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489995</v>
+        <v>490020</v>
       </c>
       <c r="R40" t="n">
-        <v>7004788</v>
+        <v>7004857</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -6037,7 +6023,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6047,12 +6033,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6067,6 +6048,26 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6084,38 +6085,52 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129230966</v>
+        <v>129223203</v>
       </c>
       <c r="B41" t="n">
-        <v>80140</v>
+        <v>98669</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -6124,10 +6139,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490020</v>
+        <v>489995</v>
       </c>
       <c r="R41" t="n">
-        <v>7004857</v>
+        <v>7004788</v>
       </c>
       <c r="S41" t="n">
         <v>9</v>
@@ -6159,7 +6174,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6169,7 +6184,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6184,26 +6204,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6224,7 +6224,7 @@
         <v>129227281</v>
       </c>
       <c r="B42" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>129222983</v>
       </c>
       <c r="B43" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6504,43 +6504,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129229897</v>
+        <v>129226789</v>
       </c>
       <c r="B44" t="n">
-        <v>57723</v>
+        <v>92471</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6549,13 +6544,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490072</v>
+        <v>490174</v>
       </c>
       <c r="R44" t="n">
-        <v>7004920</v>
+        <v>7004879</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6584,7 +6579,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6594,12 +6589,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6613,27 +6603,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6651,38 +6621,43 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129226789</v>
+        <v>129229897</v>
       </c>
       <c r="B45" t="n">
-        <v>92464</v>
+        <v>57725</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6691,13 +6666,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490174</v>
+        <v>490072</v>
       </c>
       <c r="R45" t="n">
-        <v>7004879</v>
+        <v>7004920</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6726,7 +6701,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6736,7 +6711,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6750,7 +6730,27 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6771,7 +6771,7 @@
         <v>129224339</v>
       </c>
       <c r="B46" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6900,10 +6900,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129229015</v>
+        <v>129230332</v>
       </c>
       <c r="B47" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6911,37 +6911,47 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490105</v>
+        <v>490052</v>
       </c>
       <c r="R47" t="n">
-        <v>7004966</v>
+        <v>7004901</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6970,7 +6980,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6980,7 +6990,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6994,7 +7009,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -7009,12 +7024,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7032,10 +7047,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129230332</v>
+        <v>129230142</v>
       </c>
       <c r="B48" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7077,13 +7092,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490052</v>
+        <v>490056</v>
       </c>
       <c r="R48" t="n">
-        <v>7004901</v>
+        <v>7004912</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7112,7 +7127,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7122,7 +7137,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7179,10 +7194,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129230142</v>
+        <v>129229015</v>
       </c>
       <c r="B49" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7190,47 +7205,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490056</v>
+        <v>490105</v>
       </c>
       <c r="R49" t="n">
-        <v>7004912</v>
+        <v>7004966</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7259,7 +7264,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7269,12 +7274,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7329,7 +7329,7 @@
         <v>129223439</v>
       </c>
       <c r="B50" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7462,47 +7462,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129223831</v>
+        <v>129230834</v>
       </c>
       <c r="B51" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7516,13 +7507,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490057</v>
+        <v>490020</v>
       </c>
       <c r="R51" t="n">
-        <v>7004780</v>
+        <v>7004888</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7551,7 +7542,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7561,12 +7552,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7581,6 +7572,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7598,38 +7609,47 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129230834</v>
+        <v>129223831</v>
       </c>
       <c r="B52" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7643,13 +7663,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490020</v>
+        <v>490057</v>
       </c>
       <c r="R52" t="n">
-        <v>7004888</v>
+        <v>7004780</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7678,7 +7698,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7688,12 +7708,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
+          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7708,26 +7728,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7745,10 +7745,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129226046</v>
+        <v>129231961</v>
       </c>
       <c r="B53" t="n">
-        <v>80176</v>
+        <v>98586</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7756,27 +7756,32 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7785,13 +7790,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490078</v>
+        <v>489928</v>
       </c>
       <c r="R53" t="n">
-        <v>7004812</v>
+        <v>7004745</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7820,7 +7825,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7830,12 +7835,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7850,26 +7850,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7887,38 +7867,47 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129231961</v>
+        <v>129226468</v>
       </c>
       <c r="B54" t="n">
-        <v>98576</v>
+        <v>98669</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7932,13 +7921,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489928</v>
+        <v>490119</v>
       </c>
       <c r="R54" t="n">
-        <v>7004745</v>
+        <v>7004845</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7967,7 +7956,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7977,7 +7966,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8009,52 +8003,38 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129226468</v>
+        <v>129226046</v>
       </c>
       <c r="B55" t="n">
-        <v>98659</v>
+        <v>80180</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -8063,10 +8043,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490119</v>
+        <v>490078</v>
       </c>
       <c r="R55" t="n">
-        <v>7004845</v>
+        <v>7004812</v>
       </c>
       <c r="S55" t="n">
         <v>11</v>
@@ -8098,7 +8078,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8108,12 +8088,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
+          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8128,6 +8108,26 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8145,10 +8145,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129230183</v>
+        <v>129222854</v>
       </c>
       <c r="B56" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8190,13 +8190,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490060</v>
+        <v>489942</v>
       </c>
       <c r="R56" t="n">
-        <v>7004914</v>
+        <v>7004813</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8235,12 +8235,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8292,10 +8292,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129222854</v>
+        <v>129230183</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8337,13 +8337,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489942</v>
+        <v>490060</v>
       </c>
       <c r="R57" t="n">
-        <v>7004813</v>
+        <v>7004914</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8439,67 +8439,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129225550</v>
+        <v>129223232</v>
       </c>
       <c r="B58" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490157</v>
+        <v>490017</v>
       </c>
       <c r="R58" t="n">
-        <v>7004793</v>
+        <v>7004780</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8528,7 +8509,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8538,12 +8519,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8558,6 +8534,26 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8575,48 +8571,67 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129223232</v>
+        <v>129225550</v>
       </c>
       <c r="B59" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490017</v>
+        <v>490157</v>
       </c>
       <c r="R59" t="n">
-        <v>7004780</v>
+        <v>7004793</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8645,7 +8660,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8655,7 +8670,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8670,26 +8690,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -5128,10 +5128,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129224808</v>
+        <v>129223375</v>
       </c>
       <c r="B34" t="n">
-        <v>92233</v>
+        <v>80173</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5139,27 +5139,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5168,13 +5168,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490107</v>
+        <v>490028</v>
       </c>
       <c r="R34" t="n">
-        <v>7004741</v>
+        <v>7004796</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5232,22 +5232,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5265,53 +5265,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129223375</v>
+        <v>129227795</v>
       </c>
       <c r="B35" t="n">
-        <v>80173</v>
+        <v>79039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490028</v>
+        <v>490175</v>
       </c>
       <c r="R35" t="n">
-        <v>7004796</v>
+        <v>7004918</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5340,7 +5335,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5350,7 +5345,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5369,22 +5369,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5402,45 +5402,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129227795</v>
+        <v>129224808</v>
       </c>
       <c r="B36" t="n">
-        <v>79039</v>
+        <v>92233</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490175</v>
+        <v>490107</v>
       </c>
       <c r="R36" t="n">
-        <v>7004918</v>
+        <v>7004741</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -5472,7 +5477,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5482,12 +5487,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5516,12 +5516,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -7462,38 +7462,47 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129230834</v>
+        <v>129223831</v>
       </c>
       <c r="B51" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7507,13 +7516,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490020</v>
+        <v>490057</v>
       </c>
       <c r="R51" t="n">
-        <v>7004888</v>
+        <v>7004780</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7542,7 +7551,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7552,12 +7561,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
+          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7572,26 +7581,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7609,47 +7598,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129223831</v>
+        <v>129230834</v>
       </c>
       <c r="B52" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7663,13 +7643,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490057</v>
+        <v>490020</v>
       </c>
       <c r="R52" t="n">
-        <v>7004780</v>
+        <v>7004888</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7698,7 +7678,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7708,12 +7688,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7728,6 +7708,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -957,7 +957,7 @@
         <v>129228951</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1516,38 +1516,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129223103</v>
+        <v>129226982</v>
       </c>
       <c r="B8" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1561,13 +1570,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489959</v>
+        <v>490196</v>
       </c>
       <c r="R8" t="n">
-        <v>7004819</v>
+        <v>7004884</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1596,7 +1605,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1606,12 +1615,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1626,26 +1635,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1663,10 +1652,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129226982</v>
+        <v>129226861</v>
       </c>
       <c r="B9" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1693,7 +1682,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1717,7 +1706,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490196</v>
+        <v>490181</v>
       </c>
       <c r="R9" t="n">
         <v>7004884</v>
@@ -1752,7 +1741,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1762,12 +1751,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1799,47 +1788,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129226861</v>
+        <v>129223103</v>
       </c>
       <c r="B10" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1853,13 +1833,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490181</v>
+        <v>489959</v>
       </c>
       <c r="R10" t="n">
-        <v>7004884</v>
+        <v>7004819</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1888,7 +1868,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1898,12 +1878,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1918,6 +1898,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2070,7 +2070,7 @@
         <v>129231914</v>
       </c>
       <c r="B12" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>129224667</v>
       </c>
       <c r="B13" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3490,45 +3490,64 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129230877</v>
+        <v>129225751</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490026</v>
+        <v>490094</v>
       </c>
       <c r="R22" t="n">
-        <v>7004861</v>
+        <v>7004803</v>
       </c>
       <c r="S22" t="n">
         <v>11</v>
@@ -3560,7 +3579,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3570,7 +3589,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3585,26 +3609,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3622,10 +3626,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129225751</v>
+        <v>129230745</v>
       </c>
       <c r="B23" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3652,7 +3656,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3676,10 +3680,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490094</v>
+        <v>490076</v>
       </c>
       <c r="R23" t="n">
-        <v>7004803</v>
+        <v>7004871</v>
       </c>
       <c r="S23" t="n">
         <v>11</v>
@@ -3711,7 +3715,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3721,12 +3725,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
+          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3758,64 +3762,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129230745</v>
+        <v>129230877</v>
       </c>
       <c r="B24" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490076</v>
+        <v>490026</v>
       </c>
       <c r="R24" t="n">
-        <v>7004871</v>
+        <v>7004861</v>
       </c>
       <c r="S24" t="n">
         <v>11</v>
@@ -3847,7 +3832,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3857,12 +3842,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3877,6 +3857,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3894,67 +3894,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129226592</v>
+        <v>129229156</v>
       </c>
       <c r="B25" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490132</v>
+        <v>490069</v>
       </c>
       <c r="R25" t="n">
-        <v>7004833</v>
+        <v>7004928</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3983,7 +3964,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3993,12 +3974,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4013,6 +3989,26 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4030,67 +4026,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129225418</v>
+        <v>129227087</v>
       </c>
       <c r="B26" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490122</v>
+        <v>490187</v>
       </c>
       <c r="R26" t="n">
-        <v>7004771</v>
+        <v>7004903</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4119,7 +4096,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4129,12 +4106,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4149,6 +4121,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4166,67 +4158,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129225602</v>
+        <v>129225967</v>
       </c>
       <c r="B27" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490142</v>
+        <v>490095</v>
       </c>
       <c r="R27" t="n">
-        <v>7004806</v>
+        <v>7004830</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4255,7 +4228,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4265,12 +4238,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4285,6 +4253,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4302,47 +4290,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129225165</v>
+        <v>129230367</v>
       </c>
       <c r="B28" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4356,10 +4335,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490124</v>
+        <v>490063</v>
       </c>
       <c r="R28" t="n">
-        <v>7004767</v>
+        <v>7004901</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -4391,7 +4370,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4401,12 +4380,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4421,6 +4400,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4438,10 +4437,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129229156</v>
+        <v>129230525</v>
       </c>
       <c r="B29" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4449,37 +4448,47 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490069</v>
+        <v>490071</v>
       </c>
       <c r="R29" t="n">
-        <v>7004928</v>
+        <v>7004894</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4508,7 +4517,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4518,7 +4527,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4547,12 +4561,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4570,48 +4584,67 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129227087</v>
+        <v>129226592</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490187</v>
+        <v>490132</v>
       </c>
       <c r="R30" t="n">
-        <v>7004903</v>
+        <v>7004833</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4640,7 +4673,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4650,7 +4683,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4665,26 +4703,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4702,48 +4720,67 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129225967</v>
+        <v>129225418</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490095</v>
+        <v>490122</v>
       </c>
       <c r="R31" t="n">
-        <v>7004830</v>
+        <v>7004771</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4772,7 +4809,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4782,7 +4819,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4797,26 +4839,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4834,38 +4856,47 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129230367</v>
+        <v>129225602</v>
       </c>
       <c r="B32" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4879,13 +4910,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490063</v>
+        <v>490142</v>
       </c>
       <c r="R32" t="n">
-        <v>7004901</v>
+        <v>7004806</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4914,7 +4945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4924,12 +4955,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4944,26 +4975,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4981,38 +4992,47 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129230525</v>
+        <v>129225165</v>
       </c>
       <c r="B33" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5026,13 +5046,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490071</v>
+        <v>490124</v>
       </c>
       <c r="R33" t="n">
-        <v>7004894</v>
+        <v>7004767</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5061,7 +5081,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5071,12 +5091,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5091,26 +5111,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5128,53 +5128,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129223375</v>
+        <v>129227795</v>
       </c>
       <c r="B34" t="n">
-        <v>80173</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490028</v>
+        <v>490175</v>
       </c>
       <c r="R34" t="n">
-        <v>7004796</v>
+        <v>7004918</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5203,7 +5198,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5213,7 +5208,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5232,22 +5232,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5265,48 +5265,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129227795</v>
+        <v>129223375</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>80173</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490175</v>
+        <v>490028</v>
       </c>
       <c r="R35" t="n">
-        <v>7004918</v>
+        <v>7004796</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5335,7 +5340,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5345,12 +5350,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5369,22 +5369,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5405,7 +5405,7 @@
         <v>129224808</v>
       </c>
       <c r="B36" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>129228038</v>
       </c>
       <c r="B37" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>129223986</v>
       </c>
       <c r="B39" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>129223203</v>
       </c>
       <c r="B41" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>129227281</v>
       </c>
       <c r="B42" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>129226789</v>
       </c>
       <c r="B44" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>129224339</v>
       </c>
       <c r="B46" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7462,47 +7462,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129223831</v>
+        <v>129230834</v>
       </c>
       <c r="B51" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7516,13 +7507,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490057</v>
+        <v>490020</v>
       </c>
       <c r="R51" t="n">
-        <v>7004780</v>
+        <v>7004888</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7551,7 +7542,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7561,12 +7552,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7581,6 +7572,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7598,38 +7609,47 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129230834</v>
+        <v>129223831</v>
       </c>
       <c r="B52" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7643,13 +7663,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490020</v>
+        <v>490057</v>
       </c>
       <c r="R52" t="n">
-        <v>7004888</v>
+        <v>7004780</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7678,7 +7698,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7688,12 +7708,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
+          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7708,26 +7728,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7745,10 +7745,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129231961</v>
+        <v>129226046</v>
       </c>
       <c r="B53" t="n">
-        <v>98586</v>
+        <v>80180</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7756,32 +7756,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7790,13 +7785,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489928</v>
+        <v>490078</v>
       </c>
       <c r="R53" t="n">
-        <v>7004745</v>
+        <v>7004812</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7825,7 +7820,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7835,7 +7830,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7850,6 +7850,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7867,47 +7887,38 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129226468</v>
+        <v>129231961</v>
       </c>
       <c r="B54" t="n">
-        <v>98669</v>
+        <v>98593</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7921,13 +7932,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490119</v>
+        <v>489928</v>
       </c>
       <c r="R54" t="n">
-        <v>7004845</v>
+        <v>7004745</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7956,7 +7967,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7966,12 +7977,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8003,38 +8009,52 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129226046</v>
+        <v>129226468</v>
       </c>
       <c r="B55" t="n">
-        <v>80180</v>
+        <v>98676</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -8043,10 +8063,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490078</v>
+        <v>490119</v>
       </c>
       <c r="R55" t="n">
-        <v>7004812</v>
+        <v>7004845</v>
       </c>
       <c r="S55" t="n">
         <v>11</v>
@@ -8078,7 +8098,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8088,12 +8108,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
+          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8108,26 +8128,6 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8439,48 +8439,67 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129223232</v>
+        <v>129225550</v>
       </c>
       <c r="B58" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490017</v>
+        <v>490157</v>
       </c>
       <c r="R58" t="n">
-        <v>7004780</v>
+        <v>7004793</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8509,7 +8528,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8519,7 +8538,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8534,26 +8558,6 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8571,67 +8575,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129225550</v>
+        <v>129223232</v>
       </c>
       <c r="B59" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490157</v>
+        <v>490017</v>
       </c>
       <c r="R59" t="n">
-        <v>7004793</v>
+        <v>7004780</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8660,7 +8645,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8670,12 +8655,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8690,6 +8670,26 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129227061</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>129230577</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -954,47 +954,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129228951</v>
+        <v>129230003</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1008,13 +999,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490119</v>
+        <v>490061</v>
       </c>
       <c r="R4" t="n">
-        <v>7004879</v>
+        <v>7004922</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1043,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1053,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,6 +1064,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1090,10 +1101,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129230003</v>
+        <v>129230622</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1132,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1135,13 +1146,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490061</v>
+        <v>490077</v>
       </c>
       <c r="R5" t="n">
-        <v>7004922</v>
+        <v>7004897</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1170,7 +1181,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1180,12 +1191,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
+          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1237,38 +1248,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129230622</v>
+        <v>129228951</v>
       </c>
       <c r="B6" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1282,13 +1302,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490077</v>
+        <v>490119</v>
       </c>
       <c r="R6" t="n">
-        <v>7004897</v>
+        <v>7004879</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1317,7 +1337,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1327,12 +1347,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
+          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1347,26 +1367,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1387,7 +1387,7 @@
         <v>129224447</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1516,47 +1516,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129226982</v>
+        <v>129223103</v>
       </c>
       <c r="B8" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1570,13 +1561,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490196</v>
+        <v>489959</v>
       </c>
       <c r="R8" t="n">
-        <v>7004884</v>
+        <v>7004819</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1605,7 +1596,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1615,12 +1606,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1635,6 +1626,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1652,10 +1663,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129226861</v>
+        <v>129226982</v>
       </c>
       <c r="B9" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1682,7 +1693,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1706,7 +1717,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490181</v>
+        <v>490196</v>
       </c>
       <c r="R9" t="n">
         <v>7004884</v>
@@ -1741,7 +1752,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1751,12 +1762,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1788,38 +1799,47 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129223103</v>
+        <v>129226861</v>
       </c>
       <c r="B10" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1833,13 +1853,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489959</v>
+        <v>490181</v>
       </c>
       <c r="R10" t="n">
-        <v>7004819</v>
+        <v>7004884</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1868,7 +1888,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1878,12 +1898,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1898,26 +1918,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1938,7 +1938,7 @@
         <v>129231117</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129231914</v>
       </c>
       <c r="B12" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2203,47 +2203,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129224667</v>
+        <v>129231535</v>
       </c>
       <c r="B13" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2252,10 +2248,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490027</v>
+        <v>489991</v>
       </c>
       <c r="R13" t="n">
-        <v>7004700</v>
+        <v>7004843</v>
       </c>
       <c r="S13" t="n">
         <v>8</v>
@@ -2287,7 +2283,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2297,12 +2293,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 250 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2317,6 +2313,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2334,10 +2350,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129231535</v>
+        <v>129230279</v>
       </c>
       <c r="B14" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2379,13 +2395,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489991</v>
+        <v>490064</v>
       </c>
       <c r="R14" t="n">
-        <v>7004843</v>
+        <v>7004903</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2414,7 +2430,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2424,7 +2440,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2481,10 +2497,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129230279</v>
+        <v>129230462</v>
       </c>
       <c r="B15" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2526,13 +2542,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490064</v>
+        <v>490066</v>
       </c>
       <c r="R15" t="n">
-        <v>7004903</v>
+        <v>7004896</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2561,7 +2577,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2571,12 +2587,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2628,10 +2644,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129230462</v>
+        <v>129230594</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2673,13 +2689,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490066</v>
+        <v>490071</v>
       </c>
       <c r="R16" t="n">
-        <v>7004896</v>
+        <v>7004887</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2708,7 +2724,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2718,7 +2734,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2775,43 +2791,47 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129230594</v>
+        <v>129224667</v>
       </c>
       <c r="B17" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2820,13 +2840,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490071</v>
+        <v>490027</v>
       </c>
       <c r="R17" t="n">
-        <v>7004887</v>
+        <v>7004700</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2855,7 +2875,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2865,12 +2885,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Minst 250 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2885,26 +2905,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2925,7 +2925,7 @@
         <v>129225817</v>
       </c>
       <c r="B18" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>129230997</v>
       </c>
       <c r="B19" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>129229350</v>
       </c>
       <c r="B20" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>129225796</v>
       </c>
       <c r="B21" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3490,64 +3490,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129225751</v>
+        <v>129230877</v>
       </c>
       <c r="B22" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490094</v>
+        <v>490026</v>
       </c>
       <c r="R22" t="n">
-        <v>7004803</v>
+        <v>7004861</v>
       </c>
       <c r="S22" t="n">
         <v>11</v>
@@ -3579,7 +3560,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3589,12 +3570,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3609,6 +3585,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3626,10 +3622,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129230745</v>
+        <v>129225751</v>
       </c>
       <c r="B23" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3656,7 +3652,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3680,10 +3676,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490076</v>
+        <v>490094</v>
       </c>
       <c r="R23" t="n">
-        <v>7004871</v>
+        <v>7004803</v>
       </c>
       <c r="S23" t="n">
         <v>11</v>
@@ -3715,7 +3711,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3725,12 +3721,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3762,45 +3758,64 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129230877</v>
+        <v>129230745</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490026</v>
+        <v>490076</v>
       </c>
       <c r="R24" t="n">
-        <v>7004861</v>
+        <v>7004871</v>
       </c>
       <c r="S24" t="n">
         <v>11</v>
@@ -3832,7 +3847,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3842,7 +3857,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3857,26 +3877,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3894,10 +3894,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129229156</v>
+        <v>129230367</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3905,37 +3905,47 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490069</v>
+        <v>490063</v>
       </c>
       <c r="R25" t="n">
-        <v>7004928</v>
+        <v>7004901</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3964,7 +3974,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3974,7 +3984,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4003,12 +4018,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4026,10 +4041,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129227087</v>
+        <v>129230525</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4037,37 +4052,47 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490187</v>
+        <v>490071</v>
       </c>
       <c r="R26" t="n">
-        <v>7004903</v>
+        <v>7004894</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4096,7 +4121,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4106,7 +4131,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4135,12 +4165,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4158,45 +4188,64 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129225967</v>
+        <v>129226592</v>
       </c>
       <c r="B27" t="n">
-        <v>79039</v>
+        <v>98678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490095</v>
+        <v>490132</v>
       </c>
       <c r="R27" t="n">
-        <v>7004830</v>
+        <v>7004833</v>
       </c>
       <c r="S27" t="n">
         <v>11</v>
@@ -4228,7 +4277,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4238,7 +4287,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4253,26 +4307,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4290,38 +4324,47 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129230367</v>
+        <v>129225418</v>
       </c>
       <c r="B28" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4335,13 +4378,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490063</v>
+        <v>490122</v>
       </c>
       <c r="R28" t="n">
-        <v>7004901</v>
+        <v>7004771</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4370,7 +4413,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4380,12 +4423,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4400,26 +4443,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4437,38 +4460,47 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129230525</v>
+        <v>129225602</v>
       </c>
       <c r="B29" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4482,13 +4514,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490071</v>
+        <v>490142</v>
       </c>
       <c r="R29" t="n">
-        <v>7004894</v>
+        <v>7004806</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4517,7 +4549,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4527,12 +4559,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4547,26 +4579,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4584,10 +4596,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129226592</v>
+        <v>129225165</v>
       </c>
       <c r="B30" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4614,7 +4626,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4624,7 +4636,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4638,13 +4650,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490132</v>
+        <v>490124</v>
       </c>
       <c r="R30" t="n">
-        <v>7004833</v>
+        <v>7004767</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4673,7 +4685,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4683,12 +4695,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4720,67 +4732,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129225418</v>
+        <v>129229156</v>
       </c>
       <c r="B31" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490122</v>
+        <v>490069</v>
       </c>
       <c r="R31" t="n">
-        <v>7004771</v>
+        <v>7004928</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4809,7 +4802,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4819,12 +4812,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4839,6 +4827,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4856,67 +4864,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129225602</v>
+        <v>129227087</v>
       </c>
       <c r="B32" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490142</v>
+        <v>490187</v>
       </c>
       <c r="R32" t="n">
-        <v>7004806</v>
+        <v>7004903</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4945,7 +4934,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4955,12 +4944,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4975,6 +4959,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4992,67 +4996,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129225165</v>
+        <v>129225967</v>
       </c>
       <c r="B33" t="n">
-        <v>98676</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490124</v>
+        <v>490095</v>
       </c>
       <c r="R33" t="n">
-        <v>7004767</v>
+        <v>7004830</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5081,7 +5066,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5091,12 +5076,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5111,6 +5091,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5128,45 +5128,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129227795</v>
+        <v>129224808</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>92242</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490175</v>
+        <v>490107</v>
       </c>
       <c r="R34" t="n">
-        <v>7004918</v>
+        <v>7004741</v>
       </c>
       <c r="S34" t="n">
         <v>9</v>
@@ -5198,7 +5203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5208,12 +5213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5268,7 +5268,7 @@
         <v>129223375</v>
       </c>
       <c r="B35" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5402,50 +5402,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129224808</v>
+        <v>129227795</v>
       </c>
       <c r="B36" t="n">
-        <v>92240</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490107</v>
+        <v>490175</v>
       </c>
       <c r="R36" t="n">
-        <v>7004741</v>
+        <v>7004918</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -5477,7 +5472,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5487,7 +5482,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5516,12 +5516,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5542,7 +5542,7 @@
         <v>129228038</v>
       </c>
       <c r="B37" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>129231240</v>
       </c>
       <c r="B38" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>129223986</v>
       </c>
       <c r="B39" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>129230966</v>
       </c>
       <c r="B40" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>129223203</v>
       </c>
       <c r="B41" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>129227281</v>
       </c>
       <c r="B42" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>129222983</v>
       </c>
       <c r="B43" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6504,38 +6504,43 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129226789</v>
+        <v>129229897</v>
       </c>
       <c r="B44" t="n">
-        <v>92478</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6544,13 +6549,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490174</v>
+        <v>490072</v>
       </c>
       <c r="R44" t="n">
-        <v>7004879</v>
+        <v>7004920</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6579,7 +6584,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6589,7 +6594,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6603,7 +6613,27 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6621,38 +6651,43 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129229897</v>
+        <v>129224339</v>
       </c>
       <c r="B45" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6666,13 +6701,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490072</v>
+        <v>490008</v>
       </c>
       <c r="R45" t="n">
-        <v>7004920</v>
+        <v>7004696</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6701,7 +6736,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6711,12 +6746,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6731,26 +6766,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6768,48 +6783,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129224339</v>
+        <v>129226789</v>
       </c>
       <c r="B46" t="n">
-        <v>98676</v>
+        <v>92480</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6818,13 +6823,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490008</v>
+        <v>490174</v>
       </c>
       <c r="R46" t="n">
-        <v>7004696</v>
+        <v>7004879</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6853,7 +6858,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6863,12 +6868,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6903,7 +6903,7 @@
         <v>129230332</v>
       </c>
       <c r="B47" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>129230142</v>
       </c>
       <c r="B48" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>129229015</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>129223439</v>
       </c>
       <c r="B50" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>129230834</v>
       </c>
       <c r="B51" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         <v>129223831</v>
       </c>
       <c r="B52" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>129226046</v>
       </c>
       <c r="B53" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>129231961</v>
       </c>
       <c r="B54" t="n">
-        <v>98593</v>
+        <v>98595</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>129226468</v>
       </c>
       <c r="B55" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>129222854</v>
       </c>
       <c r="B56" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>129230183</v>
       </c>
       <c r="B57" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>129225550</v>
       </c>
       <c r="B58" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>129223232</v>
       </c>
       <c r="B59" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>129225914</v>
       </c>
       <c r="B60" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -954,38 +954,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129230003</v>
+        <v>129228951</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -999,13 +1008,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490061</v>
+        <v>490119</v>
       </c>
       <c r="R4" t="n">
-        <v>7004922</v>
+        <v>7004879</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,7 +1043,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1053,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
+          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,26 +1073,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1101,7 +1090,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129230622</v>
+        <v>129230003</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1132,7 +1121,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1146,13 +1135,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490077</v>
+        <v>490061</v>
       </c>
       <c r="R5" t="n">
-        <v>7004897</v>
+        <v>7004922</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1181,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1191,12 +1180,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1248,47 +1237,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129228951</v>
+        <v>129230622</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1302,13 +1282,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490119</v>
+        <v>490077</v>
       </c>
       <c r="R6" t="n">
-        <v>7004879</v>
+        <v>7004897</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1337,7 +1317,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1347,12 +1327,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1367,6 +1347,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -3490,45 +3490,64 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129230877</v>
+        <v>129225751</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490026</v>
+        <v>490094</v>
       </c>
       <c r="R22" t="n">
-        <v>7004861</v>
+        <v>7004803</v>
       </c>
       <c r="S22" t="n">
         <v>11</v>
@@ -3560,7 +3579,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3570,7 +3589,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3585,26 +3609,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3622,7 +3626,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129225751</v>
+        <v>129230745</v>
       </c>
       <c r="B23" t="n">
         <v>98678</v>
@@ -3652,7 +3656,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3676,10 +3680,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490094</v>
+        <v>490076</v>
       </c>
       <c r="R23" t="n">
-        <v>7004803</v>
+        <v>7004871</v>
       </c>
       <c r="S23" t="n">
         <v>11</v>
@@ -3711,7 +3715,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3721,12 +3725,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
+          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3758,64 +3762,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129230745</v>
+        <v>129230877</v>
       </c>
       <c r="B24" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490076</v>
+        <v>490026</v>
       </c>
       <c r="R24" t="n">
-        <v>7004871</v>
+        <v>7004861</v>
       </c>
       <c r="S24" t="n">
         <v>11</v>
@@ -3847,7 +3832,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3857,12 +3842,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3877,6 +3857,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3894,10 +3894,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129230367</v>
+        <v>129229156</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3905,47 +3905,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490063</v>
+        <v>490069</v>
       </c>
       <c r="R25" t="n">
-        <v>7004901</v>
+        <v>7004928</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3974,7 +3964,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3984,12 +3974,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4018,12 +4003,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4041,10 +4026,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129230525</v>
+        <v>129227087</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4052,47 +4037,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490071</v>
+        <v>490187</v>
       </c>
       <c r="R26" t="n">
-        <v>7004894</v>
+        <v>7004903</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4121,7 +4096,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4131,12 +4106,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4165,12 +4135,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4188,64 +4158,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129226592</v>
+        <v>129225967</v>
       </c>
       <c r="B27" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490132</v>
+        <v>490095</v>
       </c>
       <c r="R27" t="n">
-        <v>7004833</v>
+        <v>7004830</v>
       </c>
       <c r="S27" t="n">
         <v>11</v>
@@ -4277,7 +4228,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4287,12 +4238,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4307,6 +4253,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4324,47 +4290,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129225418</v>
+        <v>129230367</v>
       </c>
       <c r="B28" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4378,13 +4335,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490122</v>
+        <v>490063</v>
       </c>
       <c r="R28" t="n">
-        <v>7004771</v>
+        <v>7004901</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4413,7 +4370,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4423,12 +4380,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4443,6 +4400,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4460,47 +4437,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129225602</v>
+        <v>129230525</v>
       </c>
       <c r="B29" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4514,13 +4482,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490142</v>
+        <v>490071</v>
       </c>
       <c r="R29" t="n">
-        <v>7004806</v>
+        <v>7004894</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4549,7 +4517,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4559,12 +4527,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4579,6 +4547,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4596,7 +4584,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129225165</v>
+        <v>129226592</v>
       </c>
       <c r="B30" t="n">
         <v>98678</v>
@@ -4626,7 +4614,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4636,7 +4624,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4650,13 +4638,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490124</v>
+        <v>490132</v>
       </c>
       <c r="R30" t="n">
-        <v>7004767</v>
+        <v>7004833</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4685,7 +4673,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4695,12 +4683,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4732,48 +4720,67 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129229156</v>
+        <v>129225418</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490069</v>
+        <v>490122</v>
       </c>
       <c r="R31" t="n">
-        <v>7004928</v>
+        <v>7004771</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4802,7 +4809,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4812,7 +4819,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4827,26 +4839,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4864,48 +4856,67 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129227087</v>
+        <v>129225602</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490187</v>
+        <v>490142</v>
       </c>
       <c r="R32" t="n">
-        <v>7004903</v>
+        <v>7004806</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4934,7 +4945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4944,7 +4955,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4959,26 +4975,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4996,48 +4992,67 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129225967</v>
+        <v>129225165</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490095</v>
+        <v>490124</v>
       </c>
       <c r="R33" t="n">
-        <v>7004830</v>
+        <v>7004767</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5066,7 +5081,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5076,7 +5091,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5091,26 +5111,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5265,38 +5265,52 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129223375</v>
+        <v>129228038</v>
       </c>
       <c r="B35" t="n">
-        <v>80175</v>
+        <v>98678</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5305,13 +5319,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490028</v>
+        <v>490161</v>
       </c>
       <c r="R35" t="n">
-        <v>7004796</v>
+        <v>7004940</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5340,7 +5354,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5350,7 +5364,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5364,27 +5383,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5539,52 +5538,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129228038</v>
+        <v>129223375</v>
       </c>
       <c r="B37" t="n">
-        <v>98678</v>
+        <v>80175</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5593,13 +5578,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490161</v>
+        <v>490028</v>
       </c>
       <c r="R37" t="n">
-        <v>7004940</v>
+        <v>7004796</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5628,7 +5613,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5638,12 +5623,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5657,7 +5637,27 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5675,38 +5675,52 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129231240</v>
+        <v>129223986</v>
       </c>
       <c r="B38" t="n">
-        <v>80175</v>
+        <v>98678</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5715,13 +5729,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490033</v>
+        <v>490070</v>
       </c>
       <c r="R38" t="n">
-        <v>7004823</v>
+        <v>7004763</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5750,7 +5764,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5760,7 +5774,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 22 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5775,26 +5794,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5812,52 +5811,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129223986</v>
+        <v>129231240</v>
       </c>
       <c r="B39" t="n">
-        <v>98678</v>
+        <v>80175</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5866,13 +5851,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490070</v>
+        <v>490033</v>
       </c>
       <c r="R39" t="n">
-        <v>7004763</v>
+        <v>7004823</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5901,7 +5886,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5911,12 +5896,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Minst 22 plantor inom ca 1 m2 yta.</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5931,6 +5911,26 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -6504,38 +6504,43 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129229897</v>
+        <v>129224339</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6549,13 +6554,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490072</v>
+        <v>490008</v>
       </c>
       <c r="R44" t="n">
-        <v>7004920</v>
+        <v>7004696</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6584,7 +6589,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6594,12 +6599,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6614,26 +6619,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6651,43 +6636,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129224339</v>
+        <v>129229897</v>
       </c>
       <c r="B45" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6701,13 +6681,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490008</v>
+        <v>490072</v>
       </c>
       <c r="R45" t="n">
-        <v>7004696</v>
+        <v>7004920</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6736,7 +6716,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6746,12 +6726,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6766,6 +6746,26 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6900,10 +6900,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129230332</v>
+        <v>129223439</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6911,27 +6911,36 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6945,13 +6954,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490052</v>
+        <v>490044</v>
       </c>
       <c r="R47" t="n">
-        <v>7004901</v>
+        <v>7004789</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6980,7 +6989,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6990,12 +6999,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7010,26 +7019,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7047,10 +7036,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129230142</v>
+        <v>129229015</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7058,47 +7047,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490056</v>
+        <v>490105</v>
       </c>
       <c r="R48" t="n">
-        <v>7004912</v>
+        <v>7004966</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7127,7 +7106,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7137,12 +7116,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7156,7 +7130,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -7171,12 +7145,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7194,10 +7168,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129229015</v>
+        <v>129230332</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7205,37 +7179,47 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490105</v>
+        <v>490052</v>
       </c>
       <c r="R49" t="n">
-        <v>7004966</v>
+        <v>7004901</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7264,7 +7248,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7274,7 +7258,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7288,7 +7277,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -7303,12 +7292,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7326,10 +7315,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129223439</v>
+        <v>129230142</v>
       </c>
       <c r="B50" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7337,36 +7326,27 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7380,13 +7360,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490044</v>
+        <v>490056</v>
       </c>
       <c r="R50" t="n">
-        <v>7004789</v>
+        <v>7004912</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7415,7 +7395,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7425,12 +7405,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7445,6 +7425,26 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -8145,10 +8145,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129222854</v>
+        <v>129223232</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8156,47 +8156,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489942</v>
+        <v>490017</v>
       </c>
       <c r="R56" t="n">
-        <v>7004813</v>
+        <v>7004780</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8225,7 +8215,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8235,12 +8225,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8269,12 +8254,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8292,7 +8277,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129230183</v>
+        <v>129222854</v>
       </c>
       <c r="B57" t="n">
         <v>57727</v>
@@ -8337,13 +8322,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490060</v>
+        <v>489942</v>
       </c>
       <c r="R57" t="n">
-        <v>7004914</v>
+        <v>7004813</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8372,7 +8357,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8382,12 +8367,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8439,47 +8424,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129225550</v>
+        <v>129230183</v>
       </c>
       <c r="B58" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8493,13 +8469,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490157</v>
+        <v>490060</v>
       </c>
       <c r="R58" t="n">
-        <v>7004793</v>
+        <v>7004914</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8528,7 +8504,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8538,12 +8514,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8558,6 +8534,26 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8575,48 +8571,67 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129223232</v>
+        <v>129225550</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>98678</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490017</v>
+        <v>490157</v>
       </c>
       <c r="R59" t="n">
-        <v>7004780</v>
+        <v>7004793</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8645,7 +8660,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8655,7 +8670,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8670,26 +8690,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -1384,10 +1384,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129224447</v>
+        <v>129223103</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,37 +1395,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490020</v>
+        <v>489959</v>
       </c>
       <c r="R7" t="n">
-        <v>7004694</v>
+        <v>7004819</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1454,7 +1464,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1464,7 +1474,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1493,12 +1508,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1516,38 +1531,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129223103</v>
+        <v>129226982</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1561,13 +1585,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489959</v>
+        <v>490196</v>
       </c>
       <c r="R8" t="n">
-        <v>7004819</v>
+        <v>7004884</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1596,7 +1620,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1606,12 +1630,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1626,26 +1650,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1663,7 +1667,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129226982</v>
+        <v>129226861</v>
       </c>
       <c r="B9" t="n">
         <v>98678</v>
@@ -1693,7 +1697,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1717,7 +1721,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490196</v>
+        <v>490181</v>
       </c>
       <c r="R9" t="n">
         <v>7004884</v>
@@ -1752,7 +1756,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1762,12 +1766,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1799,64 +1803,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129226861</v>
+        <v>129224447</v>
       </c>
       <c r="B10" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490181</v>
+        <v>490020</v>
       </c>
       <c r="R10" t="n">
-        <v>7004884</v>
+        <v>7004694</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1888,7 +1873,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1898,12 +1883,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1918,6 +1898,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -4290,38 +4290,47 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129230367</v>
+        <v>129226592</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4335,13 +4344,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490063</v>
+        <v>490132</v>
       </c>
       <c r="R28" t="n">
-        <v>7004901</v>
+        <v>7004833</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4370,7 +4379,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4380,12 +4389,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4400,26 +4409,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4437,38 +4426,47 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129230525</v>
+        <v>129225418</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4482,10 +4480,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490071</v>
+        <v>490122</v>
       </c>
       <c r="R29" t="n">
-        <v>7004894</v>
+        <v>7004771</v>
       </c>
       <c r="S29" t="n">
         <v>8</v>
@@ -4517,7 +4515,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4527,12 +4525,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4547,26 +4545,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4584,7 +4562,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129226592</v>
+        <v>129225602</v>
       </c>
       <c r="B30" t="n">
         <v>98678</v>
@@ -4614,7 +4592,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4624,7 +4602,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4638,13 +4616,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490132</v>
+        <v>490142</v>
       </c>
       <c r="R30" t="n">
-        <v>7004833</v>
+        <v>7004806</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4673,7 +4651,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4683,12 +4661,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4720,7 +4698,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129225418</v>
+        <v>129225165</v>
       </c>
       <c r="B31" t="n">
         <v>98678</v>
@@ -4750,7 +4728,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4774,13 +4752,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490122</v>
+        <v>490124</v>
       </c>
       <c r="R31" t="n">
-        <v>7004771</v>
+        <v>7004767</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4809,7 +4787,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4819,12 +4797,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
+          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4856,47 +4834,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129225602</v>
+        <v>129230367</v>
       </c>
       <c r="B32" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4910,13 +4879,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490142</v>
+        <v>490063</v>
       </c>
       <c r="R32" t="n">
-        <v>7004806</v>
+        <v>7004901</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4945,7 +4914,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4955,12 +4924,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4975,6 +4944,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4992,47 +4981,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129225165</v>
+        <v>129230525</v>
       </c>
       <c r="B33" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5046,13 +5026,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490124</v>
+        <v>490071</v>
       </c>
       <c r="R33" t="n">
-        <v>7004767</v>
+        <v>7004894</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5081,7 +5061,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5091,12 +5071,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5111,6 +5091,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -6504,48 +6504,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129224339</v>
+        <v>129226789</v>
       </c>
       <c r="B44" t="n">
-        <v>98678</v>
+        <v>92480</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6554,13 +6544,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490008</v>
+        <v>490174</v>
       </c>
       <c r="R44" t="n">
-        <v>7004696</v>
+        <v>7004879</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6589,7 +6579,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6599,12 +6589,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6618,7 +6603,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6636,38 +6621,43 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129229897</v>
+        <v>129224339</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6681,13 +6671,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490072</v>
+        <v>490008</v>
       </c>
       <c r="R45" t="n">
-        <v>7004920</v>
+        <v>7004696</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6716,7 +6706,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6726,12 +6716,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6746,26 +6736,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6783,38 +6753,43 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129226789</v>
+        <v>129229897</v>
       </c>
       <c r="B46" t="n">
-        <v>92480</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6823,13 +6798,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490174</v>
+        <v>490072</v>
       </c>
       <c r="R46" t="n">
-        <v>7004879</v>
+        <v>7004920</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6858,7 +6833,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6868,7 +6843,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6882,7 +6862,27 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6900,10 +6900,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129223439</v>
+        <v>129229015</v>
       </c>
       <c r="B47" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6911,56 +6911,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490044</v>
+        <v>490105</v>
       </c>
       <c r="R47" t="n">
-        <v>7004789</v>
+        <v>7004966</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6989,7 +6970,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6999,12 +6980,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7018,7 +6994,27 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7036,10 +7032,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129229015</v>
+        <v>129230332</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7047,37 +7043,47 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490105</v>
+        <v>490052</v>
       </c>
       <c r="R48" t="n">
-        <v>7004966</v>
+        <v>7004901</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7106,7 +7112,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7116,7 +7122,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7130,7 +7141,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -7145,12 +7156,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7168,7 +7179,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129230332</v>
+        <v>129230142</v>
       </c>
       <c r="B49" t="n">
         <v>57727</v>
@@ -7213,13 +7224,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490052</v>
+        <v>490056</v>
       </c>
       <c r="R49" t="n">
-        <v>7004901</v>
+        <v>7004912</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7248,7 +7259,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7258,7 +7269,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7315,10 +7326,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129230142</v>
+        <v>129223439</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7326,27 +7337,36 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7360,13 +7380,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490056</v>
+        <v>490044</v>
       </c>
       <c r="R50" t="n">
-        <v>7004912</v>
+        <v>7004789</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7395,7 +7415,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7405,12 +7425,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7425,26 +7445,6 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7462,38 +7462,47 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129230834</v>
+        <v>129223831</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7507,13 +7516,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490020</v>
+        <v>490057</v>
       </c>
       <c r="R51" t="n">
-        <v>7004888</v>
+        <v>7004780</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7542,7 +7551,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7552,12 +7561,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
+          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7572,26 +7581,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7609,47 +7598,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129223831</v>
+        <v>129230834</v>
       </c>
       <c r="B52" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7663,13 +7643,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490057</v>
+        <v>490020</v>
       </c>
       <c r="R52" t="n">
-        <v>7004780</v>
+        <v>7004888</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7698,7 +7678,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7708,12 +7688,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7728,6 +7708,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129227061</v>
+        <v>129230577</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490204</v>
+        <v>490070</v>
       </c>
       <c r="R2" t="n">
-        <v>7004896</v>
+        <v>7004890</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,12 +799,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +822,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129230577</v>
+        <v>129227061</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,44 +833,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490070</v>
+        <v>490204</v>
       </c>
       <c r="R3" t="n">
-        <v>7004890</v>
+        <v>7004896</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,12 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:51</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,12 +931,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -954,47 +954,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129228951</v>
+        <v>129230003</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1008,13 +999,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490119</v>
+        <v>490061</v>
       </c>
       <c r="R4" t="n">
-        <v>7004879</v>
+        <v>7004922</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1043,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1053,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,6 +1064,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1090,7 +1101,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129230003</v>
+        <v>129230622</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1121,7 +1132,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1135,13 +1146,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490061</v>
+        <v>490077</v>
       </c>
       <c r="R5" t="n">
-        <v>7004922</v>
+        <v>7004897</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1170,7 +1181,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1180,12 +1191,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
+          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1237,38 +1248,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129230622</v>
+        <v>129228951</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1282,13 +1302,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490077</v>
+        <v>490119</v>
       </c>
       <c r="R6" t="n">
-        <v>7004897</v>
+        <v>7004879</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1317,7 +1337,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1327,12 +1347,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
+          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1347,26 +1367,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1384,10 +1384,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129223103</v>
+        <v>129224447</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,47 +1395,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489959</v>
+        <v>490020</v>
       </c>
       <c r="R7" t="n">
-        <v>7004819</v>
+        <v>7004694</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1464,7 +1454,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1474,12 +1464,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1508,12 +1493,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1531,47 +1516,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129226982</v>
+        <v>129223103</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1585,13 +1561,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490196</v>
+        <v>489959</v>
       </c>
       <c r="R8" t="n">
-        <v>7004884</v>
+        <v>7004819</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1620,7 +1596,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1630,12 +1606,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1650,6 +1626,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1667,10 +1663,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129226861</v>
+        <v>129226982</v>
       </c>
       <c r="B9" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1697,7 +1693,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1721,7 +1717,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490181</v>
+        <v>490196</v>
       </c>
       <c r="R9" t="n">
         <v>7004884</v>
@@ -1756,7 +1752,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1766,12 +1762,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1803,45 +1799,64 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129224447</v>
+        <v>129226861</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490020</v>
+        <v>490181</v>
       </c>
       <c r="R10" t="n">
-        <v>7004694</v>
+        <v>7004884</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1873,7 +1888,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1883,7 +1898,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1898,26 +1918,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2070,7 +2070,7 @@
         <v>129231914</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>129224667</v>
       </c>
       <c r="B17" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>129225751</v>
       </c>
       <c r="B22" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>129230745</v>
       </c>
       <c r="B23" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4290,47 +4290,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129226592</v>
+        <v>129230367</v>
       </c>
       <c r="B28" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4344,13 +4335,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490132</v>
+        <v>490063</v>
       </c>
       <c r="R28" t="n">
-        <v>7004833</v>
+        <v>7004901</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4379,7 +4370,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4389,12 +4380,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4409,6 +4400,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4426,47 +4437,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129225418</v>
+        <v>129230525</v>
       </c>
       <c r="B29" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4480,10 +4482,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490122</v>
+        <v>490071</v>
       </c>
       <c r="R29" t="n">
-        <v>7004771</v>
+        <v>7004894</v>
       </c>
       <c r="S29" t="n">
         <v>8</v>
@@ -4515,7 +4517,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4525,12 +4527,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4545,6 +4547,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4562,10 +4584,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129225602</v>
+        <v>129226592</v>
       </c>
       <c r="B30" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4592,7 +4614,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4602,7 +4624,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4616,13 +4638,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490142</v>
+        <v>490132</v>
       </c>
       <c r="R30" t="n">
-        <v>7004806</v>
+        <v>7004833</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4651,7 +4673,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4661,12 +4683,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4698,10 +4720,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129225165</v>
+        <v>129225418</v>
       </c>
       <c r="B31" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4728,7 +4750,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4752,13 +4774,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490124</v>
+        <v>490122</v>
       </c>
       <c r="R31" t="n">
-        <v>7004767</v>
+        <v>7004771</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4787,7 +4809,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4797,12 +4819,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
+          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4834,38 +4856,47 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129230367</v>
+        <v>129225602</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4879,13 +4910,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490063</v>
+        <v>490142</v>
       </c>
       <c r="R32" t="n">
-        <v>7004901</v>
+        <v>7004806</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4914,7 +4945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4924,12 +4955,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4944,26 +4975,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4981,38 +4992,47 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129230525</v>
+        <v>129225165</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5026,13 +5046,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490071</v>
+        <v>490124</v>
       </c>
       <c r="R33" t="n">
-        <v>7004894</v>
+        <v>7004767</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5061,7 +5081,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5071,12 +5091,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5091,26 +5111,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5131,7 +5131,7 @@
         <v>129224808</v>
       </c>
       <c r="B34" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5265,52 +5265,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129228038</v>
+        <v>129223375</v>
       </c>
       <c r="B35" t="n">
-        <v>98678</v>
+        <v>80175</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5319,13 +5305,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490161</v>
+        <v>490028</v>
       </c>
       <c r="R35" t="n">
-        <v>7004940</v>
+        <v>7004796</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5354,7 +5340,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5364,12 +5350,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5383,7 +5364,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5538,38 +5539,52 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129223375</v>
+        <v>129228038</v>
       </c>
       <c r="B37" t="n">
-        <v>80175</v>
+        <v>98704</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5578,13 +5593,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490028</v>
+        <v>490161</v>
       </c>
       <c r="R37" t="n">
-        <v>7004796</v>
+        <v>7004940</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5613,7 +5628,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5623,7 +5638,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5637,27 +5657,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5678,7 +5678,7 @@
         <v>129223986</v>
       </c>
       <c r="B38" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6085,10 +6085,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129223203</v>
+        <v>129227281</v>
       </c>
       <c r="B41" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6139,13 +6139,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489995</v>
+        <v>490162</v>
       </c>
       <c r="R41" t="n">
-        <v>7004788</v>
+        <v>7004880</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 16 plantor inom ca 2 m2 yta intill en tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6221,10 +6221,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129227281</v>
+        <v>129223203</v>
       </c>
       <c r="B42" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6275,13 +6275,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490162</v>
+        <v>489995</v>
       </c>
       <c r="R42" t="n">
-        <v>7004880</v>
+        <v>7004788</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Minst 16 plantor inom ca 2 m2 yta intill en tall.</t>
+          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6504,38 +6504,43 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129226789</v>
+        <v>129229897</v>
       </c>
       <c r="B44" t="n">
-        <v>92480</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6544,13 +6549,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490174</v>
+        <v>490072</v>
       </c>
       <c r="R44" t="n">
-        <v>7004879</v>
+        <v>7004920</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6579,7 +6584,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6589,7 +6594,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6603,7 +6613,27 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6624,7 +6654,7 @@
         <v>129224339</v>
       </c>
       <c r="B45" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6753,43 +6783,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129229897</v>
+        <v>129226789</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>92494</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6798,13 +6823,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490072</v>
+        <v>490174</v>
       </c>
       <c r="R46" t="n">
-        <v>7004920</v>
+        <v>7004879</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6833,7 +6858,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6843,12 +6868,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6862,27 +6882,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -7032,10 +7032,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129230332</v>
+        <v>129223439</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7043,27 +7043,36 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -7077,13 +7086,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490052</v>
+        <v>490044</v>
       </c>
       <c r="R48" t="n">
-        <v>7004901</v>
+        <v>7004789</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7112,7 +7121,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7122,12 +7131,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7142,26 +7151,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7179,7 +7168,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129230142</v>
+        <v>129230332</v>
       </c>
       <c r="B49" t="n">
         <v>57727</v>
@@ -7224,13 +7213,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490056</v>
+        <v>490052</v>
       </c>
       <c r="R49" t="n">
-        <v>7004912</v>
+        <v>7004901</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7259,7 +7248,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7269,7 +7258,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7326,10 +7315,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129223439</v>
+        <v>129230142</v>
       </c>
       <c r="B50" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7337,36 +7326,27 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7380,13 +7360,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490044</v>
+        <v>490056</v>
       </c>
       <c r="R50" t="n">
-        <v>7004789</v>
+        <v>7004912</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7415,7 +7395,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7425,12 +7405,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7445,6 +7425,26 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7465,7 +7465,7 @@
         <v>129223831</v>
       </c>
       <c r="B51" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7745,38 +7745,52 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129226046</v>
+        <v>129226468</v>
       </c>
       <c r="B53" t="n">
-        <v>80182</v>
+        <v>98704</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7785,10 +7799,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490078</v>
+        <v>490119</v>
       </c>
       <c r="R53" t="n">
-        <v>7004812</v>
+        <v>7004845</v>
       </c>
       <c r="S53" t="n">
         <v>11</v>
@@ -7820,7 +7834,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7830,12 +7844,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
+          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7850,26 +7864,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7890,7 +7884,7 @@
         <v>129231961</v>
       </c>
       <c r="B54" t="n">
-        <v>98595</v>
+        <v>98621</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8009,52 +8003,38 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129226468</v>
+        <v>129226046</v>
       </c>
       <c r="B55" t="n">
-        <v>98678</v>
+        <v>80182</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -8063,10 +8043,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490119</v>
+        <v>490078</v>
       </c>
       <c r="R55" t="n">
-        <v>7004845</v>
+        <v>7004812</v>
       </c>
       <c r="S55" t="n">
         <v>11</v>
@@ -8098,7 +8078,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8108,12 +8088,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
+          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8128,6 +8108,26 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8145,48 +8145,67 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129223232</v>
+        <v>129225550</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490017</v>
+        <v>490157</v>
       </c>
       <c r="R56" t="n">
-        <v>7004780</v>
+        <v>7004793</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8215,7 +8234,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8225,7 +8244,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8240,26 +8264,6 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8571,67 +8575,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129225550</v>
+        <v>129223232</v>
       </c>
       <c r="B59" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490157</v>
+        <v>490017</v>
       </c>
       <c r="R59" t="n">
-        <v>7004793</v>
+        <v>7004780</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8660,7 +8645,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8670,12 +8655,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8690,6 +8670,26 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129230577</v>
+        <v>129227061</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,44 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490070</v>
+        <v>490204</v>
       </c>
       <c r="R2" t="n">
-        <v>7004890</v>
+        <v>7004896</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:51</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,12 +784,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -822,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129227061</v>
+        <v>129230577</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,34 +818,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490204</v>
+        <v>490070</v>
       </c>
       <c r="R3" t="n">
-        <v>7004896</v>
+        <v>7004890</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +897,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,12 +931,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -954,38 +954,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129230003</v>
+        <v>129228951</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -999,13 +1008,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490061</v>
+        <v>490119</v>
       </c>
       <c r="R4" t="n">
-        <v>7004922</v>
+        <v>7004879</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,7 +1043,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1053,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
+          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,26 +1073,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1101,7 +1090,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129230622</v>
+        <v>129230003</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1132,7 +1121,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1146,13 +1135,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490077</v>
+        <v>490061</v>
       </c>
       <c r="R5" t="n">
-        <v>7004897</v>
+        <v>7004922</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1181,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1191,12 +1180,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1248,47 +1237,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129228951</v>
+        <v>129230622</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1302,13 +1282,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490119</v>
+        <v>490077</v>
       </c>
       <c r="R6" t="n">
-        <v>7004879</v>
+        <v>7004897</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1337,7 +1317,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1347,12 +1327,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1367,6 +1347,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1384,45 +1384,64 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129224447</v>
+        <v>129226982</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490020</v>
+        <v>490196</v>
       </c>
       <c r="R7" t="n">
-        <v>7004694</v>
+        <v>7004884</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1454,7 +1473,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1464,7 +1483,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1479,26 +1503,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1516,38 +1520,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129223103</v>
+        <v>129226861</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1561,13 +1574,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489959</v>
+        <v>490181</v>
       </c>
       <c r="R8" t="n">
-        <v>7004819</v>
+        <v>7004884</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1596,7 +1609,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1606,12 +1619,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1626,26 +1639,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1663,64 +1656,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129226982</v>
+        <v>129224447</v>
       </c>
       <c r="B9" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490196</v>
+        <v>490020</v>
       </c>
       <c r="R9" t="n">
-        <v>7004884</v>
+        <v>7004694</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1752,7 +1726,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1762,12 +1736,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1782,6 +1751,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1799,47 +1788,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129226861</v>
+        <v>129223103</v>
       </c>
       <c r="B10" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1853,13 +1833,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490181</v>
+        <v>489959</v>
       </c>
       <c r="R10" t="n">
-        <v>7004884</v>
+        <v>7004819</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1888,7 +1868,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1898,12 +1878,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1918,6 +1898,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2070,7 +2070,7 @@
         <v>129231914</v>
       </c>
       <c r="B12" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2203,43 +2203,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129231535</v>
+        <v>129224667</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2248,10 +2252,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489991</v>
+        <v>490027</v>
       </c>
       <c r="R13" t="n">
-        <v>7004843</v>
+        <v>7004700</v>
       </c>
       <c r="S13" t="n">
         <v>8</v>
@@ -2283,7 +2287,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2293,12 +2297,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 250 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2313,26 +2317,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2350,7 +2334,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129230279</v>
+        <v>129231535</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2395,13 +2379,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490064</v>
+        <v>489991</v>
       </c>
       <c r="R14" t="n">
-        <v>7004903</v>
+        <v>7004843</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2430,7 +2414,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2440,7 +2424,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2497,7 +2481,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129230462</v>
+        <v>129230279</v>
       </c>
       <c r="B15" t="n">
         <v>57727</v>
@@ -2542,13 +2526,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490066</v>
+        <v>490064</v>
       </c>
       <c r="R15" t="n">
-        <v>7004896</v>
+        <v>7004903</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2577,7 +2561,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2587,12 +2571,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2644,7 +2628,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129230594</v>
+        <v>129230462</v>
       </c>
       <c r="B16" t="n">
         <v>57727</v>
@@ -2689,13 +2673,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490071</v>
+        <v>490066</v>
       </c>
       <c r="R16" t="n">
-        <v>7004887</v>
+        <v>7004896</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2724,7 +2708,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2734,7 +2718,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2791,47 +2775,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129224667</v>
+        <v>129230594</v>
       </c>
       <c r="B17" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2840,13 +2820,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490027</v>
+        <v>490071</v>
       </c>
       <c r="R17" t="n">
-        <v>7004700</v>
+        <v>7004887</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2875,7 +2855,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2885,12 +2865,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 250 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2905,6 +2885,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3490,64 +3490,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129225751</v>
+        <v>129230877</v>
       </c>
       <c r="B22" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490094</v>
+        <v>490026</v>
       </c>
       <c r="R22" t="n">
-        <v>7004803</v>
+        <v>7004861</v>
       </c>
       <c r="S22" t="n">
         <v>11</v>
@@ -3579,7 +3560,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3589,12 +3570,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3609,6 +3585,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3626,10 +3622,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129230745</v>
+        <v>129225751</v>
       </c>
       <c r="B23" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3656,7 +3652,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3680,10 +3676,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490076</v>
+        <v>490094</v>
       </c>
       <c r="R23" t="n">
-        <v>7004871</v>
+        <v>7004803</v>
       </c>
       <c r="S23" t="n">
         <v>11</v>
@@ -3715,7 +3711,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3725,12 +3721,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3762,45 +3758,64 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129230877</v>
+        <v>129230745</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490026</v>
+        <v>490076</v>
       </c>
       <c r="R24" t="n">
-        <v>7004861</v>
+        <v>7004871</v>
       </c>
       <c r="S24" t="n">
         <v>11</v>
@@ -3832,7 +3847,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3842,7 +3857,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3857,26 +3877,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -4158,45 +4158,64 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129225967</v>
+        <v>129226592</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490095</v>
+        <v>490132</v>
       </c>
       <c r="R27" t="n">
-        <v>7004830</v>
+        <v>7004833</v>
       </c>
       <c r="S27" t="n">
         <v>11</v>
@@ -4228,7 +4247,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4238,7 +4257,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4253,26 +4277,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4290,38 +4294,47 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129230367</v>
+        <v>129225418</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4335,13 +4348,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490063</v>
+        <v>490122</v>
       </c>
       <c r="R28" t="n">
-        <v>7004901</v>
+        <v>7004771</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4370,7 +4383,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4380,12 +4393,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4400,26 +4413,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4437,38 +4430,47 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129230525</v>
+        <v>129225602</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4482,13 +4484,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490071</v>
+        <v>490142</v>
       </c>
       <c r="R29" t="n">
-        <v>7004894</v>
+        <v>7004806</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4517,7 +4519,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4527,12 +4529,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4547,26 +4549,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4584,10 +4566,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129226592</v>
+        <v>129225165</v>
       </c>
       <c r="B30" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4614,7 +4596,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4624,7 +4606,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4638,13 +4620,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490132</v>
+        <v>490124</v>
       </c>
       <c r="R30" t="n">
-        <v>7004833</v>
+        <v>7004767</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4673,7 +4655,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4683,12 +4665,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4720,67 +4702,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129225418</v>
+        <v>129225967</v>
       </c>
       <c r="B31" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490122</v>
+        <v>490095</v>
       </c>
       <c r="R31" t="n">
-        <v>7004771</v>
+        <v>7004830</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4809,7 +4772,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4819,12 +4782,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4839,6 +4797,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4856,47 +4834,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129225602</v>
+        <v>129230367</v>
       </c>
       <c r="B32" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4910,13 +4879,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490142</v>
+        <v>490063</v>
       </c>
       <c r="R32" t="n">
-        <v>7004806</v>
+        <v>7004901</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4945,7 +4914,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4955,12 +4924,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4975,6 +4944,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4992,47 +4981,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129225165</v>
+        <v>129230525</v>
       </c>
       <c r="B33" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5046,13 +5026,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490124</v>
+        <v>490071</v>
       </c>
       <c r="R33" t="n">
-        <v>7004767</v>
+        <v>7004894</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5081,7 +5061,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5091,12 +5071,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5111,6 +5091,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129224808</v>
+        <v>129223375</v>
       </c>
       <c r="B34" t="n">
-        <v>92257</v>
+        <v>80175</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5139,27 +5139,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5168,13 +5168,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490107</v>
+        <v>490028</v>
       </c>
       <c r="R34" t="n">
-        <v>7004741</v>
+        <v>7004796</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5232,22 +5232,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5265,38 +5265,52 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129223375</v>
+        <v>129228038</v>
       </c>
       <c r="B35" t="n">
-        <v>80175</v>
+        <v>98705</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5305,13 +5319,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490028</v>
+        <v>490161</v>
       </c>
       <c r="R35" t="n">
-        <v>7004796</v>
+        <v>7004940</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5340,7 +5354,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5350,7 +5364,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5364,27 +5383,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5402,45 +5401,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129227795</v>
+        <v>129224808</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>92258</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490175</v>
+        <v>490107</v>
       </c>
       <c r="R36" t="n">
-        <v>7004918</v>
+        <v>7004741</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -5472,7 +5476,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5482,12 +5486,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5516,12 +5515,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5539,67 +5538,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129228038</v>
+        <v>129227795</v>
       </c>
       <c r="B37" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490161</v>
+        <v>490175</v>
       </c>
       <c r="R37" t="n">
-        <v>7004940</v>
+        <v>7004918</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5628,7 +5608,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5638,12 +5618,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5657,7 +5637,27 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5675,52 +5675,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129223986</v>
+        <v>129231240</v>
       </c>
       <c r="B38" t="n">
-        <v>98704</v>
+        <v>80175</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5729,13 +5715,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490070</v>
+        <v>490033</v>
       </c>
       <c r="R38" t="n">
-        <v>7004763</v>
+        <v>7004823</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5764,7 +5750,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5774,12 +5760,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 22 plantor inom ca 1 m2 yta.</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5794,6 +5775,26 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5811,38 +5812,52 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129231240</v>
+        <v>129223986</v>
       </c>
       <c r="B39" t="n">
-        <v>80175</v>
+        <v>98705</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5851,13 +5866,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490033</v>
+        <v>490070</v>
       </c>
       <c r="R39" t="n">
-        <v>7004823</v>
+        <v>7004763</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5886,7 +5901,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5896,7 +5911,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Minst 22 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5911,26 +5931,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -6085,10 +6085,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129227281</v>
+        <v>129223203</v>
       </c>
       <c r="B41" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6139,13 +6139,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490162</v>
+        <v>489995</v>
       </c>
       <c r="R41" t="n">
-        <v>7004880</v>
+        <v>7004788</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Minst 16 plantor inom ca 2 m2 yta intill en tall.</t>
+          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6221,10 +6221,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129223203</v>
+        <v>129227281</v>
       </c>
       <c r="B42" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6275,13 +6275,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>489995</v>
+        <v>490162</v>
       </c>
       <c r="R42" t="n">
-        <v>7004788</v>
+        <v>7004880</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 16 plantor inom ca 2 m2 yta intill en tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6504,43 +6504,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129229897</v>
+        <v>129226789</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>92495</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6549,13 +6544,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490072</v>
+        <v>490174</v>
       </c>
       <c r="R44" t="n">
-        <v>7004920</v>
+        <v>7004879</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6584,7 +6579,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6594,12 +6589,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6613,27 +6603,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6654,7 +6624,7 @@
         <v>129224339</v>
       </c>
       <c r="B45" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6783,38 +6753,43 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129226789</v>
+        <v>129229897</v>
       </c>
       <c r="B46" t="n">
-        <v>92494</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6823,13 +6798,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490174</v>
+        <v>490072</v>
       </c>
       <c r="R46" t="n">
-        <v>7004879</v>
+        <v>7004920</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6858,7 +6833,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6868,7 +6843,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6882,7 +6862,27 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -7032,10 +7032,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129223439</v>
+        <v>129230332</v>
       </c>
       <c r="B48" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7043,36 +7043,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -7086,13 +7077,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490044</v>
+        <v>490052</v>
       </c>
       <c r="R48" t="n">
-        <v>7004789</v>
+        <v>7004901</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7121,7 +7112,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7131,12 +7122,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7151,6 +7142,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7168,7 +7179,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129230332</v>
+        <v>129230142</v>
       </c>
       <c r="B49" t="n">
         <v>57727</v>
@@ -7213,13 +7224,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490052</v>
+        <v>490056</v>
       </c>
       <c r="R49" t="n">
-        <v>7004901</v>
+        <v>7004912</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7248,7 +7259,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7258,7 +7269,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7315,10 +7326,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129230142</v>
+        <v>129223439</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7326,27 +7337,36 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7360,13 +7380,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490056</v>
+        <v>490044</v>
       </c>
       <c r="R50" t="n">
-        <v>7004912</v>
+        <v>7004789</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7395,7 +7415,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7405,12 +7425,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7425,26 +7445,6 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7462,47 +7462,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129223831</v>
+        <v>129230834</v>
       </c>
       <c r="B51" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7516,13 +7507,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490057</v>
+        <v>490020</v>
       </c>
       <c r="R51" t="n">
-        <v>7004780</v>
+        <v>7004888</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7551,7 +7542,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7561,12 +7552,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7581,6 +7572,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7598,38 +7609,47 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129230834</v>
+        <v>129223831</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7643,13 +7663,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490020</v>
+        <v>490057</v>
       </c>
       <c r="R52" t="n">
-        <v>7004888</v>
+        <v>7004780</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7678,7 +7698,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7688,12 +7708,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
+          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7708,26 +7728,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7745,52 +7745,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129226468</v>
+        <v>129226046</v>
       </c>
       <c r="B53" t="n">
-        <v>98704</v>
+        <v>80182</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7799,10 +7785,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490119</v>
+        <v>490078</v>
       </c>
       <c r="R53" t="n">
-        <v>7004845</v>
+        <v>7004812</v>
       </c>
       <c r="S53" t="n">
         <v>11</v>
@@ -7834,7 +7820,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7844,12 +7830,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
+          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7864,6 +7850,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7884,7 +7890,7 @@
         <v>129231961</v>
       </c>
       <c r="B54" t="n">
-        <v>98621</v>
+        <v>98622</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8003,38 +8009,52 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129226046</v>
+        <v>129226468</v>
       </c>
       <c r="B55" t="n">
-        <v>80182</v>
+        <v>98705</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -8043,10 +8063,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490078</v>
+        <v>490119</v>
       </c>
       <c r="R55" t="n">
-        <v>7004812</v>
+        <v>7004845</v>
       </c>
       <c r="S55" t="n">
         <v>11</v>
@@ -8078,7 +8098,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8088,12 +8108,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
+          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8108,26 +8128,6 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8145,47 +8145,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129225550</v>
+        <v>129222854</v>
       </c>
       <c r="B56" t="n">
-        <v>98704</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -8199,10 +8190,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490157</v>
+        <v>489942</v>
       </c>
       <c r="R56" t="n">
-        <v>7004793</v>
+        <v>7004813</v>
       </c>
       <c r="S56" t="n">
         <v>8</v>
@@ -8234,7 +8225,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8244,12 +8235,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8264,6 +8255,26 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8281,7 +8292,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129222854</v>
+        <v>129230183</v>
       </c>
       <c r="B57" t="n">
         <v>57727</v>
@@ -8326,13 +8337,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489942</v>
+        <v>490060</v>
       </c>
       <c r="R57" t="n">
-        <v>7004813</v>
+        <v>7004914</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8361,7 +8372,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8371,12 +8382,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8428,38 +8439,47 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129230183</v>
+        <v>129225550</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8473,13 +8493,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490060</v>
+        <v>490157</v>
       </c>
       <c r="R58" t="n">
-        <v>7004914</v>
+        <v>7004793</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8508,7 +8528,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8518,12 +8538,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8538,26 +8558,6 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129227061</v>
+        <v>129230577</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490204</v>
+        <v>490070</v>
       </c>
       <c r="R2" t="n">
-        <v>7004896</v>
+        <v>7004890</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,12 +799,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +822,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129230577</v>
+        <v>129227061</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,44 +833,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490070</v>
+        <v>490204</v>
       </c>
       <c r="R3" t="n">
-        <v>7004890</v>
+        <v>7004896</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,12 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:51</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,12 +931,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -954,47 +954,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129228951</v>
+        <v>129230003</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1008,13 +999,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490119</v>
+        <v>490061</v>
       </c>
       <c r="R4" t="n">
-        <v>7004879</v>
+        <v>7004922</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1043,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1053,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,6 +1064,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1090,7 +1101,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129230003</v>
+        <v>129230622</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1121,7 +1132,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1135,13 +1146,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490061</v>
+        <v>490077</v>
       </c>
       <c r="R5" t="n">
-        <v>7004922</v>
+        <v>7004897</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1170,7 +1181,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1180,12 +1191,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
+          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1237,38 +1248,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129230622</v>
+        <v>129228951</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1282,13 +1302,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490077</v>
+        <v>490119</v>
       </c>
       <c r="R6" t="n">
-        <v>7004897</v>
+        <v>7004879</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1317,7 +1337,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1327,12 +1347,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
+          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1347,26 +1367,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1384,64 +1384,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129226982</v>
+        <v>129224447</v>
       </c>
       <c r="B7" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490196</v>
+        <v>490020</v>
       </c>
       <c r="R7" t="n">
-        <v>7004884</v>
+        <v>7004694</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1473,7 +1454,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1483,12 +1464,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1503,6 +1479,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1520,47 +1516,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129226861</v>
+        <v>129223103</v>
       </c>
       <c r="B8" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1574,13 +1561,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490181</v>
+        <v>489959</v>
       </c>
       <c r="R8" t="n">
-        <v>7004884</v>
+        <v>7004819</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1609,7 +1596,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1619,12 +1606,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1639,6 +1626,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1656,45 +1663,64 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129224447</v>
+        <v>129226982</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490020</v>
+        <v>490196</v>
       </c>
       <c r="R9" t="n">
-        <v>7004694</v>
+        <v>7004884</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1726,7 +1752,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1736,7 +1762,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1751,26 +1782,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1788,38 +1799,47 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129223103</v>
+        <v>129226861</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1833,13 +1853,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489959</v>
+        <v>490181</v>
       </c>
       <c r="R10" t="n">
-        <v>7004819</v>
+        <v>7004884</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1868,7 +1888,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1878,12 +1898,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1898,26 +1918,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2070,7 +2070,7 @@
         <v>129231914</v>
       </c>
       <c r="B12" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>129224667</v>
       </c>
       <c r="B13" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3064,38 +3064,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129230997</v>
+        <v>129229350</v>
       </c>
       <c r="B19" t="n">
-        <v>80175</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3104,13 +3109,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490022</v>
+        <v>490080</v>
       </c>
       <c r="R19" t="n">
-        <v>7004859</v>
+        <v>7004934</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3139,7 +3144,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3149,7 +3154,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, färska (2025), i riklig mängd längs flera meter på en gran vid en hyggeskant. Granen är gräns-snitslad för en planerad avverning.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3168,22 +3178,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3201,43 +3211,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129229350</v>
+        <v>129230997</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>80175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3246,13 +3251,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490080</v>
+        <v>490022</v>
       </c>
       <c r="R20" t="n">
-        <v>7004934</v>
+        <v>7004859</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3281,7 +3286,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3291,12 +3296,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, färska (2025), i riklig mängd längs flera meter på en gran vid en hyggeskant. Granen är gräns-snitslad för en planerad avverning.</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3315,22 +3315,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3625,7 +3625,7 @@
         <v>129225751</v>
       </c>
       <c r="B23" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>129230745</v>
       </c>
       <c r="B24" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3894,48 +3894,67 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129229156</v>
+        <v>129226592</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490069</v>
+        <v>490132</v>
       </c>
       <c r="R25" t="n">
-        <v>7004928</v>
+        <v>7004833</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3964,7 +3983,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3974,7 +3993,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3989,26 +4013,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4026,48 +4030,67 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129227087</v>
+        <v>129225418</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490187</v>
+        <v>490122</v>
       </c>
       <c r="R26" t="n">
-        <v>7004903</v>
+        <v>7004771</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4096,7 +4119,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4106,7 +4129,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4121,26 +4149,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4158,10 +4166,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129226592</v>
+        <v>129225602</v>
       </c>
       <c r="B27" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4188,7 +4196,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4198,7 +4206,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4212,13 +4220,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490132</v>
+        <v>490142</v>
       </c>
       <c r="R27" t="n">
-        <v>7004833</v>
+        <v>7004806</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4247,7 +4255,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4257,12 +4265,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4294,10 +4302,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129225418</v>
+        <v>129225165</v>
       </c>
       <c r="B28" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4324,7 +4332,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4348,13 +4356,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490122</v>
+        <v>490124</v>
       </c>
       <c r="R28" t="n">
-        <v>7004771</v>
+        <v>7004767</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4383,7 +4391,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4393,12 +4401,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
+          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4430,67 +4438,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129225602</v>
+        <v>129229156</v>
       </c>
       <c r="B29" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490142</v>
+        <v>490069</v>
       </c>
       <c r="R29" t="n">
-        <v>7004806</v>
+        <v>7004928</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4519,7 +4508,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4529,12 +4518,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4549,6 +4533,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4566,64 +4570,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129225165</v>
+        <v>129227087</v>
       </c>
       <c r="B30" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490124</v>
+        <v>490187</v>
       </c>
       <c r="R30" t="n">
-        <v>7004767</v>
+        <v>7004903</v>
       </c>
       <c r="S30" t="n">
         <v>9</v>
@@ -4655,7 +4640,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4665,12 +4650,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4685,6 +4665,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129223375</v>
+        <v>129224808</v>
       </c>
       <c r="B34" t="n">
-        <v>80175</v>
+        <v>92258</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5139,27 +5139,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5168,13 +5168,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490028</v>
+        <v>490107</v>
       </c>
       <c r="R34" t="n">
-        <v>7004796</v>
+        <v>7004741</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5232,22 +5232,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5265,52 +5265,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129228038</v>
+        <v>129223375</v>
       </c>
       <c r="B35" t="n">
-        <v>98705</v>
+        <v>80175</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5319,13 +5305,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490161</v>
+        <v>490028</v>
       </c>
       <c r="R35" t="n">
-        <v>7004940</v>
+        <v>7004796</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5354,7 +5340,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5364,12 +5350,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5383,7 +5364,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5401,50 +5402,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129224808</v>
+        <v>129227795</v>
       </c>
       <c r="B36" t="n">
-        <v>92258</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490107</v>
+        <v>490175</v>
       </c>
       <c r="R36" t="n">
-        <v>7004741</v>
+        <v>7004918</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -5476,7 +5472,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5486,7 +5482,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5515,12 +5516,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5538,48 +5539,67 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129227795</v>
+        <v>129228038</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490175</v>
+        <v>490161</v>
       </c>
       <c r="R37" t="n">
-        <v>7004918</v>
+        <v>7004940</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5608,7 +5628,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5618,12 +5638,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5637,27 +5657,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5815,7 +5815,7 @@
         <v>129223986</v>
       </c>
       <c r="B39" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5948,38 +5948,52 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129230966</v>
+        <v>129223203</v>
       </c>
       <c r="B40" t="n">
-        <v>80146</v>
+        <v>98706</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5988,10 +6002,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490020</v>
+        <v>489995</v>
       </c>
       <c r="R40" t="n">
-        <v>7004857</v>
+        <v>7004788</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -6023,7 +6037,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6033,7 +6047,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6048,26 +6067,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6085,10 +6084,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129223203</v>
+        <v>129227281</v>
       </c>
       <c r="B41" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6115,7 +6114,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6139,13 +6138,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489995</v>
+        <v>490162</v>
       </c>
       <c r="R41" t="n">
-        <v>7004788</v>
+        <v>7004880</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6174,7 +6173,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6184,12 +6183,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 16 plantor inom ca 2 m2 yta intill en tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6221,52 +6220,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129227281</v>
+        <v>129230966</v>
       </c>
       <c r="B42" t="n">
-        <v>98705</v>
+        <v>80146</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -6275,13 +6260,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490162</v>
+        <v>490020</v>
       </c>
       <c r="R42" t="n">
-        <v>7004880</v>
+        <v>7004857</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6310,7 +6295,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6320,12 +6305,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Minst 16 plantor inom ca 2 m2 yta intill en tall.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6340,6 +6320,26 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6621,43 +6621,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129224339</v>
+        <v>129229897</v>
       </c>
       <c r="B45" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6671,13 +6666,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490008</v>
+        <v>490072</v>
       </c>
       <c r="R45" t="n">
-        <v>7004696</v>
+        <v>7004920</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6706,7 +6701,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6716,12 +6711,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6736,6 +6731,26 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6753,38 +6768,43 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129229897</v>
+        <v>129224339</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6798,13 +6818,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490072</v>
+        <v>490008</v>
       </c>
       <c r="R46" t="n">
-        <v>7004920</v>
+        <v>7004696</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6833,7 +6853,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6843,12 +6863,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6863,26 +6883,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -7462,38 +7462,47 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129230834</v>
+        <v>129223831</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7507,13 +7516,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490020</v>
+        <v>490057</v>
       </c>
       <c r="R51" t="n">
-        <v>7004888</v>
+        <v>7004780</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7542,7 +7551,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7552,12 +7561,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
+          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7572,26 +7581,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7609,47 +7598,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129223831</v>
+        <v>129230834</v>
       </c>
       <c r="B52" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7663,13 +7643,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490057</v>
+        <v>490020</v>
       </c>
       <c r="R52" t="n">
-        <v>7004780</v>
+        <v>7004888</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7698,7 +7678,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7708,12 +7688,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7728,6 +7708,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7890,7 +7890,7 @@
         <v>129231961</v>
       </c>
       <c r="B54" t="n">
-        <v>98622</v>
+        <v>98623</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>129226468</v>
       </c>
       <c r="B55" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -8145,10 +8145,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129222854</v>
+        <v>129223232</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8156,47 +8156,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489942</v>
+        <v>490017</v>
       </c>
       <c r="R56" t="n">
-        <v>7004813</v>
+        <v>7004780</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8225,7 +8215,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8235,12 +8225,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8269,12 +8254,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8292,7 +8277,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129230183</v>
+        <v>129222854</v>
       </c>
       <c r="B57" t="n">
         <v>57727</v>
@@ -8337,13 +8322,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490060</v>
+        <v>489942</v>
       </c>
       <c r="R57" t="n">
-        <v>7004914</v>
+        <v>7004813</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8372,7 +8357,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8382,12 +8367,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8439,47 +8424,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129225550</v>
+        <v>129230183</v>
       </c>
       <c r="B58" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8493,13 +8469,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490157</v>
+        <v>490060</v>
       </c>
       <c r="R58" t="n">
-        <v>7004793</v>
+        <v>7004914</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8528,7 +8504,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8538,12 +8514,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8558,6 +8534,26 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8575,48 +8571,67 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129223232</v>
+        <v>129225550</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490017</v>
+        <v>490157</v>
       </c>
       <c r="R59" t="n">
-        <v>7004780</v>
+        <v>7004793</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8645,7 +8660,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8655,7 +8670,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8670,26 +8690,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129230577</v>
+        <v>129227061</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,44 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490070</v>
+        <v>490204</v>
       </c>
       <c r="R2" t="n">
-        <v>7004890</v>
+        <v>7004896</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:51</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,12 +784,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -822,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129227061</v>
+        <v>129230577</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,34 +818,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490204</v>
+        <v>490070</v>
       </c>
       <c r="R3" t="n">
-        <v>7004896</v>
+        <v>7004890</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +897,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,12 +931,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1251,7 +1251,7 @@
         <v>129228951</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>129224447</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1516,38 +1516,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129223103</v>
+        <v>129226982</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1561,13 +1570,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489959</v>
+        <v>490196</v>
       </c>
       <c r="R8" t="n">
-        <v>7004819</v>
+        <v>7004884</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1596,7 +1605,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1606,12 +1615,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1626,26 +1635,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1663,10 +1652,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129226982</v>
+        <v>129226861</v>
       </c>
       <c r="B9" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1693,7 +1682,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1717,7 +1706,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490196</v>
+        <v>490181</v>
       </c>
       <c r="R9" t="n">
         <v>7004884</v>
@@ -1752,7 +1741,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1762,12 +1751,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1799,47 +1788,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129226861</v>
+        <v>129223103</v>
       </c>
       <c r="B10" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1853,13 +1833,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490181</v>
+        <v>489959</v>
       </c>
       <c r="R10" t="n">
-        <v>7004884</v>
+        <v>7004819</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1888,7 +1868,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1898,12 +1878,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1918,6 +1898,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1935,48 +1935,67 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129231117</v>
+        <v>129231914</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490037</v>
+        <v>489938</v>
       </c>
       <c r="R11" t="n">
-        <v>7004829</v>
+        <v>7004758</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2005,7 +2024,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2015,7 +2034,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2030,26 +2054,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2067,67 +2071,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129231914</v>
+        <v>129231117</v>
       </c>
       <c r="B12" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489938</v>
+        <v>490037</v>
       </c>
       <c r="R12" t="n">
-        <v>7004758</v>
+        <v>7004829</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2156,7 +2141,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2166,12 +2151,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2186,6 +2166,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2203,47 +2203,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129224667</v>
+        <v>129231535</v>
       </c>
       <c r="B13" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2252,10 +2248,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490027</v>
+        <v>489991</v>
       </c>
       <c r="R13" t="n">
-        <v>7004700</v>
+        <v>7004843</v>
       </c>
       <c r="S13" t="n">
         <v>8</v>
@@ -2287,7 +2283,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2297,12 +2293,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 250 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2317,6 +2313,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2334,7 +2350,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129231535</v>
+        <v>129230279</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2379,13 +2395,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489991</v>
+        <v>490064</v>
       </c>
       <c r="R14" t="n">
-        <v>7004843</v>
+        <v>7004903</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2414,7 +2430,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2424,7 +2440,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2481,7 +2497,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129230279</v>
+        <v>129230462</v>
       </c>
       <c r="B15" t="n">
         <v>57727</v>
@@ -2526,13 +2542,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490064</v>
+        <v>490066</v>
       </c>
       <c r="R15" t="n">
-        <v>7004903</v>
+        <v>7004896</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2561,7 +2577,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2571,12 +2587,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2628,7 +2644,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129230462</v>
+        <v>129230594</v>
       </c>
       <c r="B16" t="n">
         <v>57727</v>
@@ -2673,13 +2689,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490066</v>
+        <v>490071</v>
       </c>
       <c r="R16" t="n">
-        <v>7004896</v>
+        <v>7004887</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2708,7 +2724,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2718,7 +2734,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2775,43 +2791,47 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129230594</v>
+        <v>129224667</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2820,13 +2840,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490071</v>
+        <v>490027</v>
       </c>
       <c r="R17" t="n">
-        <v>7004887</v>
+        <v>7004700</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2855,7 +2875,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2865,12 +2885,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Minst 250 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2885,26 +2905,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2925,7 +2925,7 @@
         <v>129225817</v>
       </c>
       <c r="B18" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>129230997</v>
       </c>
       <c r="B20" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>129225796</v>
       </c>
       <c r="B21" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>129230877</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>129225751</v>
       </c>
       <c r="B23" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>129230745</v>
       </c>
       <c r="B24" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>129226592</v>
       </c>
       <c r="B25" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>129225418</v>
       </c>
       <c r="B26" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>129225602</v>
       </c>
       <c r="B27" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>129225165</v>
       </c>
       <c r="B28" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>129229156</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>129227087</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>129225967</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5128,10 +5128,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129224808</v>
+        <v>129223375</v>
       </c>
       <c r="B34" t="n">
-        <v>92258</v>
+        <v>80177</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5139,27 +5139,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5168,13 +5168,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490107</v>
+        <v>490028</v>
       </c>
       <c r="R34" t="n">
-        <v>7004741</v>
+        <v>7004796</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5232,22 +5232,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5265,10 +5265,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129223375</v>
+        <v>129224808</v>
       </c>
       <c r="B35" t="n">
-        <v>80175</v>
+        <v>92261</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5276,27 +5276,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5305,13 +5305,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490028</v>
+        <v>490107</v>
       </c>
       <c r="R35" t="n">
-        <v>7004796</v>
+        <v>7004741</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5369,22 +5369,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5405,7 +5405,7 @@
         <v>129227795</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>129228038</v>
       </c>
       <c r="B37" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>129231240</v>
       </c>
       <c r="B38" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>129223986</v>
       </c>
       <c r="B39" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5948,52 +5948,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129223203</v>
+        <v>129230966</v>
       </c>
       <c r="B40" t="n">
-        <v>98706</v>
+        <v>80148</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -6002,10 +5988,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489995</v>
+        <v>490020</v>
       </c>
       <c r="R40" t="n">
-        <v>7004788</v>
+        <v>7004857</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -6037,7 +6023,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6047,12 +6033,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6067,6 +6048,26 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6084,10 +6085,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129227281</v>
+        <v>129223203</v>
       </c>
       <c r="B41" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6114,7 +6115,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6138,13 +6139,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490162</v>
+        <v>489995</v>
       </c>
       <c r="R41" t="n">
-        <v>7004880</v>
+        <v>7004788</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6173,7 +6174,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6183,12 +6184,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Minst 16 plantor inom ca 2 m2 yta intill en tall.</t>
+          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6220,38 +6221,52 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129230966</v>
+        <v>129227281</v>
       </c>
       <c r="B42" t="n">
-        <v>80146</v>
+        <v>98710</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -6260,13 +6275,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490020</v>
+        <v>490162</v>
       </c>
       <c r="R42" t="n">
-        <v>7004857</v>
+        <v>7004880</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6295,7 +6310,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6305,7 +6320,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Minst 16 plantor inom ca 2 m2 yta intill en tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6320,26 +6340,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6507,7 +6507,7 @@
         <v>129226789</v>
       </c>
       <c r="B44" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>129224339</v>
       </c>
       <c r="B46" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>129229015</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>129223831</v>
       </c>
       <c r="B51" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7745,10 +7745,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129226046</v>
+        <v>129231961</v>
       </c>
       <c r="B53" t="n">
-        <v>80182</v>
+        <v>98627</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7756,27 +7756,32 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7785,13 +7790,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490078</v>
+        <v>489928</v>
       </c>
       <c r="R53" t="n">
-        <v>7004812</v>
+        <v>7004745</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7820,7 +7825,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7830,12 +7835,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7850,26 +7850,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7887,38 +7867,47 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129231961</v>
+        <v>129226468</v>
       </c>
       <c r="B54" t="n">
-        <v>98623</v>
+        <v>98710</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7932,13 +7921,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489928</v>
+        <v>490119</v>
       </c>
       <c r="R54" t="n">
-        <v>7004745</v>
+        <v>7004845</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7967,7 +7956,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7977,7 +7966,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8009,52 +8003,38 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129226468</v>
+        <v>129226046</v>
       </c>
       <c r="B55" t="n">
-        <v>98706</v>
+        <v>80184</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -8063,10 +8043,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490119</v>
+        <v>490078</v>
       </c>
       <c r="R55" t="n">
-        <v>7004845</v>
+        <v>7004812</v>
       </c>
       <c r="S55" t="n">
         <v>11</v>
@@ -8098,7 +8078,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8108,12 +8088,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
+          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8128,6 +8108,26 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8148,7 +8148,7 @@
         <v>129223232</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>129225550</v>
       </c>
       <c r="B59" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -1935,67 +1935,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129231914</v>
+        <v>129231117</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489938</v>
+        <v>490037</v>
       </c>
       <c r="R11" t="n">
-        <v>7004758</v>
+        <v>7004829</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2024,7 +2005,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2034,12 +2015,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2054,6 +2030,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2071,48 +2067,67 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129231117</v>
+        <v>129231914</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490037</v>
+        <v>489938</v>
       </c>
       <c r="R12" t="n">
-        <v>7004829</v>
+        <v>7004758</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2141,7 +2156,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2151,7 +2166,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2166,26 +2186,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -3064,43 +3064,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129229350</v>
+        <v>129230997</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>80177</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3109,13 +3104,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490080</v>
+        <v>490022</v>
       </c>
       <c r="R19" t="n">
-        <v>7004934</v>
+        <v>7004859</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3144,7 +3139,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3154,12 +3149,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, färska (2025), i riklig mängd längs flera meter på en gran vid en hyggeskant. Granen är gräns-snitslad för en planerad avverning.</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3178,22 +3168,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3211,38 +3201,43 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129230997</v>
+        <v>129229350</v>
       </c>
       <c r="B20" t="n">
-        <v>80177</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3251,13 +3246,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490022</v>
+        <v>490080</v>
       </c>
       <c r="R20" t="n">
-        <v>7004859</v>
+        <v>7004934</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3286,7 +3281,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3296,7 +3291,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, färska (2025), i riklig mängd längs flera meter på en gran vid en hyggeskant. Granen är gräns-snitslad för en planerad avverning.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3315,22 +3315,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -5948,38 +5948,52 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129230966</v>
+        <v>129223203</v>
       </c>
       <c r="B40" t="n">
-        <v>80148</v>
+        <v>98710</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5988,10 +6002,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490020</v>
+        <v>489995</v>
       </c>
       <c r="R40" t="n">
-        <v>7004857</v>
+        <v>7004788</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -6023,7 +6037,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6033,7 +6047,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6048,26 +6067,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6085,7 +6084,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129223203</v>
+        <v>129227281</v>
       </c>
       <c r="B41" t="n">
         <v>98710</v>
@@ -6115,7 +6114,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6139,13 +6138,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489995</v>
+        <v>490162</v>
       </c>
       <c r="R41" t="n">
-        <v>7004788</v>
+        <v>7004880</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6174,7 +6173,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6184,12 +6183,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 16 plantor inom ca 2 m2 yta intill en tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6221,52 +6220,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129227281</v>
+        <v>129230966</v>
       </c>
       <c r="B42" t="n">
-        <v>98710</v>
+        <v>80148</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -6275,13 +6260,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490162</v>
+        <v>490020</v>
       </c>
       <c r="R42" t="n">
-        <v>7004880</v>
+        <v>7004857</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6310,7 +6295,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6320,12 +6305,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Minst 16 plantor inom ca 2 m2 yta intill en tall.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6340,6 +6320,26 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -7745,10 +7745,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129231961</v>
+        <v>129226046</v>
       </c>
       <c r="B53" t="n">
-        <v>98627</v>
+        <v>80184</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7756,32 +7756,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7790,13 +7785,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489928</v>
+        <v>490078</v>
       </c>
       <c r="R53" t="n">
-        <v>7004745</v>
+        <v>7004812</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7825,7 +7820,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7835,7 +7830,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7850,6 +7850,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7867,47 +7887,38 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129226468</v>
+        <v>129231961</v>
       </c>
       <c r="B54" t="n">
-        <v>98710</v>
+        <v>98627</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7921,13 +7932,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490119</v>
+        <v>489928</v>
       </c>
       <c r="R54" t="n">
-        <v>7004845</v>
+        <v>7004745</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7956,7 +7967,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7966,12 +7977,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8003,38 +8009,52 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129226046</v>
+        <v>129226468</v>
       </c>
       <c r="B55" t="n">
-        <v>80184</v>
+        <v>98710</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -8043,10 +8063,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490078</v>
+        <v>490119</v>
       </c>
       <c r="R55" t="n">
-        <v>7004812</v>
+        <v>7004845</v>
       </c>
       <c r="S55" t="n">
         <v>11</v>
@@ -8078,7 +8098,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8088,12 +8108,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
+          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8108,26 +8128,6 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129227061</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>129228951</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>129224447</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1516,47 +1516,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129226982</v>
+        <v>129223103</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1570,13 +1561,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490196</v>
+        <v>489959</v>
       </c>
       <c r="R8" t="n">
-        <v>7004884</v>
+        <v>7004819</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1605,7 +1596,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1615,12 +1606,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1635,6 +1626,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1652,10 +1663,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129226861</v>
+        <v>129226982</v>
       </c>
       <c r="B9" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1682,7 +1693,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1706,7 +1717,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490181</v>
+        <v>490196</v>
       </c>
       <c r="R9" t="n">
         <v>7004884</v>
@@ -1741,7 +1752,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1751,12 +1762,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1788,38 +1799,47 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129223103</v>
+        <v>129226861</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1833,13 +1853,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489959</v>
+        <v>490181</v>
       </c>
       <c r="R10" t="n">
-        <v>7004819</v>
+        <v>7004884</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1868,7 +1888,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1878,12 +1898,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1898,26 +1918,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1935,48 +1935,67 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129231117</v>
+        <v>129231914</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490037</v>
+        <v>489938</v>
       </c>
       <c r="R11" t="n">
-        <v>7004829</v>
+        <v>7004758</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2005,7 +2024,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2015,7 +2034,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2030,26 +2054,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2067,67 +2071,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129231914</v>
+        <v>129231117</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489938</v>
+        <v>490037</v>
       </c>
       <c r="R12" t="n">
-        <v>7004758</v>
+        <v>7004829</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2156,7 +2141,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2166,12 +2151,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2186,6 +2166,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2794,7 +2794,7 @@
         <v>129224667</v>
       </c>
       <c r="B17" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>129225817</v>
       </c>
       <c r="B18" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3064,38 +3064,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129230997</v>
+        <v>129229350</v>
       </c>
       <c r="B19" t="n">
-        <v>80177</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3104,13 +3109,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490022</v>
+        <v>490080</v>
       </c>
       <c r="R19" t="n">
-        <v>7004859</v>
+        <v>7004934</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3139,7 +3144,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3149,7 +3154,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, färska (2025), i riklig mängd längs flera meter på en gran vid en hyggeskant. Granen är gräns-snitslad för en planerad avverning.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3168,22 +3178,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3201,43 +3211,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129229350</v>
+        <v>129230997</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3246,13 +3251,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490080</v>
+        <v>490022</v>
       </c>
       <c r="R20" t="n">
-        <v>7004934</v>
+        <v>7004859</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3281,7 +3286,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3291,12 +3296,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, färska (2025), i riklig mängd längs flera meter på en gran vid en hyggeskant. Granen är gräns-snitslad för en planerad avverning.</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3315,22 +3315,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3351,7 +3351,7 @@
         <v>129225796</v>
       </c>
       <c r="B21" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>129230877</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>129225751</v>
       </c>
       <c r="B23" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>129230745</v>
       </c>
       <c r="B24" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3894,67 +3894,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129226592</v>
+        <v>129229156</v>
       </c>
       <c r="B25" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490132</v>
+        <v>490069</v>
       </c>
       <c r="R25" t="n">
-        <v>7004833</v>
+        <v>7004928</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3983,7 +3964,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3993,12 +3974,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4013,6 +3989,26 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4030,67 +4026,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129225418</v>
+        <v>129227087</v>
       </c>
       <c r="B26" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490122</v>
+        <v>490187</v>
       </c>
       <c r="R26" t="n">
-        <v>7004771</v>
+        <v>7004903</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4119,7 +4096,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4129,12 +4106,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4149,6 +4121,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4166,67 +4158,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129225602</v>
+        <v>129225967</v>
       </c>
       <c r="B27" t="n">
-        <v>98710</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490142</v>
+        <v>490095</v>
       </c>
       <c r="R27" t="n">
-        <v>7004806</v>
+        <v>7004830</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4255,7 +4228,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4265,12 +4238,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4285,6 +4253,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4302,47 +4290,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129225165</v>
+        <v>129230367</v>
       </c>
       <c r="B28" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4356,10 +4335,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490124</v>
+        <v>490063</v>
       </c>
       <c r="R28" t="n">
-        <v>7004767</v>
+        <v>7004901</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -4391,7 +4370,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4401,12 +4380,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4421,6 +4400,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4438,10 +4437,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129229156</v>
+        <v>129230525</v>
       </c>
       <c r="B29" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4449,37 +4448,47 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490069</v>
+        <v>490071</v>
       </c>
       <c r="R29" t="n">
-        <v>7004928</v>
+        <v>7004894</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4508,7 +4517,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4518,7 +4527,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4547,12 +4561,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4570,48 +4584,67 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129227087</v>
+        <v>129226592</v>
       </c>
       <c r="B30" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490187</v>
+        <v>490132</v>
       </c>
       <c r="R30" t="n">
-        <v>7004903</v>
+        <v>7004833</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4640,7 +4673,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4650,7 +4683,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4665,26 +4703,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4702,48 +4720,67 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129225967</v>
+        <v>129225418</v>
       </c>
       <c r="B31" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490095</v>
+        <v>490122</v>
       </c>
       <c r="R31" t="n">
-        <v>7004830</v>
+        <v>7004771</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4772,7 +4809,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4782,7 +4819,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4797,26 +4839,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4834,38 +4856,47 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129230367</v>
+        <v>129225602</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4879,13 +4910,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490063</v>
+        <v>490142</v>
       </c>
       <c r="R32" t="n">
-        <v>7004901</v>
+        <v>7004806</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4914,7 +4945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4924,12 +4955,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4944,26 +4975,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4981,38 +4992,47 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129230525</v>
+        <v>129225165</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5026,13 +5046,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490071</v>
+        <v>490124</v>
       </c>
       <c r="R33" t="n">
-        <v>7004894</v>
+        <v>7004767</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5061,7 +5081,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5071,12 +5091,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5091,26 +5111,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5128,53 +5128,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129223375</v>
+        <v>129227795</v>
       </c>
       <c r="B34" t="n">
-        <v>80177</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490028</v>
+        <v>490175</v>
       </c>
       <c r="R34" t="n">
-        <v>7004796</v>
+        <v>7004918</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5203,7 +5198,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5213,7 +5208,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5232,22 +5232,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5265,10 +5265,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129224808</v>
+        <v>129223375</v>
       </c>
       <c r="B35" t="n">
-        <v>92261</v>
+        <v>80178</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5276,27 +5276,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5305,13 +5305,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490107</v>
+        <v>490028</v>
       </c>
       <c r="R35" t="n">
-        <v>7004741</v>
+        <v>7004796</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5369,22 +5369,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5402,45 +5402,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129227795</v>
+        <v>129224808</v>
       </c>
       <c r="B36" t="n">
-        <v>79043</v>
+        <v>92263</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490175</v>
+        <v>490107</v>
       </c>
       <c r="R36" t="n">
-        <v>7004918</v>
+        <v>7004741</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -5472,7 +5477,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5482,12 +5487,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5516,12 +5516,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5542,7 +5542,7 @@
         <v>129228038</v>
       </c>
       <c r="B37" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>129231240</v>
       </c>
       <c r="B38" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>129223986</v>
       </c>
       <c r="B39" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5948,52 +5948,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129223203</v>
+        <v>129230966</v>
       </c>
       <c r="B40" t="n">
-        <v>98710</v>
+        <v>80149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -6002,10 +5988,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489995</v>
+        <v>490020</v>
       </c>
       <c r="R40" t="n">
-        <v>7004788</v>
+        <v>7004857</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -6037,7 +6023,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6047,12 +6033,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6067,6 +6048,26 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6084,10 +6085,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129227281</v>
+        <v>129223203</v>
       </c>
       <c r="B41" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6114,7 +6115,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6138,13 +6139,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490162</v>
+        <v>489995</v>
       </c>
       <c r="R41" t="n">
-        <v>7004880</v>
+        <v>7004788</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6173,7 +6174,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6183,12 +6184,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Minst 16 plantor inom ca 2 m2 yta intill en tall.</t>
+          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6220,38 +6221,52 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129230966</v>
+        <v>129227281</v>
       </c>
       <c r="B42" t="n">
-        <v>80148</v>
+        <v>98712</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -6260,13 +6275,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490020</v>
+        <v>490162</v>
       </c>
       <c r="R42" t="n">
-        <v>7004857</v>
+        <v>7004880</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6295,7 +6310,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6305,7 +6320,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Minst 16 plantor inom ca 2 m2 yta intill en tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6320,26 +6340,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6507,7 +6507,7 @@
         <v>129226789</v>
       </c>
       <c r="B44" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>129224339</v>
       </c>
       <c r="B46" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>129229015</v>
       </c>
       <c r="B47" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7032,10 +7032,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129230332</v>
+        <v>129223439</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7043,27 +7043,36 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -7077,13 +7086,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490052</v>
+        <v>490044</v>
       </c>
       <c r="R48" t="n">
-        <v>7004901</v>
+        <v>7004789</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7112,7 +7121,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7122,12 +7131,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7142,26 +7151,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7179,7 +7168,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129230142</v>
+        <v>129230332</v>
       </c>
       <c r="B49" t="n">
         <v>57727</v>
@@ -7224,13 +7213,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490056</v>
+        <v>490052</v>
       </c>
       <c r="R49" t="n">
-        <v>7004912</v>
+        <v>7004901</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7259,7 +7248,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7269,7 +7258,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7326,10 +7315,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129223439</v>
+        <v>129230142</v>
       </c>
       <c r="B50" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7337,36 +7326,27 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7380,13 +7360,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490044</v>
+        <v>490056</v>
       </c>
       <c r="R50" t="n">
-        <v>7004789</v>
+        <v>7004912</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7415,7 +7395,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7425,12 +7405,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7445,6 +7425,26 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7465,7 +7465,7 @@
         <v>129223831</v>
       </c>
       <c r="B51" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>129226046</v>
       </c>
       <c r="B53" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7887,38 +7887,47 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129231961</v>
+        <v>129226468</v>
       </c>
       <c r="B54" t="n">
-        <v>98627</v>
+        <v>98712</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7932,13 +7941,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489928</v>
+        <v>490119</v>
       </c>
       <c r="R54" t="n">
-        <v>7004745</v>
+        <v>7004845</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7967,7 +7976,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7977,7 +7986,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8009,47 +8023,38 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129226468</v>
+        <v>129231961</v>
       </c>
       <c r="B55" t="n">
-        <v>98710</v>
+        <v>98629</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -8063,13 +8068,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490119</v>
+        <v>489928</v>
       </c>
       <c r="R55" t="n">
-        <v>7004845</v>
+        <v>7004745</v>
       </c>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8098,7 +8103,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8108,12 +8113,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8145,48 +8145,67 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129223232</v>
+        <v>129225550</v>
       </c>
       <c r="B56" t="n">
-        <v>79043</v>
+        <v>98712</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490017</v>
+        <v>490157</v>
       </c>
       <c r="R56" t="n">
-        <v>7004780</v>
+        <v>7004793</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8215,7 +8234,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8225,7 +8244,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8240,26 +8264,6 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8277,10 +8281,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129222854</v>
+        <v>129223232</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8288,47 +8292,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489942</v>
+        <v>490017</v>
       </c>
       <c r="R57" t="n">
-        <v>7004813</v>
+        <v>7004780</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8357,7 +8351,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8367,12 +8361,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8401,12 +8390,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8424,7 +8413,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129230183</v>
+        <v>129222854</v>
       </c>
       <c r="B58" t="n">
         <v>57727</v>
@@ -8469,13 +8458,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490060</v>
+        <v>489942</v>
       </c>
       <c r="R58" t="n">
-        <v>7004914</v>
+        <v>7004813</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8504,7 +8493,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8514,12 +8503,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8571,47 +8560,38 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129225550</v>
+        <v>129230183</v>
       </c>
       <c r="B59" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8625,13 +8605,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490157</v>
+        <v>490060</v>
       </c>
       <c r="R59" t="n">
-        <v>7004793</v>
+        <v>7004914</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8660,7 +8640,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8670,12 +8650,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8690,6 +8670,26 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -954,38 +954,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129230003</v>
+        <v>129228951</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -999,13 +1008,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490061</v>
+        <v>490119</v>
       </c>
       <c r="R4" t="n">
-        <v>7004922</v>
+        <v>7004879</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,7 +1043,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1053,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
+          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,26 +1073,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1101,7 +1090,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129230622</v>
+        <v>129230003</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1132,7 +1121,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1146,13 +1135,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490077</v>
+        <v>490061</v>
       </c>
       <c r="R5" t="n">
-        <v>7004897</v>
+        <v>7004922</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1181,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1191,12 +1180,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1248,47 +1237,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129228951</v>
+        <v>129230622</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1302,13 +1282,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490119</v>
+        <v>490077</v>
       </c>
       <c r="R6" t="n">
-        <v>7004879</v>
+        <v>7004897</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1337,7 +1317,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1347,12 +1327,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1367,6 +1347,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1666,7 +1666,7 @@
         <v>129226982</v>
       </c>
       <c r="B9" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>129226861</v>
       </c>
       <c r="B10" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1935,67 +1935,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129231914</v>
+        <v>129231117</v>
       </c>
       <c r="B11" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489938</v>
+        <v>490037</v>
       </c>
       <c r="R11" t="n">
-        <v>7004758</v>
+        <v>7004829</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2024,7 +2005,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2034,12 +2015,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2054,6 +2030,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2071,48 +2067,67 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129231117</v>
+        <v>129231914</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490037</v>
+        <v>489938</v>
       </c>
       <c r="R12" t="n">
-        <v>7004829</v>
+        <v>7004758</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2141,7 +2156,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2151,7 +2166,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2166,26 +2186,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2794,7 +2794,7 @@
         <v>129224667</v>
       </c>
       <c r="B17" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3064,43 +3064,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129229350</v>
+        <v>129230997</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3109,13 +3104,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490080</v>
+        <v>490022</v>
       </c>
       <c r="R19" t="n">
-        <v>7004934</v>
+        <v>7004859</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3144,7 +3139,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3154,12 +3149,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, färska (2025), i riklig mängd längs flera meter på en gran vid en hyggeskant. Granen är gräns-snitslad för en planerad avverning.</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3178,22 +3168,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3211,38 +3201,43 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129230997</v>
+        <v>129229350</v>
       </c>
       <c r="B20" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3251,13 +3246,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490022</v>
+        <v>490080</v>
       </c>
       <c r="R20" t="n">
-        <v>7004859</v>
+        <v>7004934</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3286,7 +3281,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3296,7 +3291,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, färska (2025), i riklig mängd längs flera meter på en gran vid en hyggeskant. Granen är gräns-snitslad för en planerad avverning.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3315,22 +3315,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3625,7 +3625,7 @@
         <v>129225751</v>
       </c>
       <c r="B23" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>129230745</v>
       </c>
       <c r="B24" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3894,48 +3894,67 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129229156</v>
+        <v>129226592</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490069</v>
+        <v>490132</v>
       </c>
       <c r="R25" t="n">
-        <v>7004928</v>
+        <v>7004833</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3964,7 +3983,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3974,7 +3993,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3989,26 +4013,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4026,48 +4030,67 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129227087</v>
+        <v>129225418</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490187</v>
+        <v>490122</v>
       </c>
       <c r="R26" t="n">
-        <v>7004903</v>
+        <v>7004771</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4096,7 +4119,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4106,7 +4129,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4121,26 +4149,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4158,48 +4166,67 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129225967</v>
+        <v>129225602</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490095</v>
+        <v>490142</v>
       </c>
       <c r="R27" t="n">
-        <v>7004830</v>
+        <v>7004806</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4228,7 +4255,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4238,7 +4265,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4253,26 +4285,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4290,38 +4302,47 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129230367</v>
+        <v>129225165</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4335,10 +4356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490063</v>
+        <v>490124</v>
       </c>
       <c r="R28" t="n">
-        <v>7004901</v>
+        <v>7004767</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -4370,7 +4391,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4380,12 +4401,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4400,26 +4421,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4437,10 +4438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129230525</v>
+        <v>129229156</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4448,47 +4449,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490071</v>
+        <v>490069</v>
       </c>
       <c r="R29" t="n">
-        <v>7004894</v>
+        <v>7004928</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4517,7 +4508,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4527,12 +4518,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4561,12 +4547,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4584,67 +4570,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129226592</v>
+        <v>129227087</v>
       </c>
       <c r="B30" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490132</v>
+        <v>490187</v>
       </c>
       <c r="R30" t="n">
-        <v>7004833</v>
+        <v>7004903</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4673,7 +4640,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4683,12 +4650,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4703,6 +4665,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4720,67 +4702,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129225418</v>
+        <v>129225967</v>
       </c>
       <c r="B31" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490122</v>
+        <v>490095</v>
       </c>
       <c r="R31" t="n">
-        <v>7004771</v>
+        <v>7004830</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4809,7 +4772,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4819,12 +4782,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4839,6 +4797,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4856,47 +4834,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129225602</v>
+        <v>129230367</v>
       </c>
       <c r="B32" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4910,13 +4879,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490142</v>
+        <v>490063</v>
       </c>
       <c r="R32" t="n">
-        <v>7004806</v>
+        <v>7004901</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4945,7 +4914,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4955,12 +4924,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4975,6 +4944,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4992,47 +4981,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129225165</v>
+        <v>129230525</v>
       </c>
       <c r="B33" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5046,13 +5026,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490124</v>
+        <v>490071</v>
       </c>
       <c r="R33" t="n">
-        <v>7004767</v>
+        <v>7004894</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5081,7 +5061,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5091,12 +5071,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5111,6 +5091,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5128,45 +5128,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129227795</v>
+        <v>129224808</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>92267</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490175</v>
+        <v>490107</v>
       </c>
       <c r="R34" t="n">
-        <v>7004918</v>
+        <v>7004741</v>
       </c>
       <c r="S34" t="n">
         <v>9</v>
@@ -5198,7 +5203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5208,12 +5213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5402,50 +5402,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129224808</v>
+        <v>129227795</v>
       </c>
       <c r="B36" t="n">
-        <v>92263</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490107</v>
+        <v>490175</v>
       </c>
       <c r="R36" t="n">
-        <v>7004741</v>
+        <v>7004918</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -5477,7 +5472,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5487,7 +5482,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5516,12 +5516,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5542,7 +5542,7 @@
         <v>129228038</v>
       </c>
       <c r="B37" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>129223986</v>
       </c>
       <c r="B39" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>129223203</v>
       </c>
       <c r="B41" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>129227281</v>
       </c>
       <c r="B42" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>129226789</v>
       </c>
       <c r="B44" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6621,38 +6621,43 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129229897</v>
+        <v>129224339</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6666,13 +6671,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490072</v>
+        <v>490008</v>
       </c>
       <c r="R45" t="n">
-        <v>7004920</v>
+        <v>7004696</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6701,7 +6706,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6711,12 +6716,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6731,26 +6736,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6768,43 +6753,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129224339</v>
+        <v>129229897</v>
       </c>
       <c r="B46" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6818,13 +6798,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490008</v>
+        <v>490072</v>
       </c>
       <c r="R46" t="n">
-        <v>7004696</v>
+        <v>7004920</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6853,7 +6833,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6863,12 +6843,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6883,6 +6863,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6900,10 +6900,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129229015</v>
+        <v>129230332</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6911,37 +6911,47 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490105</v>
+        <v>490052</v>
       </c>
       <c r="R47" t="n">
-        <v>7004966</v>
+        <v>7004901</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6970,7 +6980,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6980,7 +6990,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6994,7 +7009,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -7009,12 +7024,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7032,10 +7047,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129223439</v>
+        <v>129230142</v>
       </c>
       <c r="B48" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7043,36 +7058,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -7086,13 +7092,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490044</v>
+        <v>490056</v>
       </c>
       <c r="R48" t="n">
-        <v>7004789</v>
+        <v>7004912</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7121,7 +7127,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7131,12 +7137,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7151,6 +7157,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7168,10 +7194,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129230332</v>
+        <v>129223439</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7179,27 +7205,36 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -7213,13 +7248,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490052</v>
+        <v>490044</v>
       </c>
       <c r="R49" t="n">
-        <v>7004901</v>
+        <v>7004789</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7248,7 +7283,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7258,12 +7293,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7278,26 +7313,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7315,10 +7330,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129230142</v>
+        <v>129229015</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7326,47 +7341,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490056</v>
+        <v>490105</v>
       </c>
       <c r="R50" t="n">
-        <v>7004912</v>
+        <v>7004966</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7395,7 +7400,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7405,12 +7410,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7465,7 +7465,7 @@
         <v>129223831</v>
       </c>
       <c r="B51" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7887,47 +7887,38 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129226468</v>
+        <v>129231961</v>
       </c>
       <c r="B54" t="n">
-        <v>98712</v>
+        <v>98633</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7941,13 +7932,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490119</v>
+        <v>489928</v>
       </c>
       <c r="R54" t="n">
-        <v>7004845</v>
+        <v>7004745</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7976,7 +7967,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7986,12 +7977,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8023,38 +8009,47 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129231961</v>
+        <v>129226468</v>
       </c>
       <c r="B55" t="n">
-        <v>98629</v>
+        <v>98716</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -8068,13 +8063,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489928</v>
+        <v>490119</v>
       </c>
       <c r="R55" t="n">
-        <v>7004745</v>
+        <v>7004845</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8103,7 +8098,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8113,7 +8108,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8148,7 +8148,7 @@
         <v>129225550</v>
       </c>
       <c r="B56" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -954,47 +954,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129228951</v>
+        <v>129230003</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1008,13 +999,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490119</v>
+        <v>490061</v>
       </c>
       <c r="R4" t="n">
-        <v>7004879</v>
+        <v>7004922</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1043,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1053,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,6 +1064,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1090,7 +1101,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129230003</v>
+        <v>129230622</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1121,7 +1132,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1135,13 +1146,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490061</v>
+        <v>490077</v>
       </c>
       <c r="R5" t="n">
-        <v>7004922</v>
+        <v>7004897</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1170,7 +1181,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1180,12 +1191,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
+          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1237,38 +1248,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129230622</v>
+        <v>129228951</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1282,13 +1302,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490077</v>
+        <v>490119</v>
       </c>
       <c r="R6" t="n">
-        <v>7004897</v>
+        <v>7004879</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1317,7 +1337,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1327,12 +1347,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
+          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1347,26 +1367,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1384,45 +1384,64 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129224447</v>
+        <v>129226982</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490020</v>
+        <v>490196</v>
       </c>
       <c r="R7" t="n">
-        <v>7004694</v>
+        <v>7004884</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1454,7 +1473,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1464,7 +1483,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1479,26 +1503,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1516,38 +1520,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129223103</v>
+        <v>129226861</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1561,13 +1574,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489959</v>
+        <v>490181</v>
       </c>
       <c r="R8" t="n">
-        <v>7004819</v>
+        <v>7004884</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1596,7 +1609,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1606,12 +1619,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1626,26 +1639,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1663,64 +1656,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129226982</v>
+        <v>129224447</v>
       </c>
       <c r="B9" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490196</v>
+        <v>490020</v>
       </c>
       <c r="R9" t="n">
-        <v>7004884</v>
+        <v>7004694</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1752,7 +1726,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1762,12 +1736,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1782,6 +1751,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1799,47 +1788,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129226861</v>
+        <v>129223103</v>
       </c>
       <c r="B10" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1853,13 +1833,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490181</v>
+        <v>489959</v>
       </c>
       <c r="R10" t="n">
-        <v>7004884</v>
+        <v>7004819</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1888,7 +1868,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1898,12 +1878,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1918,6 +1898,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2070,7 +2070,7 @@
         <v>129231914</v>
       </c>
       <c r="B12" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>129224667</v>
       </c>
       <c r="B17" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>129225751</v>
       </c>
       <c r="B23" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>129230745</v>
       </c>
       <c r="B24" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3894,67 +3894,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129226592</v>
+        <v>129229156</v>
       </c>
       <c r="B25" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490132</v>
+        <v>490069</v>
       </c>
       <c r="R25" t="n">
-        <v>7004833</v>
+        <v>7004928</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3983,7 +3964,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3993,12 +3974,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4013,6 +3989,26 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4030,67 +4026,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129225418</v>
+        <v>129227087</v>
       </c>
       <c r="B26" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490122</v>
+        <v>490187</v>
       </c>
       <c r="R26" t="n">
-        <v>7004771</v>
+        <v>7004903</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4119,7 +4096,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4129,12 +4106,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4149,6 +4121,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4166,67 +4158,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129225602</v>
+        <v>129225967</v>
       </c>
       <c r="B27" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490142</v>
+        <v>490095</v>
       </c>
       <c r="R27" t="n">
-        <v>7004806</v>
+        <v>7004830</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4255,7 +4228,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4265,12 +4238,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4285,6 +4253,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4302,47 +4290,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129225165</v>
+        <v>129230367</v>
       </c>
       <c r="B28" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4356,10 +4335,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490124</v>
+        <v>490063</v>
       </c>
       <c r="R28" t="n">
-        <v>7004767</v>
+        <v>7004901</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -4391,7 +4370,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4401,12 +4380,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4421,6 +4400,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4438,10 +4437,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129229156</v>
+        <v>129230525</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4449,37 +4448,47 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490069</v>
+        <v>490071</v>
       </c>
       <c r="R29" t="n">
-        <v>7004928</v>
+        <v>7004894</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4508,7 +4517,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4518,7 +4527,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4547,12 +4561,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4570,48 +4584,67 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129227087</v>
+        <v>129226592</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490187</v>
+        <v>490132</v>
       </c>
       <c r="R30" t="n">
-        <v>7004903</v>
+        <v>7004833</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4640,7 +4673,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4650,7 +4683,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4665,26 +4703,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4702,48 +4720,67 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129225967</v>
+        <v>129225418</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490095</v>
+        <v>490122</v>
       </c>
       <c r="R31" t="n">
-        <v>7004830</v>
+        <v>7004771</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4772,7 +4809,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4782,7 +4819,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4797,26 +4839,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4834,38 +4856,47 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129230367</v>
+        <v>129225602</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4879,13 +4910,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490063</v>
+        <v>490142</v>
       </c>
       <c r="R32" t="n">
-        <v>7004901</v>
+        <v>7004806</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4914,7 +4945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4924,12 +4955,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4944,26 +4975,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4981,38 +4992,47 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129230525</v>
+        <v>129225165</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5026,13 +5046,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490071</v>
+        <v>490124</v>
       </c>
       <c r="R33" t="n">
-        <v>7004894</v>
+        <v>7004767</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5061,7 +5081,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5071,12 +5091,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5091,26 +5111,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129224808</v>
+        <v>129223375</v>
       </c>
       <c r="B34" t="n">
-        <v>92267</v>
+        <v>80178</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5139,27 +5139,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5168,13 +5168,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490107</v>
+        <v>490028</v>
       </c>
       <c r="R34" t="n">
-        <v>7004741</v>
+        <v>7004796</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5232,22 +5232,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5265,53 +5265,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129223375</v>
+        <v>129227795</v>
       </c>
       <c r="B35" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490028</v>
+        <v>490175</v>
       </c>
       <c r="R35" t="n">
-        <v>7004796</v>
+        <v>7004918</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5340,7 +5335,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5350,7 +5345,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5369,22 +5369,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5402,48 +5402,67 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129227795</v>
+        <v>129228038</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490175</v>
+        <v>490161</v>
       </c>
       <c r="R36" t="n">
-        <v>7004918</v>
+        <v>7004940</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5472,7 +5491,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5482,12 +5501,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5501,27 +5520,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5539,52 +5538,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129228038</v>
+        <v>129224808</v>
       </c>
       <c r="B37" t="n">
-        <v>98716</v>
+        <v>92268</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5593,13 +5578,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490161</v>
+        <v>490107</v>
       </c>
       <c r="R37" t="n">
-        <v>7004940</v>
+        <v>7004741</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5628,7 +5613,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5638,12 +5623,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5657,7 +5637,27 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5815,7 +5815,7 @@
         <v>129223986</v>
       </c>
       <c r="B39" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5948,38 +5948,52 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129230966</v>
+        <v>129223203</v>
       </c>
       <c r="B40" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5988,10 +6002,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490020</v>
+        <v>489995</v>
       </c>
       <c r="R40" t="n">
-        <v>7004857</v>
+        <v>7004788</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -6023,7 +6037,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6033,7 +6047,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6048,26 +6067,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6085,10 +6084,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129223203</v>
+        <v>129227281</v>
       </c>
       <c r="B41" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6115,7 +6114,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6139,13 +6138,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489995</v>
+        <v>490162</v>
       </c>
       <c r="R41" t="n">
-        <v>7004788</v>
+        <v>7004880</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6174,7 +6173,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6184,12 +6183,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 16 plantor inom ca 2 m2 yta intill en tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6221,52 +6220,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129227281</v>
+        <v>129230966</v>
       </c>
       <c r="B42" t="n">
-        <v>98716</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -6275,13 +6260,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490162</v>
+        <v>490020</v>
       </c>
       <c r="R42" t="n">
-        <v>7004880</v>
+        <v>7004857</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6310,7 +6295,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6320,12 +6305,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Minst 16 plantor inom ca 2 m2 yta intill en tall.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6340,6 +6320,26 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6507,7 +6507,7 @@
         <v>129226789</v>
       </c>
       <c r="B44" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6621,43 +6621,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129224339</v>
+        <v>129229897</v>
       </c>
       <c r="B45" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6671,13 +6666,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490008</v>
+        <v>490072</v>
       </c>
       <c r="R45" t="n">
-        <v>7004696</v>
+        <v>7004920</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6706,7 +6701,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6716,12 +6711,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6736,6 +6731,26 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6753,38 +6768,43 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129229897</v>
+        <v>129224339</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6798,13 +6818,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490072</v>
+        <v>490008</v>
       </c>
       <c r="R46" t="n">
-        <v>7004920</v>
+        <v>7004696</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6833,7 +6853,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6843,12 +6863,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6863,26 +6883,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6900,10 +6900,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129230332</v>
+        <v>129223439</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6911,27 +6911,36 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6945,13 +6954,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490052</v>
+        <v>490044</v>
       </c>
       <c r="R47" t="n">
-        <v>7004901</v>
+        <v>7004789</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6980,7 +6989,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6990,12 +6999,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7010,26 +7019,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7047,10 +7036,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129230142</v>
+        <v>129229015</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7058,47 +7047,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490056</v>
+        <v>490105</v>
       </c>
       <c r="R48" t="n">
-        <v>7004912</v>
+        <v>7004966</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7127,7 +7106,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7137,12 +7116,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7156,7 +7130,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -7171,12 +7145,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7194,10 +7168,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129223439</v>
+        <v>129230332</v>
       </c>
       <c r="B49" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7205,36 +7179,27 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -7248,13 +7213,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490044</v>
+        <v>490052</v>
       </c>
       <c r="R49" t="n">
-        <v>7004789</v>
+        <v>7004901</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7283,7 +7248,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7293,12 +7258,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7313,6 +7278,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7330,10 +7315,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129229015</v>
+        <v>129230142</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7341,37 +7326,47 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490105</v>
+        <v>490056</v>
       </c>
       <c r="R50" t="n">
-        <v>7004966</v>
+        <v>7004912</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7400,7 +7395,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7410,7 +7405,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7465,7 +7465,7 @@
         <v>129223831</v>
       </c>
       <c r="B51" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>129231961</v>
       </c>
       <c r="B54" t="n">
-        <v>98633</v>
+        <v>98641</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>129226468</v>
       </c>
       <c r="B55" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -8145,67 +8145,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129225550</v>
+        <v>129223232</v>
       </c>
       <c r="B56" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490157</v>
+        <v>490017</v>
       </c>
       <c r="R56" t="n">
-        <v>7004793</v>
+        <v>7004780</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8234,7 +8215,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8244,12 +8225,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8264,6 +8240,26 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8281,10 +8277,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129223232</v>
+        <v>129222854</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8292,37 +8288,47 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490017</v>
+        <v>489942</v>
       </c>
       <c r="R57" t="n">
-        <v>7004780</v>
+        <v>7004813</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8351,7 +8357,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8361,7 +8367,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8390,12 +8401,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8413,7 +8424,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129222854</v>
+        <v>129230183</v>
       </c>
       <c r="B58" t="n">
         <v>57727</v>
@@ -8458,13 +8469,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489942</v>
+        <v>490060</v>
       </c>
       <c r="R58" t="n">
-        <v>7004813</v>
+        <v>7004914</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8493,7 +8504,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8503,12 +8514,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8560,38 +8571,47 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129230183</v>
+        <v>129225550</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8605,13 +8625,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490060</v>
+        <v>490157</v>
       </c>
       <c r="R59" t="n">
-        <v>7004914</v>
+        <v>7004793</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8640,7 +8660,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8650,12 +8670,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8670,26 +8690,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129227061</v>
+        <v>129230577</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490204</v>
+        <v>490070</v>
       </c>
       <c r="R2" t="n">
-        <v>7004896</v>
+        <v>7004890</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,12 +799,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +822,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129230577</v>
+        <v>129227061</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,44 +833,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490070</v>
+        <v>490204</v>
       </c>
       <c r="R3" t="n">
-        <v>7004890</v>
+        <v>7004896</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,12 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:51</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,12 +931,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -954,38 +954,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129230003</v>
+        <v>129228951</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -999,13 +1008,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490061</v>
+        <v>490119</v>
       </c>
       <c r="R4" t="n">
-        <v>7004922</v>
+        <v>7004879</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,7 +1043,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1053,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
+          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,26 +1073,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1101,7 +1090,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129230622</v>
+        <v>129230003</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1132,7 +1121,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1146,13 +1135,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490077</v>
+        <v>490061</v>
       </c>
       <c r="R5" t="n">
-        <v>7004897</v>
+        <v>7004922</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1181,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1191,12 +1180,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1248,47 +1237,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129228951</v>
+        <v>129230622</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1302,13 +1282,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490119</v>
+        <v>490077</v>
       </c>
       <c r="R6" t="n">
-        <v>7004879</v>
+        <v>7004897</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1337,7 +1317,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1347,12 +1327,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1367,6 +1347,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1384,47 +1384,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129226982</v>
+        <v>129223103</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1438,13 +1429,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490196</v>
+        <v>489959</v>
       </c>
       <c r="R7" t="n">
-        <v>7004884</v>
+        <v>7004819</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1473,7 +1464,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1483,12 +1474,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1503,6 +1494,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1520,7 +1531,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129226861</v>
+        <v>129226982</v>
       </c>
       <c r="B8" t="n">
         <v>98724</v>
@@ -1550,7 +1561,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1574,7 +1585,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490181</v>
+        <v>490196</v>
       </c>
       <c r="R8" t="n">
         <v>7004884</v>
@@ -1609,7 +1620,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1619,12 +1630,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1656,45 +1667,64 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129224447</v>
+        <v>129226861</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490020</v>
+        <v>490181</v>
       </c>
       <c r="R9" t="n">
-        <v>7004694</v>
+        <v>7004884</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1726,7 +1756,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1736,7 +1766,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1751,26 +1786,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1788,10 +1803,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129223103</v>
+        <v>129224447</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1799,47 +1814,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489959</v>
+        <v>490020</v>
       </c>
       <c r="R10" t="n">
-        <v>7004819</v>
+        <v>7004694</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1868,7 +1873,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1878,12 +1883,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1935,48 +1935,67 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129231117</v>
+        <v>129231914</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490037</v>
+        <v>489938</v>
       </c>
       <c r="R11" t="n">
-        <v>7004829</v>
+        <v>7004758</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2005,7 +2024,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2015,7 +2034,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2030,26 +2054,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2067,67 +2071,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129231914</v>
+        <v>129231117</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489938</v>
+        <v>490037</v>
       </c>
       <c r="R12" t="n">
-        <v>7004758</v>
+        <v>7004829</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2156,7 +2141,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2166,12 +2151,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2186,6 +2166,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2203,7 +2203,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129231535</v>
+        <v>129230279</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -2248,13 +2248,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489991</v>
+        <v>490064</v>
       </c>
       <c r="R13" t="n">
-        <v>7004843</v>
+        <v>7004903</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2350,7 +2350,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129230279</v>
+        <v>129230462</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490064</v>
+        <v>490066</v>
       </c>
       <c r="R14" t="n">
-        <v>7004903</v>
+        <v>7004896</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2497,7 +2497,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129230462</v>
+        <v>129230594</v>
       </c>
       <c r="B15" t="n">
         <v>57727</v>
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490066</v>
+        <v>490071</v>
       </c>
       <c r="R15" t="n">
-        <v>7004896</v>
+        <v>7004887</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2644,43 +2644,47 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129230594</v>
+        <v>129224667</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2689,13 +2693,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490071</v>
+        <v>490027</v>
       </c>
       <c r="R16" t="n">
-        <v>7004887</v>
+        <v>7004700</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2724,7 +2728,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2734,12 +2738,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Minst 250 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2754,26 +2758,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2791,47 +2775,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129224667</v>
+        <v>129231535</v>
       </c>
       <c r="B17" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2840,10 +2820,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490027</v>
+        <v>489991</v>
       </c>
       <c r="R17" t="n">
-        <v>7004700</v>
+        <v>7004843</v>
       </c>
       <c r="S17" t="n">
         <v>8</v>
@@ -2875,7 +2855,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2885,12 +2865,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 250 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2905,6 +2885,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3894,48 +3894,67 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129229156</v>
+        <v>129226592</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490069</v>
+        <v>490132</v>
       </c>
       <c r="R25" t="n">
-        <v>7004928</v>
+        <v>7004833</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3964,7 +3983,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3974,7 +3993,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3989,26 +4013,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4026,48 +4030,67 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129227087</v>
+        <v>129225418</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490187</v>
+        <v>490122</v>
       </c>
       <c r="R26" t="n">
-        <v>7004903</v>
+        <v>7004771</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4096,7 +4119,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4106,7 +4129,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4121,26 +4149,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4158,48 +4166,67 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129225967</v>
+        <v>129225602</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490095</v>
+        <v>490142</v>
       </c>
       <c r="R27" t="n">
-        <v>7004830</v>
+        <v>7004806</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4228,7 +4255,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4238,7 +4265,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4253,26 +4285,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4290,38 +4302,47 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129230367</v>
+        <v>129225165</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4335,10 +4356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490063</v>
+        <v>490124</v>
       </c>
       <c r="R28" t="n">
-        <v>7004901</v>
+        <v>7004767</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -4370,7 +4391,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4380,12 +4401,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4400,26 +4421,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4437,7 +4438,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129230525</v>
+        <v>129230367</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -4482,13 +4483,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490071</v>
+        <v>490063</v>
       </c>
       <c r="R29" t="n">
-        <v>7004894</v>
+        <v>7004901</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4517,7 +4518,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4527,12 +4528,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4584,47 +4585,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129226592</v>
+        <v>129230525</v>
       </c>
       <c r="B30" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4638,13 +4630,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490132</v>
+        <v>490071</v>
       </c>
       <c r="R30" t="n">
-        <v>7004833</v>
+        <v>7004894</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4673,7 +4665,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4683,12 +4675,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4703,6 +4695,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4720,67 +4732,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129225418</v>
+        <v>129229156</v>
       </c>
       <c r="B31" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490122</v>
+        <v>490069</v>
       </c>
       <c r="R31" t="n">
-        <v>7004771</v>
+        <v>7004928</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4809,7 +4802,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4819,12 +4812,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4839,6 +4827,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4856,67 +4864,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129225602</v>
+        <v>129227087</v>
       </c>
       <c r="B32" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490142</v>
+        <v>490187</v>
       </c>
       <c r="R32" t="n">
-        <v>7004806</v>
+        <v>7004903</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4945,7 +4934,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4955,12 +4944,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4975,6 +4959,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4992,67 +4996,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129225165</v>
+        <v>129225967</v>
       </c>
       <c r="B33" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490124</v>
+        <v>490095</v>
       </c>
       <c r="R33" t="n">
-        <v>7004767</v>
+        <v>7004830</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5081,7 +5066,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5091,12 +5076,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5111,6 +5091,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5128,53 +5128,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129223375</v>
+        <v>129227795</v>
       </c>
       <c r="B34" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490028</v>
+        <v>490175</v>
       </c>
       <c r="R34" t="n">
-        <v>7004796</v>
+        <v>7004918</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5203,7 +5198,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5213,7 +5208,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5232,22 +5232,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5265,48 +5265,67 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129227795</v>
+        <v>129228038</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490175</v>
+        <v>490161</v>
       </c>
       <c r="R35" t="n">
-        <v>7004918</v>
+        <v>7004940</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5335,7 +5354,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5345,12 +5364,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5364,27 +5383,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5402,52 +5401,38 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129228038</v>
+        <v>129224808</v>
       </c>
       <c r="B36" t="n">
-        <v>98724</v>
+        <v>92268</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5456,13 +5441,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490161</v>
+        <v>490107</v>
       </c>
       <c r="R36" t="n">
-        <v>7004940</v>
+        <v>7004741</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5491,7 +5476,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5501,12 +5486,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5520,7 +5500,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5538,10 +5538,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129224808</v>
+        <v>129223375</v>
       </c>
       <c r="B37" t="n">
-        <v>92268</v>
+        <v>80178</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5549,27 +5549,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490107</v>
+        <v>490028</v>
       </c>
       <c r="R37" t="n">
-        <v>7004741</v>
+        <v>7004796</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5642,22 +5642,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5948,52 +5948,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129223203</v>
+        <v>129230966</v>
       </c>
       <c r="B40" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -6002,10 +5988,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489995</v>
+        <v>490020</v>
       </c>
       <c r="R40" t="n">
-        <v>7004788</v>
+        <v>7004857</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -6037,7 +6023,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6047,12 +6033,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6067,6 +6048,26 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6084,7 +6085,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129227281</v>
+        <v>129223203</v>
       </c>
       <c r="B41" t="n">
         <v>98724</v>
@@ -6114,7 +6115,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6138,13 +6139,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490162</v>
+        <v>489995</v>
       </c>
       <c r="R41" t="n">
-        <v>7004880</v>
+        <v>7004788</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6173,7 +6174,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6183,12 +6184,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Minst 16 plantor inom ca 2 m2 yta intill en tall.</t>
+          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6220,38 +6221,52 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129230966</v>
+        <v>129227281</v>
       </c>
       <c r="B42" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -6260,13 +6275,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490020</v>
+        <v>490162</v>
       </c>
       <c r="R42" t="n">
-        <v>7004857</v>
+        <v>7004880</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6295,7 +6310,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6305,7 +6320,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Minst 16 plantor inom ca 2 m2 yta intill en tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6320,26 +6340,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6504,38 +6504,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129226789</v>
+        <v>129224339</v>
       </c>
       <c r="B44" t="n">
-        <v>92505</v>
+        <v>98724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6544,13 +6554,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490174</v>
+        <v>490008</v>
       </c>
       <c r="R44" t="n">
-        <v>7004879</v>
+        <v>7004696</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6579,7 +6589,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6589,7 +6599,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6603,7 +6618,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6621,43 +6636,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129229897</v>
+        <v>129226789</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>92505</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6666,13 +6676,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490072</v>
+        <v>490174</v>
       </c>
       <c r="R45" t="n">
-        <v>7004920</v>
+        <v>7004879</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6701,7 +6711,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6711,12 +6721,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6730,27 +6735,7 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6768,43 +6753,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129224339</v>
+        <v>129229897</v>
       </c>
       <c r="B46" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6818,13 +6798,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490008</v>
+        <v>490072</v>
       </c>
       <c r="R46" t="n">
-        <v>7004696</v>
+        <v>7004920</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6853,7 +6833,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6863,12 +6843,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6883,6 +6863,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6900,10 +6900,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129223439</v>
+        <v>129230332</v>
       </c>
       <c r="B47" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6911,36 +6911,27 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6954,13 +6945,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490044</v>
+        <v>490052</v>
       </c>
       <c r="R47" t="n">
-        <v>7004789</v>
+        <v>7004901</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6989,7 +6980,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6999,12 +6990,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7019,6 +7010,26 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7036,10 +7047,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129229015</v>
+        <v>129230142</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7047,37 +7058,47 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490105</v>
+        <v>490056</v>
       </c>
       <c r="R48" t="n">
-        <v>7004966</v>
+        <v>7004912</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7106,7 +7127,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7116,7 +7137,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7130,7 +7156,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -7145,12 +7171,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7168,10 +7194,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129230332</v>
+        <v>129229015</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7179,47 +7205,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490052</v>
+        <v>490105</v>
       </c>
       <c r="R49" t="n">
-        <v>7004901</v>
+        <v>7004966</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7248,7 +7264,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7258,12 +7274,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:37</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7277,7 +7288,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -7292,12 +7303,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7315,10 +7326,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129230142</v>
+        <v>129223439</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7326,27 +7337,36 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7360,13 +7380,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490056</v>
+        <v>490044</v>
       </c>
       <c r="R50" t="n">
-        <v>7004912</v>
+        <v>7004789</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7395,7 +7415,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7405,12 +7425,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7425,26 +7445,6 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7462,47 +7462,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129223831</v>
+        <v>129230834</v>
       </c>
       <c r="B51" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7516,13 +7507,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490057</v>
+        <v>490020</v>
       </c>
       <c r="R51" t="n">
-        <v>7004780</v>
+        <v>7004888</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7551,7 +7542,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7561,12 +7552,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7581,6 +7572,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7598,38 +7609,47 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129230834</v>
+        <v>129223831</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7643,13 +7663,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490020</v>
+        <v>490057</v>
       </c>
       <c r="R52" t="n">
-        <v>7004888</v>
+        <v>7004780</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7678,7 +7698,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7688,12 +7708,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
+          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7708,26 +7728,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -8145,10 +8145,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129223232</v>
+        <v>129222854</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8156,37 +8156,47 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490017</v>
+        <v>489942</v>
       </c>
       <c r="R56" t="n">
-        <v>7004780</v>
+        <v>7004813</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8215,7 +8225,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8225,7 +8235,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8254,12 +8269,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8277,7 +8292,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129222854</v>
+        <v>129230183</v>
       </c>
       <c r="B57" t="n">
         <v>57727</v>
@@ -8322,13 +8337,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489942</v>
+        <v>490060</v>
       </c>
       <c r="R57" t="n">
-        <v>7004813</v>
+        <v>7004914</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8357,7 +8372,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8367,12 +8382,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8424,10 +8439,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129230183</v>
+        <v>129223232</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8435,47 +8450,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490060</v>
+        <v>490017</v>
       </c>
       <c r="R58" t="n">
-        <v>7004914</v>
+        <v>7004780</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8504,7 +8509,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8514,12 +8519,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:31</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -954,47 +954,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129228951</v>
+        <v>129230003</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1008,13 +999,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490119</v>
+        <v>490061</v>
       </c>
       <c r="R4" t="n">
-        <v>7004879</v>
+        <v>7004922</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1043,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1053,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,6 +1064,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1090,7 +1101,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129230003</v>
+        <v>129230622</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1121,7 +1132,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1135,13 +1146,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490061</v>
+        <v>490077</v>
       </c>
       <c r="R5" t="n">
-        <v>7004922</v>
+        <v>7004897</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1170,7 +1181,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1180,12 +1191,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
+          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1237,38 +1248,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129230622</v>
+        <v>129228951</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1282,13 +1302,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490077</v>
+        <v>490119</v>
       </c>
       <c r="R6" t="n">
-        <v>7004897</v>
+        <v>7004879</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1317,7 +1337,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1327,12 +1347,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
+          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1347,26 +1367,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1384,38 +1384,47 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129223103</v>
+        <v>129226982</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1429,13 +1438,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489959</v>
+        <v>490196</v>
       </c>
       <c r="R7" t="n">
-        <v>7004819</v>
+        <v>7004884</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1464,7 +1473,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1474,12 +1483,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1494,26 +1503,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1531,7 +1520,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129226982</v>
+        <v>129226861</v>
       </c>
       <c r="B8" t="n">
         <v>98724</v>
@@ -1561,7 +1550,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1585,7 +1574,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490196</v>
+        <v>490181</v>
       </c>
       <c r="R8" t="n">
         <v>7004884</v>
@@ -1620,7 +1609,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1630,12 +1619,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1667,47 +1656,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129226861</v>
+        <v>129223103</v>
       </c>
       <c r="B9" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1721,13 +1701,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490181</v>
+        <v>489959</v>
       </c>
       <c r="R9" t="n">
-        <v>7004884</v>
+        <v>7004819</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1756,7 +1736,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1766,12 +1746,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1786,6 +1766,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2203,7 +2203,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129230279</v>
+        <v>129231535</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -2248,13 +2248,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490064</v>
+        <v>489991</v>
       </c>
       <c r="R13" t="n">
-        <v>7004903</v>
+        <v>7004843</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2350,7 +2350,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129230462</v>
+        <v>129230279</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490066</v>
+        <v>490064</v>
       </c>
       <c r="R14" t="n">
-        <v>7004896</v>
+        <v>7004903</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2775,7 +2775,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129231535</v>
+        <v>129230462</v>
       </c>
       <c r="B17" t="n">
         <v>57727</v>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>489991</v>
+        <v>490066</v>
       </c>
       <c r="R17" t="n">
-        <v>7004843</v>
+        <v>7004896</v>
       </c>
       <c r="S17" t="n">
         <v>8</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3894,67 +3894,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129226592</v>
+        <v>129229156</v>
       </c>
       <c r="B25" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490132</v>
+        <v>490069</v>
       </c>
       <c r="R25" t="n">
-        <v>7004833</v>
+        <v>7004928</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3983,7 +3964,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3993,12 +3974,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4013,6 +3989,26 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4030,67 +4026,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129225418</v>
+        <v>129227087</v>
       </c>
       <c r="B26" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490122</v>
+        <v>490187</v>
       </c>
       <c r="R26" t="n">
-        <v>7004771</v>
+        <v>7004903</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4119,7 +4096,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4129,12 +4106,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4149,6 +4121,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4166,67 +4158,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129225602</v>
+        <v>129225967</v>
       </c>
       <c r="B27" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490142</v>
+        <v>490095</v>
       </c>
       <c r="R27" t="n">
-        <v>7004806</v>
+        <v>7004830</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4255,7 +4228,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4265,12 +4238,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4285,6 +4253,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4302,47 +4290,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129225165</v>
+        <v>129230367</v>
       </c>
       <c r="B28" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4356,10 +4335,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490124</v>
+        <v>490063</v>
       </c>
       <c r="R28" t="n">
-        <v>7004767</v>
+        <v>7004901</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -4391,7 +4370,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4401,12 +4380,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4421,6 +4400,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4438,7 +4437,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129230367</v>
+        <v>129230525</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -4483,13 +4482,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490063</v>
+        <v>490071</v>
       </c>
       <c r="R29" t="n">
-        <v>7004901</v>
+        <v>7004894</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4518,7 +4517,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4528,12 +4527,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4585,38 +4584,47 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129230525</v>
+        <v>129226592</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4630,13 +4638,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490071</v>
+        <v>490132</v>
       </c>
       <c r="R30" t="n">
-        <v>7004894</v>
+        <v>7004833</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4665,7 +4673,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4675,12 +4683,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4695,26 +4703,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4732,48 +4720,67 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129229156</v>
+        <v>129225418</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490069</v>
+        <v>490122</v>
       </c>
       <c r="R31" t="n">
-        <v>7004928</v>
+        <v>7004771</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4802,7 +4809,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4812,7 +4819,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4827,26 +4839,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4864,48 +4856,67 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129227087</v>
+        <v>129225602</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490187</v>
+        <v>490142</v>
       </c>
       <c r="R32" t="n">
-        <v>7004903</v>
+        <v>7004806</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4934,7 +4945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4944,7 +4955,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4959,26 +4975,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4996,48 +4992,67 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129225967</v>
+        <v>129225165</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490095</v>
+        <v>490124</v>
       </c>
       <c r="R33" t="n">
-        <v>7004830</v>
+        <v>7004767</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5066,7 +5081,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5076,7 +5091,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5091,26 +5111,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5128,48 +5128,53 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129227795</v>
+        <v>129223375</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490175</v>
+        <v>490028</v>
       </c>
       <c r="R34" t="n">
-        <v>7004918</v>
+        <v>7004796</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5198,7 +5203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5208,12 +5213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5232,22 +5232,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5265,67 +5265,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129228038</v>
+        <v>129227795</v>
       </c>
       <c r="B35" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490161</v>
+        <v>490175</v>
       </c>
       <c r="R35" t="n">
-        <v>7004940</v>
+        <v>7004918</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5354,7 +5335,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5364,12 +5345,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5383,7 +5364,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5538,38 +5539,52 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129223375</v>
+        <v>129228038</v>
       </c>
       <c r="B37" t="n">
-        <v>80178</v>
+        <v>98724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5578,13 +5593,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490028</v>
+        <v>490161</v>
       </c>
       <c r="R37" t="n">
-        <v>7004796</v>
+        <v>7004940</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5613,7 +5628,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5623,7 +5638,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5637,27 +5657,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -6504,48 +6504,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129224339</v>
+        <v>129226789</v>
       </c>
       <c r="B44" t="n">
-        <v>98724</v>
+        <v>92505</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6554,13 +6544,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490008</v>
+        <v>490174</v>
       </c>
       <c r="R44" t="n">
-        <v>7004696</v>
+        <v>7004879</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6589,7 +6579,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6599,12 +6589,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6618,7 +6603,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6636,38 +6621,43 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129226789</v>
+        <v>129229897</v>
       </c>
       <c r="B45" t="n">
-        <v>92505</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6676,13 +6666,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490174</v>
+        <v>490072</v>
       </c>
       <c r="R45" t="n">
-        <v>7004879</v>
+        <v>7004920</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6711,7 +6701,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6721,7 +6711,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6735,7 +6730,27 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6753,38 +6768,43 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129229897</v>
+        <v>129224339</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6798,13 +6818,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490072</v>
+        <v>490008</v>
       </c>
       <c r="R46" t="n">
-        <v>7004920</v>
+        <v>7004696</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6833,7 +6853,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6843,12 +6863,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6863,26 +6883,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129230577</v>
+        <v>129227061</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,44 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490070</v>
+        <v>490204</v>
       </c>
       <c r="R2" t="n">
-        <v>7004890</v>
+        <v>7004896</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:51</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,12 +784,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -822,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129227061</v>
+        <v>129230577</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,34 +818,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490204</v>
+        <v>490070</v>
       </c>
       <c r="R3" t="n">
-        <v>7004896</v>
+        <v>7004890</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +897,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,12 +931,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1251,7 +1251,7 @@
         <v>129228951</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1384,47 +1384,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129226982</v>
+        <v>129223103</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1438,13 +1429,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490196</v>
+        <v>489959</v>
       </c>
       <c r="R7" t="n">
-        <v>7004884</v>
+        <v>7004819</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1473,7 +1464,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1483,12 +1474,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1503,6 +1494,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1520,10 +1531,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129226861</v>
+        <v>129226982</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1550,7 +1561,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1574,7 +1585,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490181</v>
+        <v>490196</v>
       </c>
       <c r="R8" t="n">
         <v>7004884</v>
@@ -1609,7 +1620,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1619,12 +1630,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1656,38 +1667,47 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129223103</v>
+        <v>129226861</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1701,13 +1721,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>489959</v>
+        <v>490181</v>
       </c>
       <c r="R9" t="n">
-        <v>7004819</v>
+        <v>7004884</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1736,7 +1756,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1746,12 +1766,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1766,26 +1786,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1935,67 +1935,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129231914</v>
+        <v>129231117</v>
       </c>
       <c r="B11" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489938</v>
+        <v>490037</v>
       </c>
       <c r="R11" t="n">
-        <v>7004758</v>
+        <v>7004829</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2024,7 +2005,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2034,12 +2015,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2054,6 +2030,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2071,48 +2067,67 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129231117</v>
+        <v>129231914</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490037</v>
+        <v>489938</v>
       </c>
       <c r="R12" t="n">
-        <v>7004829</v>
+        <v>7004758</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2141,7 +2156,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2151,7 +2166,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2166,26 +2186,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129230594</v>
+        <v>129230462</v>
       </c>
       <c r="B15" t="n">
         <v>57727</v>
@@ -2542,13 +2542,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490071</v>
+        <v>490066</v>
       </c>
       <c r="R15" t="n">
-        <v>7004887</v>
+        <v>7004896</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2644,47 +2644,43 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129224667</v>
+        <v>129230594</v>
       </c>
       <c r="B16" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2693,13 +2689,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490027</v>
+        <v>490071</v>
       </c>
       <c r="R16" t="n">
-        <v>7004700</v>
+        <v>7004887</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2728,7 +2724,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2738,12 +2734,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minst 250 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2758,6 +2754,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2775,43 +2791,47 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129230462</v>
+        <v>129224667</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2820,10 +2840,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490066</v>
+        <v>490027</v>
       </c>
       <c r="R17" t="n">
-        <v>7004896</v>
+        <v>7004700</v>
       </c>
       <c r="S17" t="n">
         <v>8</v>
@@ -2855,7 +2875,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2865,12 +2885,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Minst 250 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2885,26 +2905,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3064,38 +3064,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129230997</v>
+        <v>129229350</v>
       </c>
       <c r="B19" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3104,13 +3109,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490022</v>
+        <v>490080</v>
       </c>
       <c r="R19" t="n">
-        <v>7004859</v>
+        <v>7004934</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3139,7 +3144,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3149,7 +3154,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, färska (2025), i riklig mängd längs flera meter på en gran vid en hyggeskant. Granen är gräns-snitslad för en planerad avverning.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3168,22 +3178,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3201,43 +3211,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129229350</v>
+        <v>129230997</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3246,13 +3251,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490080</v>
+        <v>490022</v>
       </c>
       <c r="R20" t="n">
-        <v>7004934</v>
+        <v>7004859</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3281,7 +3286,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3291,12 +3296,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, färska (2025), i riklig mängd längs flera meter på en gran vid en hyggeskant. Granen är gräns-snitslad för en planerad avverning.</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3315,22 +3315,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3625,7 +3625,7 @@
         <v>129225751</v>
       </c>
       <c r="B23" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>129230745</v>
       </c>
       <c r="B24" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>129226592</v>
       </c>
       <c r="B30" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>129225418</v>
       </c>
       <c r="B31" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>129225602</v>
       </c>
       <c r="B32" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>129225165</v>
       </c>
       <c r="B33" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5128,10 +5128,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129223375</v>
+        <v>129224808</v>
       </c>
       <c r="B34" t="n">
-        <v>80178</v>
+        <v>92271</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5139,27 +5139,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5168,13 +5168,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490028</v>
+        <v>490107</v>
       </c>
       <c r="R34" t="n">
-        <v>7004796</v>
+        <v>7004741</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5232,22 +5232,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5265,48 +5265,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129227795</v>
+        <v>129223375</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490175</v>
+        <v>490028</v>
       </c>
       <c r="R35" t="n">
-        <v>7004918</v>
+        <v>7004796</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5335,7 +5340,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5345,12 +5350,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5369,22 +5369,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5402,50 +5402,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129224808</v>
+        <v>129227795</v>
       </c>
       <c r="B36" t="n">
-        <v>92268</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490107</v>
+        <v>490175</v>
       </c>
       <c r="R36" t="n">
-        <v>7004741</v>
+        <v>7004918</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -5477,7 +5472,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5487,7 +5482,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5516,12 +5516,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5542,7 +5542,7 @@
         <v>129228038</v>
       </c>
       <c r="B37" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>129223986</v>
       </c>
       <c r="B39" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
         <v>129223203</v>
       </c>
       <c r="B41" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>129227281</v>
       </c>
       <c r="B42" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>129226789</v>
       </c>
       <c r="B44" t="n">
-        <v>92505</v>
+        <v>92508</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6621,38 +6621,43 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129229897</v>
+        <v>129224339</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6666,13 +6671,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490072</v>
+        <v>490008</v>
       </c>
       <c r="R45" t="n">
-        <v>7004920</v>
+        <v>7004696</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6701,7 +6706,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6711,12 +6716,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6731,26 +6736,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6768,43 +6753,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129224339</v>
+        <v>129229897</v>
       </c>
       <c r="B46" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6818,13 +6798,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490008</v>
+        <v>490072</v>
       </c>
       <c r="R46" t="n">
-        <v>7004696</v>
+        <v>7004920</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6853,7 +6833,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6863,12 +6843,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6883,6 +6863,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6900,10 +6900,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129230332</v>
+        <v>129229015</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6911,47 +6911,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490052</v>
+        <v>490105</v>
       </c>
       <c r="R47" t="n">
-        <v>7004901</v>
+        <v>7004966</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6980,7 +6970,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6990,12 +6980,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:37</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7009,7 +6994,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -7024,12 +7009,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7047,7 +7032,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129230142</v>
+        <v>129230332</v>
       </c>
       <c r="B48" t="n">
         <v>57727</v>
@@ -7092,13 +7077,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490056</v>
+        <v>490052</v>
       </c>
       <c r="R48" t="n">
-        <v>7004912</v>
+        <v>7004901</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7127,7 +7112,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7137,7 +7122,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7194,10 +7179,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129229015</v>
+        <v>129230142</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7205,37 +7190,47 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490105</v>
+        <v>490056</v>
       </c>
       <c r="R49" t="n">
-        <v>7004966</v>
+        <v>7004912</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7264,7 +7259,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7274,7 +7269,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7612,7 +7612,7 @@
         <v>129223831</v>
       </c>
       <c r="B52" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7745,38 +7745,52 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129226046</v>
+        <v>129226468</v>
       </c>
       <c r="B53" t="n">
-        <v>80185</v>
+        <v>98727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7785,10 +7799,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490078</v>
+        <v>490119</v>
       </c>
       <c r="R53" t="n">
-        <v>7004812</v>
+        <v>7004845</v>
       </c>
       <c r="S53" t="n">
         <v>11</v>
@@ -7820,7 +7834,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7830,12 +7844,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
+          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7850,26 +7864,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7890,7 +7884,7 @@
         <v>129231961</v>
       </c>
       <c r="B54" t="n">
-        <v>98641</v>
+        <v>98644</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -8009,52 +8003,38 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129226468</v>
+        <v>129226046</v>
       </c>
       <c r="B55" t="n">
-        <v>98724</v>
+        <v>80185</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -8063,10 +8043,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490119</v>
+        <v>490078</v>
       </c>
       <c r="R55" t="n">
-        <v>7004845</v>
+        <v>7004812</v>
       </c>
       <c r="S55" t="n">
         <v>11</v>
@@ -8098,7 +8078,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8108,12 +8088,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
+          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8128,6 +8108,26 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8439,48 +8439,67 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129223232</v>
+        <v>129225550</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490017</v>
+        <v>490157</v>
       </c>
       <c r="R58" t="n">
-        <v>7004780</v>
+        <v>7004793</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8509,7 +8528,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8519,7 +8538,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8534,26 +8558,6 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8571,67 +8575,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129225550</v>
+        <v>129223232</v>
       </c>
       <c r="B59" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490157</v>
+        <v>490017</v>
       </c>
       <c r="R59" t="n">
-        <v>7004793</v>
+        <v>7004780</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8660,7 +8645,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8670,12 +8655,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8690,6 +8670,26 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -954,7 +954,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129230003</v>
+        <v>129230622</v>
       </c>
       <c r="B4" t="n">
         <v>57727</v>
@@ -985,7 +985,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -999,13 +999,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490061</v>
+        <v>490077</v>
       </c>
       <c r="R4" t="n">
-        <v>7004922</v>
+        <v>7004897</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
+          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1101,7 +1101,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129230622</v>
+        <v>129230003</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1132,7 +1132,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1146,13 +1146,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490077</v>
+        <v>490061</v>
       </c>
       <c r="R5" t="n">
-        <v>7004897</v>
+        <v>7004922</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1384,10 +1384,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129223103</v>
+        <v>129224447</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,47 +1395,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489959</v>
+        <v>490020</v>
       </c>
       <c r="R7" t="n">
-        <v>7004819</v>
+        <v>7004694</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1464,7 +1454,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1474,12 +1464,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1508,12 +1493,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1531,47 +1516,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129226982</v>
+        <v>129223103</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1585,13 +1561,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490196</v>
+        <v>489959</v>
       </c>
       <c r="R8" t="n">
-        <v>7004884</v>
+        <v>7004819</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1620,7 +1596,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1630,12 +1606,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1650,6 +1626,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1667,7 +1663,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129226861</v>
+        <v>129226982</v>
       </c>
       <c r="B9" t="n">
         <v>98727</v>
@@ -1697,7 +1693,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1721,7 +1717,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490181</v>
+        <v>490196</v>
       </c>
       <c r="R9" t="n">
         <v>7004884</v>
@@ -1756,7 +1752,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1766,12 +1762,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1803,45 +1799,64 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129224447</v>
+        <v>129226861</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490020</v>
+        <v>490181</v>
       </c>
       <c r="R10" t="n">
-        <v>7004694</v>
+        <v>7004884</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1873,7 +1888,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1883,7 +1898,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1898,26 +1918,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1935,48 +1935,67 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129231117</v>
+        <v>129231914</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490037</v>
+        <v>489938</v>
       </c>
       <c r="R11" t="n">
-        <v>7004829</v>
+        <v>7004758</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2005,7 +2024,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2015,7 +2034,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2030,26 +2054,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2067,67 +2071,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129231914</v>
+        <v>129231117</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489938</v>
+        <v>490037</v>
       </c>
       <c r="R12" t="n">
-        <v>7004758</v>
+        <v>7004829</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2156,7 +2141,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2166,12 +2151,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2186,6 +2166,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2203,43 +2203,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129231535</v>
+        <v>129224667</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2248,10 +2252,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489991</v>
+        <v>490027</v>
       </c>
       <c r="R13" t="n">
-        <v>7004843</v>
+        <v>7004700</v>
       </c>
       <c r="S13" t="n">
         <v>8</v>
@@ -2283,7 +2287,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2293,12 +2297,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 250 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2313,26 +2317,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2350,7 +2334,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129230279</v>
+        <v>129231535</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2395,13 +2379,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490064</v>
+        <v>489991</v>
       </c>
       <c r="R14" t="n">
-        <v>7004903</v>
+        <v>7004843</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2430,7 +2414,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2440,7 +2424,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2497,7 +2481,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129230462</v>
+        <v>129230279</v>
       </c>
       <c r="B15" t="n">
         <v>57727</v>
@@ -2542,13 +2526,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490066</v>
+        <v>490064</v>
       </c>
       <c r="R15" t="n">
-        <v>7004896</v>
+        <v>7004903</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2577,7 +2561,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2587,12 +2571,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2644,7 +2628,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129230594</v>
+        <v>129230462</v>
       </c>
       <c r="B16" t="n">
         <v>57727</v>
@@ -2689,13 +2673,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490071</v>
+        <v>490066</v>
       </c>
       <c r="R16" t="n">
-        <v>7004887</v>
+        <v>7004896</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2724,7 +2708,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2734,7 +2718,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2791,47 +2775,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129224667</v>
+        <v>129230594</v>
       </c>
       <c r="B17" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2840,13 +2820,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490027</v>
+        <v>490071</v>
       </c>
       <c r="R17" t="n">
-        <v>7004700</v>
+        <v>7004887</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2875,7 +2855,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2885,12 +2865,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 250 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2905,6 +2885,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3490,45 +3490,64 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129230877</v>
+        <v>129225751</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490026</v>
+        <v>490094</v>
       </c>
       <c r="R22" t="n">
-        <v>7004861</v>
+        <v>7004803</v>
       </c>
       <c r="S22" t="n">
         <v>11</v>
@@ -3560,7 +3579,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3570,7 +3589,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3585,26 +3609,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3622,7 +3626,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129225751</v>
+        <v>129230745</v>
       </c>
       <c r="B23" t="n">
         <v>98727</v>
@@ -3652,7 +3656,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3676,10 +3680,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490094</v>
+        <v>490076</v>
       </c>
       <c r="R23" t="n">
-        <v>7004803</v>
+        <v>7004871</v>
       </c>
       <c r="S23" t="n">
         <v>11</v>
@@ -3711,7 +3715,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3721,12 +3725,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
+          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3758,64 +3762,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129230745</v>
+        <v>129230877</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490076</v>
+        <v>490026</v>
       </c>
       <c r="R24" t="n">
-        <v>7004871</v>
+        <v>7004861</v>
       </c>
       <c r="S24" t="n">
         <v>11</v>
@@ -3847,7 +3832,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3857,12 +3842,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3877,6 +3857,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3894,48 +3894,67 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129229156</v>
+        <v>129226592</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490069</v>
+        <v>490132</v>
       </c>
       <c r="R25" t="n">
-        <v>7004928</v>
+        <v>7004833</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3964,7 +3983,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3974,7 +3993,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3989,26 +4013,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4026,48 +4030,67 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129227087</v>
+        <v>129225418</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490187</v>
+        <v>490122</v>
       </c>
       <c r="R26" t="n">
-        <v>7004903</v>
+        <v>7004771</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4096,7 +4119,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4106,7 +4129,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4121,26 +4149,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4158,48 +4166,67 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129225967</v>
+        <v>129225602</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490095</v>
+        <v>490142</v>
       </c>
       <c r="R27" t="n">
-        <v>7004830</v>
+        <v>7004806</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4228,7 +4255,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4238,7 +4265,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4253,26 +4285,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4290,38 +4302,47 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129230367</v>
+        <v>129225165</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4335,10 +4356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490063</v>
+        <v>490124</v>
       </c>
       <c r="R28" t="n">
-        <v>7004901</v>
+        <v>7004767</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -4370,7 +4391,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4380,12 +4401,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4400,26 +4421,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4437,10 +4438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129230525</v>
+        <v>129229156</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4448,47 +4449,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490071</v>
+        <v>490069</v>
       </c>
       <c r="R29" t="n">
-        <v>7004894</v>
+        <v>7004928</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4517,7 +4508,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4527,12 +4518,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4561,12 +4547,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4584,67 +4570,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129226592</v>
+        <v>129227087</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490132</v>
+        <v>490187</v>
       </c>
       <c r="R30" t="n">
-        <v>7004833</v>
+        <v>7004903</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4673,7 +4640,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4683,12 +4650,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4703,6 +4665,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4720,67 +4702,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129225418</v>
+        <v>129225967</v>
       </c>
       <c r="B31" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490122</v>
+        <v>490095</v>
       </c>
       <c r="R31" t="n">
-        <v>7004771</v>
+        <v>7004830</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4809,7 +4772,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4819,12 +4782,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4839,6 +4797,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4856,47 +4834,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129225602</v>
+        <v>129230367</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4910,13 +4879,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490142</v>
+        <v>490063</v>
       </c>
       <c r="R32" t="n">
-        <v>7004806</v>
+        <v>7004901</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4945,7 +4914,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4955,12 +4924,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4975,6 +4944,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4992,47 +4981,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129225165</v>
+        <v>129230525</v>
       </c>
       <c r="B33" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5046,13 +5026,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490124</v>
+        <v>490071</v>
       </c>
       <c r="R33" t="n">
-        <v>7004767</v>
+        <v>7004894</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5081,7 +5061,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5091,12 +5071,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5111,6 +5091,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129224808</v>
+        <v>129223375</v>
       </c>
       <c r="B34" t="n">
-        <v>92271</v>
+        <v>80178</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5139,27 +5139,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5168,13 +5168,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490107</v>
+        <v>490028</v>
       </c>
       <c r="R34" t="n">
-        <v>7004741</v>
+        <v>7004796</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5232,22 +5232,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5265,53 +5265,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129223375</v>
+        <v>129227795</v>
       </c>
       <c r="B35" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490028</v>
+        <v>490175</v>
       </c>
       <c r="R35" t="n">
-        <v>7004796</v>
+        <v>7004918</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5340,7 +5335,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5350,7 +5345,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5369,22 +5369,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5402,45 +5402,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129227795</v>
+        <v>129224808</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>92271</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490175</v>
+        <v>490107</v>
       </c>
       <c r="R36" t="n">
-        <v>7004918</v>
+        <v>7004741</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -5472,7 +5477,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5482,12 +5487,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5516,12 +5516,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -6504,38 +6504,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129226789</v>
+        <v>129224339</v>
       </c>
       <c r="B44" t="n">
-        <v>92508</v>
+        <v>98727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6544,13 +6554,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490174</v>
+        <v>490008</v>
       </c>
       <c r="R44" t="n">
-        <v>7004879</v>
+        <v>7004696</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6579,7 +6589,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6589,7 +6599,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6603,7 +6618,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6621,48 +6636,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129224339</v>
+        <v>129226789</v>
       </c>
       <c r="B45" t="n">
-        <v>98727</v>
+        <v>92508</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6671,13 +6676,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490008</v>
+        <v>490174</v>
       </c>
       <c r="R45" t="n">
-        <v>7004696</v>
+        <v>7004879</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6706,7 +6711,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6716,12 +6721,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -7462,38 +7462,47 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129230834</v>
+        <v>129223831</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7507,13 +7516,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490020</v>
+        <v>490057</v>
       </c>
       <c r="R51" t="n">
-        <v>7004888</v>
+        <v>7004780</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7542,7 +7551,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7552,12 +7561,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
+          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7572,26 +7581,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7609,47 +7598,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129223831</v>
+        <v>129230834</v>
       </c>
       <c r="B52" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7663,13 +7643,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490057</v>
+        <v>490020</v>
       </c>
       <c r="R52" t="n">
-        <v>7004780</v>
+        <v>7004888</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7698,7 +7678,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7708,12 +7688,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7728,6 +7708,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7745,52 +7745,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129226468</v>
+        <v>129226046</v>
       </c>
       <c r="B53" t="n">
-        <v>98727</v>
+        <v>80185</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7799,10 +7785,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490119</v>
+        <v>490078</v>
       </c>
       <c r="R53" t="n">
-        <v>7004845</v>
+        <v>7004812</v>
       </c>
       <c r="S53" t="n">
         <v>11</v>
@@ -7834,7 +7820,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7844,12 +7830,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
+          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7864,6 +7850,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -8003,38 +8009,52 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129226046</v>
+        <v>129226468</v>
       </c>
       <c r="B55" t="n">
-        <v>80185</v>
+        <v>98727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -8043,10 +8063,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490078</v>
+        <v>490119</v>
       </c>
       <c r="R55" t="n">
-        <v>7004812</v>
+        <v>7004845</v>
       </c>
       <c r="S55" t="n">
         <v>11</v>
@@ -8078,7 +8098,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8088,12 +8108,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
+          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8108,26 +8128,6 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8145,38 +8145,47 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129222854</v>
+        <v>129225550</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -8190,10 +8199,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489942</v>
+        <v>490157</v>
       </c>
       <c r="R56" t="n">
-        <v>7004813</v>
+        <v>7004793</v>
       </c>
       <c r="S56" t="n">
         <v>8</v>
@@ -8225,7 +8234,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8235,12 +8244,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8255,26 +8264,6 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8292,7 +8281,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129230183</v>
+        <v>129222854</v>
       </c>
       <c r="B57" t="n">
         <v>57727</v>
@@ -8337,13 +8326,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490060</v>
+        <v>489942</v>
       </c>
       <c r="R57" t="n">
-        <v>7004914</v>
+        <v>7004813</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8372,7 +8361,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8382,12 +8371,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8439,67 +8428,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129225550</v>
+        <v>129223232</v>
       </c>
       <c r="B58" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490157</v>
+        <v>490017</v>
       </c>
       <c r="R58" t="n">
-        <v>7004793</v>
+        <v>7004780</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8528,7 +8498,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8538,12 +8508,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8558,6 +8523,26 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8575,10 +8560,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129223232</v>
+        <v>129230183</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8586,37 +8571,47 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490017</v>
+        <v>490060</v>
       </c>
       <c r="R59" t="n">
-        <v>7004780</v>
+        <v>7004914</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8645,7 +8640,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8655,7 +8650,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8684,12 +8684,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -954,7 +954,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129230622</v>
+        <v>129230003</v>
       </c>
       <c r="B4" t="n">
         <v>57727</v>
@@ -985,7 +985,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -999,13 +999,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490077</v>
+        <v>490061</v>
       </c>
       <c r="R4" t="n">
-        <v>7004897</v>
+        <v>7004922</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1101,7 +1101,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129230003</v>
+        <v>129230622</v>
       </c>
       <c r="B5" t="n">
         <v>57727</v>
@@ -1132,7 +1132,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1146,13 +1146,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490061</v>
+        <v>490077</v>
       </c>
       <c r="R5" t="n">
-        <v>7004922</v>
+        <v>7004897</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
+          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2203,47 +2203,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129224667</v>
+        <v>129231535</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2252,10 +2248,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490027</v>
+        <v>489991</v>
       </c>
       <c r="R13" t="n">
-        <v>7004700</v>
+        <v>7004843</v>
       </c>
       <c r="S13" t="n">
         <v>8</v>
@@ -2287,7 +2283,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2297,12 +2293,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 250 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2317,6 +2313,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2334,7 +2350,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129231535</v>
+        <v>129230279</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2379,13 +2395,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489991</v>
+        <v>490064</v>
       </c>
       <c r="R14" t="n">
-        <v>7004843</v>
+        <v>7004903</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2414,7 +2430,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2424,7 +2440,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2481,7 +2497,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129230279</v>
+        <v>129230462</v>
       </c>
       <c r="B15" t="n">
         <v>57727</v>
@@ -2526,13 +2542,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490064</v>
+        <v>490066</v>
       </c>
       <c r="R15" t="n">
-        <v>7004903</v>
+        <v>7004896</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2561,7 +2577,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2571,12 +2587,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2628,7 +2644,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129230462</v>
+        <v>129230594</v>
       </c>
       <c r="B16" t="n">
         <v>57727</v>
@@ -2673,13 +2689,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490066</v>
+        <v>490071</v>
       </c>
       <c r="R16" t="n">
-        <v>7004896</v>
+        <v>7004887</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2708,7 +2724,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2718,7 +2734,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2775,43 +2791,47 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129230594</v>
+        <v>129224667</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2820,13 +2840,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490071</v>
+        <v>490027</v>
       </c>
       <c r="R17" t="n">
-        <v>7004887</v>
+        <v>7004700</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2855,7 +2875,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2865,12 +2885,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Minst 250 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2885,26 +2905,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3064,43 +3064,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129229350</v>
+        <v>129230997</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3109,13 +3104,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490080</v>
+        <v>490022</v>
       </c>
       <c r="R19" t="n">
-        <v>7004934</v>
+        <v>7004859</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3144,7 +3139,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3154,12 +3149,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, färska (2025), i riklig mängd längs flera meter på en gran vid en hyggeskant. Granen är gräns-snitslad för en planerad avverning.</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3178,22 +3168,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3211,38 +3201,43 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129230997</v>
+        <v>129229350</v>
       </c>
       <c r="B20" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3251,13 +3246,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490022</v>
+        <v>490080</v>
       </c>
       <c r="R20" t="n">
-        <v>7004859</v>
+        <v>7004934</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3286,7 +3281,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3296,7 +3291,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, färska (2025), i riklig mängd längs flera meter på en gran vid en hyggeskant. Granen är gräns-snitslad för en planerad avverning.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3315,22 +3315,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3490,64 +3490,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129225751</v>
+        <v>129230877</v>
       </c>
       <c r="B22" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490094</v>
+        <v>490026</v>
       </c>
       <c r="R22" t="n">
-        <v>7004803</v>
+        <v>7004861</v>
       </c>
       <c r="S22" t="n">
         <v>11</v>
@@ -3579,7 +3560,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3589,12 +3570,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3609,6 +3585,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3626,7 +3622,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129230745</v>
+        <v>129225751</v>
       </c>
       <c r="B23" t="n">
         <v>98727</v>
@@ -3656,7 +3652,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3680,10 +3676,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490076</v>
+        <v>490094</v>
       </c>
       <c r="R23" t="n">
-        <v>7004871</v>
+        <v>7004803</v>
       </c>
       <c r="S23" t="n">
         <v>11</v>
@@ -3715,7 +3711,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3725,12 +3721,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3762,45 +3758,64 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129230877</v>
+        <v>129230745</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490026</v>
+        <v>490076</v>
       </c>
       <c r="R24" t="n">
-        <v>7004861</v>
+        <v>7004871</v>
       </c>
       <c r="S24" t="n">
         <v>11</v>
@@ -3832,7 +3847,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3842,7 +3857,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3857,26 +3877,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -4438,10 +4438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129229156</v>
+        <v>129230367</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4449,37 +4449,47 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490069</v>
+        <v>490063</v>
       </c>
       <c r="R29" t="n">
-        <v>7004928</v>
+        <v>7004901</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4508,7 +4518,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4518,7 +4528,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4547,12 +4562,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4570,10 +4585,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129227087</v>
+        <v>129230525</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4581,37 +4596,47 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490187</v>
+        <v>490071</v>
       </c>
       <c r="R30" t="n">
-        <v>7004903</v>
+        <v>7004894</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4640,7 +4665,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4650,7 +4675,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4679,12 +4709,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4702,7 +4732,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129225967</v>
+        <v>129229156</v>
       </c>
       <c r="B31" t="n">
         <v>79044</v>
@@ -4737,13 +4767,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490095</v>
+        <v>490069</v>
       </c>
       <c r="R31" t="n">
-        <v>7004830</v>
+        <v>7004928</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4772,7 +4802,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4782,7 +4812,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4811,12 +4841,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4834,10 +4864,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129230367</v>
+        <v>129227087</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4845,44 +4875,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490063</v>
+        <v>490187</v>
       </c>
       <c r="R32" t="n">
-        <v>7004901</v>
+        <v>7004903</v>
       </c>
       <c r="S32" t="n">
         <v>9</v>
@@ -4914,7 +4934,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4924,12 +4944,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4958,12 +4973,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4981,10 +4996,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129230525</v>
+        <v>129225967</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4992,47 +5007,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490071</v>
+        <v>490095</v>
       </c>
       <c r="R33" t="n">
-        <v>7004894</v>
+        <v>7004830</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5061,7 +5066,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5071,12 +5076,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5128,10 +5128,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129223375</v>
+        <v>129224808</v>
       </c>
       <c r="B34" t="n">
-        <v>80178</v>
+        <v>92271</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5139,27 +5139,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5168,13 +5168,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490028</v>
+        <v>490107</v>
       </c>
       <c r="R34" t="n">
-        <v>7004796</v>
+        <v>7004741</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5232,22 +5232,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5265,48 +5265,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129227795</v>
+        <v>129223375</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490175</v>
+        <v>490028</v>
       </c>
       <c r="R35" t="n">
-        <v>7004918</v>
+        <v>7004796</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5335,7 +5340,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5345,12 +5350,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5369,22 +5369,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5402,50 +5402,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129224808</v>
+        <v>129227795</v>
       </c>
       <c r="B36" t="n">
-        <v>92271</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490107</v>
+        <v>490175</v>
       </c>
       <c r="R36" t="n">
-        <v>7004741</v>
+        <v>7004918</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -5477,7 +5472,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5487,7 +5482,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5516,12 +5516,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -6504,48 +6504,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129224339</v>
+        <v>129226789</v>
       </c>
       <c r="B44" t="n">
-        <v>98727</v>
+        <v>92508</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6554,13 +6544,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490008</v>
+        <v>490174</v>
       </c>
       <c r="R44" t="n">
-        <v>7004696</v>
+        <v>7004879</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6589,7 +6579,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6599,12 +6589,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6618,7 +6603,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6636,38 +6621,43 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129226789</v>
+        <v>129229897</v>
       </c>
       <c r="B45" t="n">
-        <v>92508</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6676,13 +6666,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490174</v>
+        <v>490072</v>
       </c>
       <c r="R45" t="n">
-        <v>7004879</v>
+        <v>7004920</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6711,7 +6701,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6721,7 +6711,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6735,7 +6730,27 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6753,38 +6768,43 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129229897</v>
+        <v>129224339</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6798,13 +6818,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490072</v>
+        <v>490008</v>
       </c>
       <c r="R46" t="n">
-        <v>7004920</v>
+        <v>7004696</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6833,7 +6853,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6843,12 +6863,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6863,26 +6883,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6900,10 +6900,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129229015</v>
+        <v>129230332</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6911,37 +6911,47 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490105</v>
+        <v>490052</v>
       </c>
       <c r="R47" t="n">
-        <v>7004966</v>
+        <v>7004901</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6970,7 +6980,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6980,7 +6990,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6994,7 +7009,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -7009,12 +7024,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7032,7 +7047,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129230332</v>
+        <v>129230142</v>
       </c>
       <c r="B48" t="n">
         <v>57727</v>
@@ -7077,13 +7092,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490052</v>
+        <v>490056</v>
       </c>
       <c r="R48" t="n">
-        <v>7004901</v>
+        <v>7004912</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7112,7 +7127,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7122,7 +7137,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7179,10 +7194,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129230142</v>
+        <v>129229015</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7190,47 +7205,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490056</v>
+        <v>490105</v>
       </c>
       <c r="R49" t="n">
-        <v>7004912</v>
+        <v>7004966</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7259,7 +7264,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7269,12 +7274,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7462,47 +7462,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129223831</v>
+        <v>129230834</v>
       </c>
       <c r="B51" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7516,13 +7507,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490057</v>
+        <v>490020</v>
       </c>
       <c r="R51" t="n">
-        <v>7004780</v>
+        <v>7004888</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7551,7 +7542,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7561,12 +7552,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7581,6 +7572,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7598,38 +7609,47 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129230834</v>
+        <v>129223831</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7643,13 +7663,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490020</v>
+        <v>490057</v>
       </c>
       <c r="R52" t="n">
-        <v>7004888</v>
+        <v>7004780</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7678,7 +7698,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7688,12 +7708,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
+          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7708,26 +7728,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7745,10 +7745,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129226046</v>
+        <v>129231961</v>
       </c>
       <c r="B53" t="n">
-        <v>80185</v>
+        <v>98644</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7756,27 +7756,32 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>219790</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7785,13 +7790,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490078</v>
+        <v>489928</v>
       </c>
       <c r="R53" t="n">
-        <v>7004812</v>
+        <v>7004745</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7820,7 +7825,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7830,12 +7835,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7850,26 +7850,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7887,38 +7867,47 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129231961</v>
+        <v>129226468</v>
       </c>
       <c r="B54" t="n">
-        <v>98644</v>
+        <v>98727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7932,13 +7921,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489928</v>
+        <v>490119</v>
       </c>
       <c r="R54" t="n">
-        <v>7004745</v>
+        <v>7004845</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7967,7 +7956,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7977,7 +7966,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8009,52 +8003,38 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129226468</v>
+        <v>129226046</v>
       </c>
       <c r="B55" t="n">
-        <v>98727</v>
+        <v>80185</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -8063,10 +8043,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490119</v>
+        <v>490078</v>
       </c>
       <c r="R55" t="n">
-        <v>7004845</v>
+        <v>7004812</v>
       </c>
       <c r="S55" t="n">
         <v>11</v>
@@ -8098,7 +8078,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8108,12 +8088,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
+          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8128,6 +8108,26 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8145,67 +8145,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129225550</v>
+        <v>129223232</v>
       </c>
       <c r="B56" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490157</v>
+        <v>490017</v>
       </c>
       <c r="R56" t="n">
-        <v>7004793</v>
+        <v>7004780</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8234,7 +8215,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8244,12 +8225,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8264,6 +8240,26 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8428,10 +8424,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129223232</v>
+        <v>129230183</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8439,37 +8435,47 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490017</v>
+        <v>490060</v>
       </c>
       <c r="R58" t="n">
-        <v>7004780</v>
+        <v>7004914</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8498,7 +8504,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8508,7 +8514,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8537,12 +8548,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8560,38 +8571,47 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129230183</v>
+        <v>129225550</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8605,13 +8625,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490060</v>
+        <v>490157</v>
       </c>
       <c r="R59" t="n">
-        <v>7004914</v>
+        <v>7004793</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8640,7 +8660,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8650,12 +8670,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8670,26 +8690,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -1516,38 +1516,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129223103</v>
+        <v>129226982</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1561,13 +1570,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489959</v>
+        <v>490196</v>
       </c>
       <c r="R8" t="n">
-        <v>7004819</v>
+        <v>7004884</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1596,7 +1605,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1606,12 +1615,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1626,26 +1635,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1663,7 +1652,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129226982</v>
+        <v>129226861</v>
       </c>
       <c r="B9" t="n">
         <v>98727</v>
@@ -1693,7 +1682,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1717,7 +1706,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490196</v>
+        <v>490181</v>
       </c>
       <c r="R9" t="n">
         <v>7004884</v>
@@ -1752,7 +1741,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1762,12 +1751,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1799,47 +1788,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129226861</v>
+        <v>129223103</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1853,13 +1833,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490181</v>
+        <v>489959</v>
       </c>
       <c r="R10" t="n">
-        <v>7004884</v>
+        <v>7004819</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1888,7 +1868,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1898,12 +1878,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1918,6 +1898,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1935,67 +1935,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129231914</v>
+        <v>129231117</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489938</v>
+        <v>490037</v>
       </c>
       <c r="R11" t="n">
-        <v>7004758</v>
+        <v>7004829</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2024,7 +2005,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2034,12 +2015,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2054,6 +2030,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2071,48 +2067,67 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129231117</v>
+        <v>129231914</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490037</v>
+        <v>489938</v>
       </c>
       <c r="R12" t="n">
-        <v>7004829</v>
+        <v>7004758</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2141,7 +2156,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2151,7 +2166,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2166,26 +2186,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2203,7 +2203,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129231535</v>
+        <v>129230279</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -2248,13 +2248,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489991</v>
+        <v>490064</v>
       </c>
       <c r="R13" t="n">
-        <v>7004843</v>
+        <v>7004903</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2350,7 +2350,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129230279</v>
+        <v>129230594</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490064</v>
+        <v>490071</v>
       </c>
       <c r="R14" t="n">
-        <v>7004903</v>
+        <v>7004887</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2644,7 +2644,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129230594</v>
+        <v>129231535</v>
       </c>
       <c r="B16" t="n">
         <v>57727</v>
@@ -2689,13 +2689,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490071</v>
+        <v>489991</v>
       </c>
       <c r="R16" t="n">
-        <v>7004887</v>
+        <v>7004843</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3064,38 +3064,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129230997</v>
+        <v>129229350</v>
       </c>
       <c r="B19" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3104,13 +3109,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490022</v>
+        <v>490080</v>
       </c>
       <c r="R19" t="n">
-        <v>7004859</v>
+        <v>7004934</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3139,7 +3144,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3149,7 +3154,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, färska (2025), i riklig mängd längs flera meter på en gran vid en hyggeskant. Granen är gräns-snitslad för en planerad avverning.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3168,22 +3178,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3201,43 +3211,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129229350</v>
+        <v>129230997</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3246,13 +3251,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490080</v>
+        <v>490022</v>
       </c>
       <c r="R20" t="n">
-        <v>7004934</v>
+        <v>7004859</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3281,7 +3286,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3291,12 +3296,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, färska (2025), i riklig mängd längs flera meter på en gran vid en hyggeskant. Granen är gräns-snitslad för en planerad avverning.</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3315,22 +3315,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3490,45 +3490,64 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129230877</v>
+        <v>129225751</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490026</v>
+        <v>490094</v>
       </c>
       <c r="R22" t="n">
-        <v>7004861</v>
+        <v>7004803</v>
       </c>
       <c r="S22" t="n">
         <v>11</v>
@@ -3560,7 +3579,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3570,7 +3589,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3585,26 +3609,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3622,7 +3626,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129225751</v>
+        <v>129230745</v>
       </c>
       <c r="B23" t="n">
         <v>98727</v>
@@ -3652,7 +3656,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3676,10 +3680,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490094</v>
+        <v>490076</v>
       </c>
       <c r="R23" t="n">
-        <v>7004803</v>
+        <v>7004871</v>
       </c>
       <c r="S23" t="n">
         <v>11</v>
@@ -3711,7 +3715,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3721,12 +3725,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
+          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3758,64 +3762,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129230745</v>
+        <v>129230877</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490076</v>
+        <v>490026</v>
       </c>
       <c r="R24" t="n">
-        <v>7004871</v>
+        <v>7004861</v>
       </c>
       <c r="S24" t="n">
         <v>11</v>
@@ -3847,7 +3832,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3857,12 +3842,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3877,6 +3857,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3894,67 +3894,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129226592</v>
+        <v>129229156</v>
       </c>
       <c r="B25" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490132</v>
+        <v>490069</v>
       </c>
       <c r="R25" t="n">
-        <v>7004833</v>
+        <v>7004928</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3983,7 +3964,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3993,12 +3974,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4013,6 +3989,26 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4030,67 +4026,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129225418</v>
+        <v>129227087</v>
       </c>
       <c r="B26" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490122</v>
+        <v>490187</v>
       </c>
       <c r="R26" t="n">
-        <v>7004771</v>
+        <v>7004903</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4119,7 +4096,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4129,12 +4106,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4149,6 +4121,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4166,67 +4158,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129225602</v>
+        <v>129225967</v>
       </c>
       <c r="B27" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490142</v>
+        <v>490095</v>
       </c>
       <c r="R27" t="n">
-        <v>7004806</v>
+        <v>7004830</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4255,7 +4228,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4265,12 +4238,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4285,6 +4253,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4302,47 +4290,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129225165</v>
+        <v>129230367</v>
       </c>
       <c r="B28" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4356,10 +4335,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490124</v>
+        <v>490063</v>
       </c>
       <c r="R28" t="n">
-        <v>7004767</v>
+        <v>7004901</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -4391,7 +4370,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4401,12 +4380,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4421,6 +4400,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4438,7 +4437,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129230367</v>
+        <v>129230525</v>
       </c>
       <c r="B29" t="n">
         <v>57727</v>
@@ -4483,13 +4482,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490063</v>
+        <v>490071</v>
       </c>
       <c r="R29" t="n">
-        <v>7004901</v>
+        <v>7004894</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4518,7 +4517,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4528,12 +4527,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4585,38 +4584,47 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129230525</v>
+        <v>129226592</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4630,13 +4638,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490071</v>
+        <v>490132</v>
       </c>
       <c r="R30" t="n">
-        <v>7004894</v>
+        <v>7004833</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4665,7 +4673,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4675,12 +4683,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4695,26 +4703,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4732,48 +4720,67 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129229156</v>
+        <v>129225418</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490069</v>
+        <v>490122</v>
       </c>
       <c r="R31" t="n">
-        <v>7004928</v>
+        <v>7004771</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4802,7 +4809,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4812,7 +4819,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4827,26 +4839,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4864,48 +4856,67 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129227087</v>
+        <v>129225602</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490187</v>
+        <v>490142</v>
       </c>
       <c r="R32" t="n">
-        <v>7004903</v>
+        <v>7004806</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4934,7 +4945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4944,7 +4955,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4959,26 +4975,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4996,48 +4992,67 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129225967</v>
+        <v>129225165</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490095</v>
+        <v>490124</v>
       </c>
       <c r="R33" t="n">
-        <v>7004830</v>
+        <v>7004767</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5066,7 +5081,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5076,7 +5091,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5091,26 +5111,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5128,38 +5128,52 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129224808</v>
+        <v>129228038</v>
       </c>
       <c r="B34" t="n">
-        <v>92271</v>
+        <v>98727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5168,13 +5182,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490107</v>
+        <v>490161</v>
       </c>
       <c r="R34" t="n">
-        <v>7004741</v>
+        <v>7004940</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5203,7 +5217,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5213,7 +5227,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5227,27 +5246,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5539,52 +5538,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129228038</v>
+        <v>129224808</v>
       </c>
       <c r="B37" t="n">
-        <v>98727</v>
+        <v>92271</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5593,13 +5578,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490161</v>
+        <v>490107</v>
       </c>
       <c r="R37" t="n">
-        <v>7004940</v>
+        <v>7004741</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5628,7 +5613,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5638,12 +5623,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5657,7 +5637,27 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -6900,7 +6900,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129230332</v>
+        <v>129230142</v>
       </c>
       <c r="B47" t="n">
         <v>57727</v>
@@ -6945,13 +6945,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490052</v>
+        <v>490056</v>
       </c>
       <c r="R47" t="n">
-        <v>7004901</v>
+        <v>7004912</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -7047,7 +7047,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129230142</v>
+        <v>129230332</v>
       </c>
       <c r="B48" t="n">
         <v>57727</v>
@@ -7092,13 +7092,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490056</v>
+        <v>490052</v>
       </c>
       <c r="R48" t="n">
-        <v>7004912</v>
+        <v>7004901</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -7194,10 +7194,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129229015</v>
+        <v>129223439</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7205,37 +7205,56 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490105</v>
+        <v>490044</v>
       </c>
       <c r="R49" t="n">
-        <v>7004966</v>
+        <v>7004789</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7264,7 +7283,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7274,7 +7293,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7288,27 +7312,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7326,10 +7330,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129223439</v>
+        <v>129229015</v>
       </c>
       <c r="B50" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7337,56 +7341,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490044</v>
+        <v>490105</v>
       </c>
       <c r="R50" t="n">
-        <v>7004789</v>
+        <v>7004966</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7415,7 +7400,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7425,12 +7410,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7444,7 +7424,27 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7462,38 +7462,47 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129230834</v>
+        <v>129223831</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7507,13 +7516,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490020</v>
+        <v>490057</v>
       </c>
       <c r="R51" t="n">
-        <v>7004888</v>
+        <v>7004780</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7542,7 +7551,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7552,12 +7561,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
+          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7572,26 +7581,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7609,47 +7598,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129223831</v>
+        <v>129230834</v>
       </c>
       <c r="B52" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7663,13 +7643,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490057</v>
+        <v>490020</v>
       </c>
       <c r="R52" t="n">
-        <v>7004780</v>
+        <v>7004888</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7698,7 +7678,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7708,12 +7688,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7728,6 +7708,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -8277,7 +8277,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129222854</v>
+        <v>129230183</v>
       </c>
       <c r="B57" t="n">
         <v>57727</v>
@@ -8322,13 +8322,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489942</v>
+        <v>490060</v>
       </c>
       <c r="R57" t="n">
-        <v>7004813</v>
+        <v>7004914</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8367,12 +8367,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8424,7 +8424,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129230183</v>
+        <v>129222854</v>
       </c>
       <c r="B58" t="n">
         <v>57727</v>
@@ -8469,13 +8469,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490060</v>
+        <v>489942</v>
       </c>
       <c r="R58" t="n">
-        <v>7004914</v>
+        <v>7004813</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -1384,10 +1384,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129224447</v>
+        <v>129223103</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,37 +1395,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490020</v>
+        <v>489959</v>
       </c>
       <c r="R7" t="n">
-        <v>7004694</v>
+        <v>7004819</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1454,7 +1464,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1464,7 +1474,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1493,12 +1508,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1516,64 +1531,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129226982</v>
+        <v>129224447</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490196</v>
+        <v>490020</v>
       </c>
       <c r="R8" t="n">
-        <v>7004884</v>
+        <v>7004694</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1605,7 +1601,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1615,12 +1611,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1635,6 +1626,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1652,7 +1663,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129226861</v>
+        <v>129226982</v>
       </c>
       <c r="B9" t="n">
         <v>98727</v>
@@ -1682,7 +1693,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1706,7 +1717,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490181</v>
+        <v>490196</v>
       </c>
       <c r="R9" t="n">
         <v>7004884</v>
@@ -1741,7 +1752,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1751,12 +1762,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1788,38 +1799,47 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129223103</v>
+        <v>129226861</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1833,13 +1853,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489959</v>
+        <v>490181</v>
       </c>
       <c r="R10" t="n">
-        <v>7004819</v>
+        <v>7004884</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1868,7 +1888,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1878,12 +1898,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1898,26 +1918,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2203,7 +2203,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129230279</v>
+        <v>129231535</v>
       </c>
       <c r="B13" t="n">
         <v>57727</v>
@@ -2248,13 +2248,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490064</v>
+        <v>489991</v>
       </c>
       <c r="R13" t="n">
-        <v>7004903</v>
+        <v>7004843</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2350,7 +2350,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129230594</v>
+        <v>129230279</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490071</v>
+        <v>490064</v>
       </c>
       <c r="R14" t="n">
-        <v>7004887</v>
+        <v>7004903</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2644,7 +2644,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129231535</v>
+        <v>129230594</v>
       </c>
       <c r="B16" t="n">
         <v>57727</v>
@@ -2689,13 +2689,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>489991</v>
+        <v>490071</v>
       </c>
       <c r="R16" t="n">
-        <v>7004843</v>
+        <v>7004887</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3064,43 +3064,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129229350</v>
+        <v>129230997</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>80178</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3109,13 +3104,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>490080</v>
+        <v>490022</v>
       </c>
       <c r="R19" t="n">
-        <v>7004934</v>
+        <v>7004859</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3144,7 +3139,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3154,12 +3149,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, färska (2025), i riklig mängd längs flera meter på en gran vid en hyggeskant. Granen är gräns-snitslad för en planerad avverning.</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3178,22 +3168,22 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3211,38 +3201,43 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129230997</v>
+        <v>129229350</v>
       </c>
       <c r="B20" t="n">
-        <v>80178</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3251,13 +3246,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490022</v>
+        <v>490080</v>
       </c>
       <c r="R20" t="n">
-        <v>7004859</v>
+        <v>7004934</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3286,7 +3281,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3296,7 +3291,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, färska (2025), i riklig mängd längs flera meter på en gran vid en hyggeskant. Granen är gräns-snitslad för en planerad avverning.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3315,22 +3315,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3490,64 +3490,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129225751</v>
+        <v>129230877</v>
       </c>
       <c r="B22" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490094</v>
+        <v>490026</v>
       </c>
       <c r="R22" t="n">
-        <v>7004803</v>
+        <v>7004861</v>
       </c>
       <c r="S22" t="n">
         <v>11</v>
@@ -3579,7 +3560,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3589,12 +3570,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3609,6 +3585,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3626,7 +3622,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129230745</v>
+        <v>129225751</v>
       </c>
       <c r="B23" t="n">
         <v>98727</v>
@@ -3656,7 +3652,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3680,10 +3676,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490076</v>
+        <v>490094</v>
       </c>
       <c r="R23" t="n">
-        <v>7004871</v>
+        <v>7004803</v>
       </c>
       <c r="S23" t="n">
         <v>11</v>
@@ -3715,7 +3711,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3725,12 +3721,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3762,45 +3758,64 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129230877</v>
+        <v>129230745</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490026</v>
+        <v>490076</v>
       </c>
       <c r="R24" t="n">
-        <v>7004861</v>
+        <v>7004871</v>
       </c>
       <c r="S24" t="n">
         <v>11</v>
@@ -3832,7 +3847,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3842,7 +3857,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3857,26 +3877,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3894,48 +3894,67 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129229156</v>
+        <v>129226592</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490069</v>
+        <v>490132</v>
       </c>
       <c r="R25" t="n">
-        <v>7004928</v>
+        <v>7004833</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3964,7 +3983,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3974,7 +3993,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3989,26 +4013,6 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4026,48 +4030,67 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129227087</v>
+        <v>129225418</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490187</v>
+        <v>490122</v>
       </c>
       <c r="R26" t="n">
-        <v>7004903</v>
+        <v>7004771</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4096,7 +4119,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4106,7 +4129,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4121,26 +4149,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4158,48 +4166,67 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129225967</v>
+        <v>129225602</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490095</v>
+        <v>490142</v>
       </c>
       <c r="R27" t="n">
-        <v>7004830</v>
+        <v>7004806</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4228,7 +4255,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4238,7 +4265,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4253,26 +4285,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4290,38 +4302,47 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129230367</v>
+        <v>129225165</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4335,10 +4356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490063</v>
+        <v>490124</v>
       </c>
       <c r="R28" t="n">
-        <v>7004901</v>
+        <v>7004767</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -4370,7 +4391,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4380,12 +4401,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4400,26 +4421,6 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4437,10 +4438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129230525</v>
+        <v>129229156</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4448,47 +4449,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490071</v>
+        <v>490069</v>
       </c>
       <c r="R29" t="n">
-        <v>7004894</v>
+        <v>7004928</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4517,7 +4508,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4527,12 +4518,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4561,12 +4547,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4584,47 +4570,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129226592</v>
+        <v>129230367</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4638,13 +4615,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490132</v>
+        <v>490063</v>
       </c>
       <c r="R30" t="n">
-        <v>7004833</v>
+        <v>7004901</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4673,7 +4650,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4683,12 +4660,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4703,6 +4680,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4720,47 +4717,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129225418</v>
+        <v>129230525</v>
       </c>
       <c r="B31" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4774,10 +4762,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490122</v>
+        <v>490071</v>
       </c>
       <c r="R31" t="n">
-        <v>7004771</v>
+        <v>7004894</v>
       </c>
       <c r="S31" t="n">
         <v>8</v>
@@ -4809,7 +4797,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4819,12 +4807,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4839,6 +4827,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4856,67 +4864,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129225602</v>
+        <v>129227087</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490142</v>
+        <v>490187</v>
       </c>
       <c r="R32" t="n">
-        <v>7004806</v>
+        <v>7004903</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4945,7 +4934,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4955,12 +4944,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4975,6 +4959,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4992,67 +4996,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129225165</v>
+        <v>129225967</v>
       </c>
       <c r="B33" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490124</v>
+        <v>490095</v>
       </c>
       <c r="R33" t="n">
-        <v>7004767</v>
+        <v>7004830</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5081,7 +5066,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5091,12 +5076,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5111,6 +5091,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5128,52 +5128,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129228038</v>
+        <v>129224808</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>92271</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5182,13 +5168,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490161</v>
+        <v>490107</v>
       </c>
       <c r="R34" t="n">
-        <v>7004940</v>
+        <v>7004741</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5217,7 +5203,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5227,12 +5213,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5246,7 +5227,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5264,53 +5265,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129223375</v>
+        <v>129227795</v>
       </c>
       <c r="B35" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490028</v>
+        <v>490175</v>
       </c>
       <c r="R35" t="n">
-        <v>7004796</v>
+        <v>7004918</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5339,7 +5335,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5349,7 +5345,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5368,22 +5369,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5401,48 +5402,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129227795</v>
+        <v>129223375</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490175</v>
+        <v>490028</v>
       </c>
       <c r="R36" t="n">
-        <v>7004918</v>
+        <v>7004796</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5471,7 +5477,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5481,12 +5487,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5505,22 +5506,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5538,38 +5539,52 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129224808</v>
+        <v>129228038</v>
       </c>
       <c r="B37" t="n">
-        <v>92271</v>
+        <v>98727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5578,13 +5593,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490107</v>
+        <v>490161</v>
       </c>
       <c r="R37" t="n">
-        <v>7004741</v>
+        <v>7004940</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5613,7 +5628,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5623,7 +5638,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5637,27 +5657,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5675,38 +5675,52 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129231240</v>
+        <v>129223986</v>
       </c>
       <c r="B38" t="n">
-        <v>80178</v>
+        <v>98727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5715,13 +5729,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490033</v>
+        <v>490070</v>
       </c>
       <c r="R38" t="n">
-        <v>7004823</v>
+        <v>7004763</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5750,7 +5764,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5760,7 +5774,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 22 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5775,26 +5794,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5812,52 +5811,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129223986</v>
+        <v>129231240</v>
       </c>
       <c r="B39" t="n">
-        <v>98727</v>
+        <v>80178</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5866,13 +5851,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490070</v>
+        <v>490033</v>
       </c>
       <c r="R39" t="n">
-        <v>7004763</v>
+        <v>7004823</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5901,7 +5886,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5911,12 +5896,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Minst 22 plantor inom ca 1 m2 yta.</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5931,6 +5911,26 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5948,38 +5948,52 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129230966</v>
+        <v>129223203</v>
       </c>
       <c r="B40" t="n">
-        <v>80149</v>
+        <v>98727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5988,10 +6002,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>490020</v>
+        <v>489995</v>
       </c>
       <c r="R40" t="n">
-        <v>7004857</v>
+        <v>7004788</v>
       </c>
       <c r="S40" t="n">
         <v>9</v>
@@ -6023,7 +6037,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6033,7 +6047,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6048,26 +6067,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6085,7 +6084,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129223203</v>
+        <v>129227281</v>
       </c>
       <c r="B41" t="n">
         <v>98727</v>
@@ -6115,7 +6114,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6139,13 +6138,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>489995</v>
+        <v>490162</v>
       </c>
       <c r="R41" t="n">
-        <v>7004788</v>
+        <v>7004880</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6174,7 +6173,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6184,12 +6183,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 16 plantor inom ca 2 m2 yta intill en tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6221,52 +6220,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129227281</v>
+        <v>129230966</v>
       </c>
       <c r="B42" t="n">
-        <v>98727</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -6275,13 +6260,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490162</v>
+        <v>490020</v>
       </c>
       <c r="R42" t="n">
-        <v>7004880</v>
+        <v>7004857</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6310,7 +6295,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6320,12 +6305,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Minst 16 plantor inom ca 2 m2 yta intill en tall.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6340,6 +6320,26 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6504,38 +6504,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129226789</v>
+        <v>129224339</v>
       </c>
       <c r="B44" t="n">
-        <v>92508</v>
+        <v>98727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6544,13 +6554,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490174</v>
+        <v>490008</v>
       </c>
       <c r="R44" t="n">
-        <v>7004879</v>
+        <v>7004696</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6579,7 +6589,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6589,7 +6599,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6603,7 +6618,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6768,48 +6783,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129224339</v>
+        <v>129226789</v>
       </c>
       <c r="B46" t="n">
-        <v>98727</v>
+        <v>92508</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6818,13 +6823,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490008</v>
+        <v>490174</v>
       </c>
       <c r="R46" t="n">
-        <v>7004696</v>
+        <v>7004879</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6853,7 +6858,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6863,12 +6868,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6900,10 +6900,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129230142</v>
+        <v>129229015</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6911,47 +6911,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490056</v>
+        <v>490105</v>
       </c>
       <c r="R47" t="n">
-        <v>7004912</v>
+        <v>7004966</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6980,7 +6970,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6990,12 +6980,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7009,7 +6994,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -7024,12 +7009,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7194,10 +7179,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129223439</v>
+        <v>129230142</v>
       </c>
       <c r="B49" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7205,36 +7190,27 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -7248,13 +7224,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490044</v>
+        <v>490056</v>
       </c>
       <c r="R49" t="n">
-        <v>7004789</v>
+        <v>7004912</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7283,7 +7259,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7293,12 +7269,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7313,6 +7289,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7330,10 +7326,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129229015</v>
+        <v>129223439</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7341,37 +7337,56 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490105</v>
+        <v>490044</v>
       </c>
       <c r="R50" t="n">
-        <v>7004966</v>
+        <v>7004789</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7400,7 +7415,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7410,7 +7425,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7424,27 +7444,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7462,47 +7462,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129223831</v>
+        <v>129230834</v>
       </c>
       <c r="B51" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7516,13 +7507,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490057</v>
+        <v>490020</v>
       </c>
       <c r="R51" t="n">
-        <v>7004780</v>
+        <v>7004888</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7551,7 +7542,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7561,12 +7552,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7581,6 +7572,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7598,38 +7609,47 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129230834</v>
+        <v>129223831</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7643,13 +7663,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490020</v>
+        <v>490057</v>
       </c>
       <c r="R52" t="n">
-        <v>7004888</v>
+        <v>7004780</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7678,7 +7698,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7688,12 +7708,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
+          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7708,26 +7728,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7745,38 +7745,47 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129231961</v>
+        <v>129226468</v>
       </c>
       <c r="B53" t="n">
-        <v>98644</v>
+        <v>98727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7790,13 +7799,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>489928</v>
+        <v>490119</v>
       </c>
       <c r="R53" t="n">
-        <v>7004745</v>
+        <v>7004845</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7825,7 +7834,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7835,7 +7844,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7867,52 +7881,38 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129226468</v>
+        <v>129226046</v>
       </c>
       <c r="B54" t="n">
-        <v>98727</v>
+        <v>80185</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490119</v>
+        <v>490078</v>
       </c>
       <c r="R54" t="n">
-        <v>7004845</v>
+        <v>7004812</v>
       </c>
       <c r="S54" t="n">
         <v>11</v>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
+          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7986,6 +7986,26 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -8003,10 +8023,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129226046</v>
+        <v>129231961</v>
       </c>
       <c r="B55" t="n">
-        <v>80185</v>
+        <v>98644</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -8014,27 +8034,32 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -8043,13 +8068,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490078</v>
+        <v>489928</v>
       </c>
       <c r="R55" t="n">
-        <v>7004812</v>
+        <v>7004745</v>
       </c>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8078,7 +8103,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8088,12 +8113,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8108,26 +8128,6 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8277,7 +8277,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129230183</v>
+        <v>129222854</v>
       </c>
       <c r="B57" t="n">
         <v>57727</v>
@@ -8322,13 +8322,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490060</v>
+        <v>489942</v>
       </c>
       <c r="R57" t="n">
-        <v>7004914</v>
+        <v>7004813</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8367,12 +8367,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8424,7 +8424,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129222854</v>
+        <v>129230183</v>
       </c>
       <c r="B58" t="n">
         <v>57727</v>
@@ -8469,13 +8469,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489942</v>
+        <v>490060</v>
       </c>
       <c r="R58" t="n">
-        <v>7004813</v>
+        <v>7004914</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129227061</v>
+        <v>129230577</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490204</v>
+        <v>490070</v>
       </c>
       <c r="R2" t="n">
-        <v>7004896</v>
+        <v>7004890</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,12 +799,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +822,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129230577</v>
+        <v>129227061</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,44 +833,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490070</v>
+        <v>490204</v>
       </c>
       <c r="R3" t="n">
-        <v>7004890</v>
+        <v>7004896</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,12 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:51</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,12 +931,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1384,38 +1384,47 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129223103</v>
+        <v>129226982</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1429,13 +1438,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489959</v>
+        <v>490196</v>
       </c>
       <c r="R7" t="n">
-        <v>7004819</v>
+        <v>7004884</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1464,7 +1473,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1474,12 +1483,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1494,26 +1503,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1531,45 +1520,64 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129224447</v>
+        <v>129226861</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490020</v>
+        <v>490181</v>
       </c>
       <c r="R8" t="n">
-        <v>7004694</v>
+        <v>7004884</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1601,7 +1609,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1611,7 +1619,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1626,26 +1639,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1663,64 +1656,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129226982</v>
+        <v>129224447</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490196</v>
+        <v>490020</v>
       </c>
       <c r="R9" t="n">
-        <v>7004884</v>
+        <v>7004694</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1752,7 +1726,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1762,12 +1736,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1782,6 +1751,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1799,47 +1788,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129226861</v>
+        <v>129223103</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1853,13 +1833,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490181</v>
+        <v>489959</v>
       </c>
       <c r="R10" t="n">
-        <v>7004884</v>
+        <v>7004819</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1888,7 +1868,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1898,12 +1878,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1918,6 +1898,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1935,48 +1935,67 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129231117</v>
+        <v>129231914</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490037</v>
+        <v>489938</v>
       </c>
       <c r="R11" t="n">
-        <v>7004829</v>
+        <v>7004758</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2005,7 +2024,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2015,7 +2034,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2030,26 +2054,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2067,67 +2071,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129231914</v>
+        <v>129231117</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489938</v>
+        <v>490037</v>
       </c>
       <c r="R12" t="n">
-        <v>7004758</v>
+        <v>7004829</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2156,7 +2141,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2166,12 +2151,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2186,6 +2166,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -3894,67 +3894,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129226592</v>
+        <v>129229156</v>
       </c>
       <c r="B25" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490132</v>
+        <v>490069</v>
       </c>
       <c r="R25" t="n">
-        <v>7004833</v>
+        <v>7004928</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3983,7 +3964,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3993,12 +3974,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4013,6 +3989,26 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4030,67 +4026,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129225418</v>
+        <v>129227087</v>
       </c>
       <c r="B26" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490122</v>
+        <v>490187</v>
       </c>
       <c r="R26" t="n">
-        <v>7004771</v>
+        <v>7004903</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4119,7 +4096,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4129,12 +4106,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4149,6 +4121,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4166,67 +4158,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129225602</v>
+        <v>129225967</v>
       </c>
       <c r="B27" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490142</v>
+        <v>490095</v>
       </c>
       <c r="R27" t="n">
-        <v>7004806</v>
+        <v>7004830</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4255,7 +4228,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4265,12 +4238,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4285,6 +4253,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4302,47 +4290,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129225165</v>
+        <v>129230367</v>
       </c>
       <c r="B28" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4356,10 +4335,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490124</v>
+        <v>490063</v>
       </c>
       <c r="R28" t="n">
-        <v>7004767</v>
+        <v>7004901</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -4391,7 +4370,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4401,12 +4380,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4421,6 +4400,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4438,10 +4437,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129229156</v>
+        <v>129230525</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4449,37 +4448,47 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490069</v>
+        <v>490071</v>
       </c>
       <c r="R29" t="n">
-        <v>7004928</v>
+        <v>7004894</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4508,7 +4517,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4518,7 +4527,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4547,12 +4561,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4570,38 +4584,47 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129230367</v>
+        <v>129226592</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4615,13 +4638,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490063</v>
+        <v>490132</v>
       </c>
       <c r="R30" t="n">
-        <v>7004901</v>
+        <v>7004833</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4650,7 +4673,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4660,12 +4683,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4680,26 +4703,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4717,38 +4720,47 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129230525</v>
+        <v>129225418</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4762,10 +4774,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490071</v>
+        <v>490122</v>
       </c>
       <c r="R31" t="n">
-        <v>7004894</v>
+        <v>7004771</v>
       </c>
       <c r="S31" t="n">
         <v>8</v>
@@ -4797,7 +4809,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4807,12 +4819,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4827,26 +4839,6 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4864,48 +4856,67 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129227087</v>
+        <v>129225602</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490187</v>
+        <v>490142</v>
       </c>
       <c r="R32" t="n">
-        <v>7004903</v>
+        <v>7004806</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4934,7 +4945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4944,7 +4955,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4959,26 +4975,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4996,48 +4992,67 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129225967</v>
+        <v>129225165</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490095</v>
+        <v>490124</v>
       </c>
       <c r="R33" t="n">
-        <v>7004830</v>
+        <v>7004767</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5066,7 +5081,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5076,7 +5091,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5091,26 +5111,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5265,48 +5265,53 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129227795</v>
+        <v>129223375</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>80178</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490175</v>
+        <v>490028</v>
       </c>
       <c r="R35" t="n">
-        <v>7004918</v>
+        <v>7004796</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5335,7 +5340,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5345,12 +5350,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5369,22 +5369,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5402,53 +5402,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129223375</v>
+        <v>129227795</v>
       </c>
       <c r="B36" t="n">
-        <v>80178</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490028</v>
+        <v>490175</v>
       </c>
       <c r="R36" t="n">
-        <v>7004796</v>
+        <v>7004918</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5477,7 +5472,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5487,7 +5482,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5506,22 +5506,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -6504,43 +6504,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129224339</v>
+        <v>129229897</v>
       </c>
       <c r="B44" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6554,13 +6549,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490008</v>
+        <v>490072</v>
       </c>
       <c r="R44" t="n">
-        <v>7004696</v>
+        <v>7004920</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6589,7 +6584,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6599,12 +6594,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6619,6 +6614,26 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6636,38 +6651,43 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129229897</v>
+        <v>129224339</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6681,13 +6701,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490072</v>
+        <v>490008</v>
       </c>
       <c r="R45" t="n">
-        <v>7004920</v>
+        <v>7004696</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6716,7 +6736,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6726,12 +6746,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6746,26 +6766,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -7032,10 +7032,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129230332</v>
+        <v>129223439</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>57887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7043,27 +7043,36 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -7077,13 +7086,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490052</v>
+        <v>490044</v>
       </c>
       <c r="R48" t="n">
-        <v>7004901</v>
+        <v>7004789</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7112,7 +7121,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7122,12 +7131,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7142,26 +7151,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7179,7 +7168,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129230142</v>
+        <v>129230332</v>
       </c>
       <c r="B49" t="n">
         <v>57727</v>
@@ -7224,13 +7213,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490056</v>
+        <v>490052</v>
       </c>
       <c r="R49" t="n">
-        <v>7004912</v>
+        <v>7004901</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7259,7 +7248,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7269,7 +7258,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7326,10 +7315,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129223439</v>
+        <v>129230142</v>
       </c>
       <c r="B50" t="n">
-        <v>57887</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7337,36 +7326,27 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7380,13 +7360,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490044</v>
+        <v>490056</v>
       </c>
       <c r="R50" t="n">
-        <v>7004789</v>
+        <v>7004912</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7415,7 +7395,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7425,12 +7405,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7445,6 +7425,26 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7745,52 +7745,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129226468</v>
+        <v>129226046</v>
       </c>
       <c r="B53" t="n">
-        <v>98727</v>
+        <v>80185</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7799,10 +7785,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490119</v>
+        <v>490078</v>
       </c>
       <c r="R53" t="n">
-        <v>7004845</v>
+        <v>7004812</v>
       </c>
       <c r="S53" t="n">
         <v>11</v>
@@ -7834,7 +7820,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7844,12 +7830,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
+          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7864,6 +7850,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7881,10 +7887,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129226046</v>
+        <v>129231961</v>
       </c>
       <c r="B54" t="n">
-        <v>80185</v>
+        <v>98644</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7892,27 +7898,32 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7921,13 +7932,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490078</v>
+        <v>489928</v>
       </c>
       <c r="R54" t="n">
-        <v>7004812</v>
+        <v>7004745</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7956,7 +7967,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7966,12 +7977,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7986,26 +7992,6 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -8023,38 +8009,47 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129231961</v>
+        <v>129226468</v>
       </c>
       <c r="B55" t="n">
-        <v>98644</v>
+        <v>98727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -8068,13 +8063,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489928</v>
+        <v>490119</v>
       </c>
       <c r="R55" t="n">
-        <v>7004745</v>
+        <v>7004845</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8103,7 +8098,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8113,7 +8108,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8145,10 +8145,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129223232</v>
+        <v>129222854</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8156,37 +8156,47 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490017</v>
+        <v>489942</v>
       </c>
       <c r="R56" t="n">
-        <v>7004780</v>
+        <v>7004813</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8215,7 +8225,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8225,7 +8235,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8254,12 +8269,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8277,7 +8292,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129222854</v>
+        <v>129230183</v>
       </c>
       <c r="B57" t="n">
         <v>57727</v>
@@ -8322,13 +8337,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>489942</v>
+        <v>490060</v>
       </c>
       <c r="R57" t="n">
-        <v>7004813</v>
+        <v>7004914</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8357,7 +8372,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8367,12 +8382,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8424,38 +8439,47 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129230183</v>
+        <v>129225550</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8469,13 +8493,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490060</v>
+        <v>490157</v>
       </c>
       <c r="R58" t="n">
-        <v>7004914</v>
+        <v>7004793</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8504,7 +8528,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8514,12 +8538,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8534,26 +8558,6 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8571,67 +8575,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129225550</v>
+        <v>129223232</v>
       </c>
       <c r="B59" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490157</v>
+        <v>490017</v>
       </c>
       <c r="R59" t="n">
-        <v>7004793</v>
+        <v>7004780</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8660,7 +8645,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8670,12 +8655,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8690,6 +8670,26 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129230577</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>129227061</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>129230003</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>129230622</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>129228951</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1384,64 +1384,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129226982</v>
+        <v>129224447</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>490196</v>
+        <v>490020</v>
       </c>
       <c r="R7" t="n">
-        <v>7004884</v>
+        <v>7004694</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1473,7 +1454,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1483,12 +1464,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1503,6 +1479,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1520,47 +1516,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129226861</v>
+        <v>129223103</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1574,13 +1561,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>490181</v>
+        <v>489959</v>
       </c>
       <c r="R8" t="n">
-        <v>7004884</v>
+        <v>7004819</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1609,7 +1596,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1619,12 +1606,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1639,6 +1626,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1656,45 +1663,64 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129224447</v>
+        <v>129226982</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490020</v>
+        <v>490196</v>
       </c>
       <c r="R9" t="n">
-        <v>7004694</v>
+        <v>7004884</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1726,7 +1752,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1736,7 +1762,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1751,26 +1782,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1788,38 +1799,47 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129223103</v>
+        <v>129226861</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1833,13 +1853,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>489959</v>
+        <v>490181</v>
       </c>
       <c r="R10" t="n">
-        <v>7004819</v>
+        <v>7004884</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1868,7 +1888,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1878,12 +1898,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1898,26 +1918,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1935,67 +1935,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129231914</v>
+        <v>129231117</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>489938</v>
+        <v>490037</v>
       </c>
       <c r="R11" t="n">
-        <v>7004758</v>
+        <v>7004829</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2024,7 +2005,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2034,12 +2015,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2054,6 +2030,26 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2071,48 +2067,67 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129231117</v>
+        <v>129231914</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>490037</v>
+        <v>489938</v>
       </c>
       <c r="R12" t="n">
-        <v>7004829</v>
+        <v>7004758</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2141,7 +2156,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2151,7 +2166,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2166,26 +2186,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2206,7 +2206,7 @@
         <v>129231535</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>129230279</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>129230462</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>129230594</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>129224667</v>
       </c>
       <c r="B17" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>129225817</v>
       </c>
       <c r="B18" t="n">
-        <v>80150</v>
+        <v>80176</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>129230997</v>
       </c>
       <c r="B19" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>129229350</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>129225796</v>
       </c>
       <c r="B21" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3490,45 +3490,64 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129230877</v>
+        <v>129225751</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490026</v>
+        <v>490094</v>
       </c>
       <c r="R22" t="n">
-        <v>7004861</v>
+        <v>7004803</v>
       </c>
       <c r="S22" t="n">
         <v>11</v>
@@ -3560,7 +3579,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3570,7 +3589,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3585,26 +3609,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3622,10 +3626,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129225751</v>
+        <v>129230745</v>
       </c>
       <c r="B23" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3652,7 +3656,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3676,10 +3680,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490094</v>
+        <v>490076</v>
       </c>
       <c r="R23" t="n">
-        <v>7004803</v>
+        <v>7004871</v>
       </c>
       <c r="S23" t="n">
         <v>11</v>
@@ -3711,7 +3715,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3721,12 +3725,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
+          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3758,64 +3762,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129230745</v>
+        <v>129230877</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490076</v>
+        <v>490026</v>
       </c>
       <c r="R24" t="n">
-        <v>7004871</v>
+        <v>7004861</v>
       </c>
       <c r="S24" t="n">
         <v>11</v>
@@ -3847,7 +3832,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3857,12 +3842,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3877,6 +3857,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3894,10 +3894,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129229156</v>
+        <v>129227087</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3929,13 +3929,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490069</v>
+        <v>490187</v>
       </c>
       <c r="R25" t="n">
-        <v>7004928</v>
+        <v>7004903</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4026,10 +4026,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129227087</v>
+        <v>129225967</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4061,13 +4061,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490187</v>
+        <v>490095</v>
       </c>
       <c r="R26" t="n">
-        <v>7004903</v>
+        <v>7004830</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4158,10 +4158,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129225967</v>
+        <v>129230367</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4169,37 +4169,47 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490095</v>
+        <v>490063</v>
       </c>
       <c r="R27" t="n">
-        <v>7004830</v>
+        <v>7004901</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4228,7 +4238,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4238,7 +4248,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4267,12 +4282,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4290,10 +4305,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129230367</v>
+        <v>129230525</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4335,13 +4350,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490063</v>
+        <v>490071</v>
       </c>
       <c r="R28" t="n">
-        <v>7004901</v>
+        <v>7004894</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4370,7 +4385,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4380,12 +4395,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4437,38 +4452,47 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129230525</v>
+        <v>129226592</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4482,13 +4506,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490071</v>
+        <v>490132</v>
       </c>
       <c r="R29" t="n">
-        <v>7004894</v>
+        <v>7004833</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4517,7 +4541,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4527,12 +4551,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4547,26 +4571,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4584,10 +4588,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129226592</v>
+        <v>129225602</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4614,7 +4618,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4624,7 +4628,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4638,13 +4642,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490132</v>
+        <v>490142</v>
       </c>
       <c r="R30" t="n">
-        <v>7004833</v>
+        <v>7004806</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4673,7 +4677,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4683,12 +4687,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4720,10 +4724,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129225418</v>
+        <v>129225165</v>
       </c>
       <c r="B31" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4750,7 +4754,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4774,13 +4778,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490122</v>
+        <v>490124</v>
       </c>
       <c r="R31" t="n">
-        <v>7004771</v>
+        <v>7004767</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4809,7 +4813,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4819,12 +4823,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
+          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4856,67 +4860,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129225602</v>
+        <v>129229156</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490142</v>
+        <v>490069</v>
       </c>
       <c r="R32" t="n">
-        <v>7004806</v>
+        <v>7004928</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4945,7 +4930,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4955,12 +4940,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4975,6 +4955,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4992,10 +4992,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129225165</v>
+        <v>129225418</v>
       </c>
       <c r="B33" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5046,13 +5046,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490124</v>
+        <v>490122</v>
       </c>
       <c r="R33" t="n">
-        <v>7004767</v>
+        <v>7004771</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
+          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5131,7 +5131,7 @@
         <v>129224808</v>
       </c>
       <c r="B34" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>129223375</v>
       </c>
       <c r="B35" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>129227795</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>129228038</v>
       </c>
       <c r="B37" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5675,52 +5675,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129223986</v>
+        <v>129231240</v>
       </c>
       <c r="B38" t="n">
-        <v>98727</v>
+        <v>80204</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5729,13 +5715,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490070</v>
+        <v>490033</v>
       </c>
       <c r="R38" t="n">
-        <v>7004763</v>
+        <v>7004823</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5764,7 +5750,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5774,12 +5760,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 22 plantor inom ca 1 m2 yta.</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5794,6 +5775,26 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5811,38 +5812,52 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129231240</v>
+        <v>129223986</v>
       </c>
       <c r="B39" t="n">
-        <v>80178</v>
+        <v>98756</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5851,13 +5866,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490033</v>
+        <v>490070</v>
       </c>
       <c r="R39" t="n">
-        <v>7004823</v>
+        <v>7004763</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5886,7 +5901,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5896,7 +5911,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Minst 22 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5911,26 +5931,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5951,7 +5951,7 @@
         <v>129223203</v>
       </c>
       <c r="B40" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>129227281</v>
       </c>
       <c r="B41" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>129230966</v>
       </c>
       <c r="B42" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>129222983</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6504,43 +6504,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129229897</v>
+        <v>129226789</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>92536</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6549,13 +6544,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490072</v>
+        <v>490174</v>
       </c>
       <c r="R44" t="n">
-        <v>7004920</v>
+        <v>7004879</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6584,7 +6579,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6594,12 +6589,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6613,27 +6603,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6651,43 +6621,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129224339</v>
+        <v>129229897</v>
       </c>
       <c r="B45" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6701,13 +6666,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490008</v>
+        <v>490072</v>
       </c>
       <c r="R45" t="n">
-        <v>7004696</v>
+        <v>7004920</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6736,7 +6701,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6746,12 +6711,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6766,6 +6731,26 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6783,38 +6768,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129226789</v>
+        <v>129224339</v>
       </c>
       <c r="B46" t="n">
-        <v>92508</v>
+        <v>98756</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6823,13 +6818,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>490174</v>
+        <v>490008</v>
       </c>
       <c r="R46" t="n">
-        <v>7004879</v>
+        <v>7004696</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6858,7 +6853,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6868,7 +6863,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 56 plantor och 3 fröställningar inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6900,10 +6900,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129229015</v>
+        <v>129230332</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6911,37 +6911,47 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490105</v>
+        <v>490052</v>
       </c>
       <c r="R47" t="n">
-        <v>7004966</v>
+        <v>7004901</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6970,7 +6980,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6980,7 +6990,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6994,7 +7009,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -7009,12 +7024,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7032,10 +7047,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129223439</v>
+        <v>129230142</v>
       </c>
       <c r="B48" t="n">
-        <v>57887</v>
+        <v>57730</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7043,36 +7058,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -7086,13 +7092,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490044</v>
+        <v>490056</v>
       </c>
       <c r="R48" t="n">
-        <v>7004789</v>
+        <v>7004912</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -7121,7 +7127,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7131,12 +7137,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7151,6 +7157,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7168,10 +7194,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129230332</v>
+        <v>129229015</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7179,47 +7205,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490052</v>
+        <v>490105</v>
       </c>
       <c r="R49" t="n">
-        <v>7004901</v>
+        <v>7004966</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -7248,7 +7264,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7258,12 +7274,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:37</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7277,7 +7288,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -7292,12 +7303,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7315,10 +7326,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129230142</v>
+        <v>129223439</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>57890</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7326,27 +7337,36 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7360,13 +7380,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490056</v>
+        <v>490044</v>
       </c>
       <c r="R50" t="n">
-        <v>7004912</v>
+        <v>7004789</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7395,7 +7415,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7405,12 +7425,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7425,26 +7445,6 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7462,38 +7462,47 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129230834</v>
+        <v>129223831</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7507,13 +7516,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490020</v>
+        <v>490057</v>
       </c>
       <c r="R51" t="n">
-        <v>7004888</v>
+        <v>7004780</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7542,7 +7551,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7552,12 +7561,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
+          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7572,26 +7581,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7609,47 +7598,38 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129223831</v>
+        <v>129230834</v>
       </c>
       <c r="B52" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7663,13 +7643,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490057</v>
+        <v>490020</v>
       </c>
       <c r="R52" t="n">
-        <v>7004780</v>
+        <v>7004888</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7698,7 +7678,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7708,12 +7688,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7728,6 +7708,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7748,7 +7748,7 @@
         <v>129226046</v>
       </c>
       <c r="B53" t="n">
-        <v>80185</v>
+        <v>80211</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7887,38 +7887,47 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129231961</v>
+        <v>129226468</v>
       </c>
       <c r="B54" t="n">
-        <v>98644</v>
+        <v>98756</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7932,13 +7941,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489928</v>
+        <v>490119</v>
       </c>
       <c r="R54" t="n">
-        <v>7004745</v>
+        <v>7004845</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7967,7 +7976,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7977,7 +7986,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8009,47 +8023,38 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129226468</v>
+        <v>129231961</v>
       </c>
       <c r="B55" t="n">
-        <v>98727</v>
+        <v>98673</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -8063,13 +8068,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490119</v>
+        <v>489928</v>
       </c>
       <c r="R55" t="n">
-        <v>7004845</v>
+        <v>7004745</v>
       </c>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8098,7 +8103,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8108,12 +8113,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8145,38 +8145,47 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129222854</v>
+        <v>129225550</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -8190,10 +8199,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>489942</v>
+        <v>490157</v>
       </c>
       <c r="R56" t="n">
-        <v>7004813</v>
+        <v>7004793</v>
       </c>
       <c r="S56" t="n">
         <v>8</v>
@@ -8225,7 +8234,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8235,12 +8244,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8255,26 +8264,6 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8292,10 +8281,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129230183</v>
+        <v>129223232</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -8303,47 +8292,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490060</v>
+        <v>490017</v>
       </c>
       <c r="R57" t="n">
-        <v>7004914</v>
+        <v>7004780</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8372,7 +8351,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8382,12 +8361,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:31</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8416,12 +8390,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8439,47 +8413,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129225550</v>
+        <v>129222854</v>
       </c>
       <c r="B58" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8493,10 +8458,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>490157</v>
+        <v>489942</v>
       </c>
       <c r="R58" t="n">
-        <v>7004793</v>
+        <v>7004813</v>
       </c>
       <c r="S58" t="n">
         <v>8</v>
@@ -8528,7 +8493,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8538,12 +8503,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8558,6 +8523,26 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8575,10 +8560,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129223232</v>
+        <v>129230183</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8586,37 +8571,47 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490017</v>
+        <v>490060</v>
       </c>
       <c r="R59" t="n">
-        <v>7004780</v>
+        <v>7004914</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8645,7 +8640,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8655,7 +8650,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8684,12 +8684,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8710,7 +8710,7 @@
         <v>129225914</v>
       </c>
       <c r="B60" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129230577</v>
+        <v>129227061</v>
       </c>
       <c r="B2" t="n">
-        <v>57730</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,44 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490070</v>
+        <v>490204</v>
       </c>
       <c r="R2" t="n">
-        <v>7004890</v>
+        <v>7004896</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:51</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,12 +784,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -822,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129227061</v>
+        <v>129230577</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,34 +818,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490204</v>
+        <v>490070</v>
       </c>
       <c r="R3" t="n">
-        <v>7004896</v>
+        <v>7004890</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +897,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,12 +931,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -2203,43 +2203,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129231535</v>
+        <v>129224667</v>
       </c>
       <c r="B13" t="n">
-        <v>57730</v>
+        <v>98756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2248,10 +2252,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>489991</v>
+        <v>490027</v>
       </c>
       <c r="R13" t="n">
-        <v>7004843</v>
+        <v>7004700</v>
       </c>
       <c r="S13" t="n">
         <v>8</v>
@@ -2283,7 +2287,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2293,12 +2297,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 250 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2313,26 +2317,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2350,7 +2334,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129230279</v>
+        <v>129231535</v>
       </c>
       <c r="B14" t="n">
         <v>57730</v>
@@ -2395,13 +2379,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>490064</v>
+        <v>489991</v>
       </c>
       <c r="R14" t="n">
-        <v>7004903</v>
+        <v>7004843</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2430,7 +2414,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2440,7 +2424,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2497,7 +2481,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129230462</v>
+        <v>129230279</v>
       </c>
       <c r="B15" t="n">
         <v>57730</v>
@@ -2542,13 +2526,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490066</v>
+        <v>490064</v>
       </c>
       <c r="R15" t="n">
-        <v>7004896</v>
+        <v>7004903</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2577,7 +2561,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2587,12 +2571,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2644,7 +2628,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129230594</v>
+        <v>129230462</v>
       </c>
       <c r="B16" t="n">
         <v>57730</v>
@@ -2689,13 +2673,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490071</v>
+        <v>490066</v>
       </c>
       <c r="R16" t="n">
-        <v>7004887</v>
+        <v>7004896</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2724,7 +2708,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2734,7 +2718,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2791,47 +2775,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129224667</v>
+        <v>129230594</v>
       </c>
       <c r="B17" t="n">
-        <v>98756</v>
+        <v>57730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2840,13 +2820,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490027</v>
+        <v>490071</v>
       </c>
       <c r="R17" t="n">
-        <v>7004700</v>
+        <v>7004887</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2875,7 +2855,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2885,12 +2865,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 250 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2905,6 +2885,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3894,7 +3894,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129227087</v>
+        <v>129225967</v>
       </c>
       <c r="B25" t="n">
         <v>79070</v>
@@ -3929,13 +3929,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490187</v>
+        <v>490095</v>
       </c>
       <c r="R25" t="n">
-        <v>7004903</v>
+        <v>7004830</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4026,10 +4026,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129225967</v>
+        <v>129230367</v>
       </c>
       <c r="B26" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4037,37 +4037,47 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490095</v>
+        <v>490063</v>
       </c>
       <c r="R26" t="n">
-        <v>7004830</v>
+        <v>7004901</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -4096,7 +4106,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4106,7 +4116,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4135,12 +4150,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4158,7 +4173,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129230367</v>
+        <v>129230525</v>
       </c>
       <c r="B27" t="n">
         <v>57730</v>
@@ -4203,13 +4218,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490063</v>
+        <v>490071</v>
       </c>
       <c r="R27" t="n">
-        <v>7004901</v>
+        <v>7004894</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4238,7 +4253,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4248,12 +4263,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4305,10 +4320,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129230525</v>
+        <v>129227087</v>
       </c>
       <c r="B28" t="n">
-        <v>57730</v>
+        <v>79070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4316,47 +4331,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490071</v>
+        <v>490187</v>
       </c>
       <c r="R28" t="n">
-        <v>7004894</v>
+        <v>7004903</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4385,7 +4390,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4395,12 +4400,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4452,67 +4452,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129226592</v>
+        <v>129229156</v>
       </c>
       <c r="B29" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490132</v>
+        <v>490069</v>
       </c>
       <c r="R29" t="n">
-        <v>7004833</v>
+        <v>7004928</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4541,7 +4522,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4551,12 +4532,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4571,6 +4547,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4588,7 +4584,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129225602</v>
+        <v>129226592</v>
       </c>
       <c r="B30" t="n">
         <v>98756</v>
@@ -4618,7 +4614,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4628,7 +4624,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4642,13 +4638,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490142</v>
+        <v>490132</v>
       </c>
       <c r="R30" t="n">
-        <v>7004806</v>
+        <v>7004833</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4677,7 +4673,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4687,12 +4683,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4724,7 +4720,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129225165</v>
+        <v>129225418</v>
       </c>
       <c r="B31" t="n">
         <v>98756</v>
@@ -4754,7 +4750,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4778,13 +4774,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490124</v>
+        <v>490122</v>
       </c>
       <c r="R31" t="n">
-        <v>7004767</v>
+        <v>7004771</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4813,7 +4809,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4823,12 +4819,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
+          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4860,48 +4856,67 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129229156</v>
+        <v>129225602</v>
       </c>
       <c r="B32" t="n">
-        <v>79070</v>
+        <v>98756</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490069</v>
+        <v>490142</v>
       </c>
       <c r="R32" t="n">
-        <v>7004928</v>
+        <v>7004806</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4930,7 +4945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4940,7 +4955,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4955,26 +4975,6 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4992,7 +4992,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129225418</v>
+        <v>129225165</v>
       </c>
       <c r="B33" t="n">
         <v>98756</v>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -5046,13 +5046,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490122</v>
+        <v>490124</v>
       </c>
       <c r="R33" t="n">
-        <v>7004771</v>
+        <v>7004767</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
+          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5675,38 +5675,52 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129231240</v>
+        <v>129223986</v>
       </c>
       <c r="B38" t="n">
-        <v>80204</v>
+        <v>98756</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5715,13 +5729,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490033</v>
+        <v>490070</v>
       </c>
       <c r="R38" t="n">
-        <v>7004823</v>
+        <v>7004763</v>
       </c>
       <c r="S38" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5750,7 +5764,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5760,7 +5774,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Minst 22 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5775,26 +5794,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5812,52 +5811,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129223986</v>
+        <v>129231240</v>
       </c>
       <c r="B39" t="n">
-        <v>98756</v>
+        <v>80204</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5866,13 +5851,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490070</v>
+        <v>490033</v>
       </c>
       <c r="R39" t="n">
-        <v>7004763</v>
+        <v>7004823</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5901,7 +5886,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5911,12 +5896,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Minst 22 plantor inom ca 1 m2 yta.</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5931,6 +5911,26 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -6504,38 +6504,43 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129226789</v>
+        <v>129229897</v>
       </c>
       <c r="B44" t="n">
-        <v>92536</v>
+        <v>57730</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4769</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6544,13 +6549,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490174</v>
+        <v>490072</v>
       </c>
       <c r="R44" t="n">
-        <v>7004879</v>
+        <v>7004920</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6579,7 +6584,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6589,7 +6594,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6603,7 +6613,27 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6621,43 +6651,38 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129229897</v>
+        <v>129226789</v>
       </c>
       <c r="B45" t="n">
-        <v>57730</v>
+        <v>92536</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6666,13 +6691,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490072</v>
+        <v>490174</v>
       </c>
       <c r="R45" t="n">
-        <v>7004920</v>
+        <v>7004879</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6701,7 +6726,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6711,12 +6736,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6730,27 +6750,7 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -7887,47 +7887,38 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129226468</v>
+        <v>129231961</v>
       </c>
       <c r="B54" t="n">
-        <v>98756</v>
+        <v>98673</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7941,13 +7932,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>490119</v>
+        <v>489928</v>
       </c>
       <c r="R54" t="n">
-        <v>7004845</v>
+        <v>7004745</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7976,7 +7967,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7986,12 +7977,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8023,38 +8009,47 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129231961</v>
+        <v>129226468</v>
       </c>
       <c r="B55" t="n">
-        <v>98673</v>
+        <v>98756</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -8068,13 +8063,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>489928</v>
+        <v>490119</v>
       </c>
       <c r="R55" t="n">
-        <v>7004745</v>
+        <v>7004845</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8103,7 +8098,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8113,7 +8108,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>129230577</v>
       </c>
       <c r="B3" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>129230003</v>
       </c>
       <c r="B4" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>129230622</v>
       </c>
       <c r="B5" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>129223103</v>
       </c>
       <c r="B8" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>129231535</v>
       </c>
       <c r="B14" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>129230279</v>
       </c>
       <c r="B15" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>129230462</v>
       </c>
       <c r="B16" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>129230594</v>
       </c>
       <c r="B17" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>129229350</v>
       </c>
       <c r="B20" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>129230367</v>
       </c>
       <c r="B26" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>129230525</v>
       </c>
       <c r="B27" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>129222983</v>
       </c>
       <c r="B43" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>129229897</v>
       </c>
       <c r="B44" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>129230332</v>
       </c>
       <c r="B47" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>129230142</v>
       </c>
       <c r="B48" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>129230834</v>
       </c>
       <c r="B52" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>129222854</v>
       </c>
       <c r="B58" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>129230183</v>
       </c>
       <c r="B59" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>129225914</v>
       </c>
       <c r="B60" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>129230577</v>
       </c>
       <c r="B3" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>129230003</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>129230622</v>
       </c>
       <c r="B5" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>129223103</v>
       </c>
       <c r="B8" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>129231535</v>
       </c>
       <c r="B14" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>129230279</v>
       </c>
       <c r="B15" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>129230462</v>
       </c>
       <c r="B16" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>129230594</v>
       </c>
       <c r="B17" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>129229350</v>
       </c>
       <c r="B20" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>129230367</v>
       </c>
       <c r="B26" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>129230525</v>
       </c>
       <c r="B27" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>129222983</v>
       </c>
       <c r="B43" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>129229897</v>
       </c>
       <c r="B44" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>129230332</v>
       </c>
       <c r="B47" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>129230142</v>
       </c>
       <c r="B48" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>129230834</v>
       </c>
       <c r="B52" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>129222854</v>
       </c>
       <c r="B58" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>129230183</v>
       </c>
       <c r="B59" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>129225914</v>
       </c>
       <c r="B60" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>129230577</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>129230003</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>129230622</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>129223103</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>129231535</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>129230279</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>129230462</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>129230594</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>129229350</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>129230367</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>129230525</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>129222983</v>
       </c>
       <c r="B43" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>129229897</v>
       </c>
       <c r="B44" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>129230332</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>129230142</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>129230834</v>
       </c>
       <c r="B52" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>129222854</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>129230183</v>
       </c>
       <c r="B59" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129227061</v>
+        <v>129225817</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490204</v>
+        <v>490077</v>
       </c>
       <c r="R2" t="n">
-        <v>7004896</v>
+        <v>7004807</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,22 +784,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,43 +817,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129230577</v>
+        <v>129224808</v>
       </c>
       <c r="B3" t="n">
-        <v>57740</v>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -852,13 +857,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490070</v>
+        <v>490107</v>
       </c>
       <c r="R3" t="n">
-        <v>7004890</v>
+        <v>7004741</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,12 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:51</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -954,43 +954,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129230003</v>
+        <v>129226715</v>
       </c>
       <c r="B4" t="n">
-        <v>57740</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -999,13 +994,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490061</v>
+        <v>490182</v>
       </c>
       <c r="R4" t="n">
-        <v>7004922</v>
+        <v>7004791</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1039,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,26 +1054,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1101,43 +1071,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129230622</v>
+        <v>129226789</v>
       </c>
       <c r="B5" t="n">
-        <v>57740</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1146,10 +1111,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490077</v>
+        <v>490174</v>
       </c>
       <c r="R5" t="n">
-        <v>7004897</v>
+        <v>7004879</v>
       </c>
       <c r="S5" t="n">
         <v>11</v>
@@ -1181,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1191,12 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,27 +1170,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1248,10 +1188,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129228951</v>
+        <v>129223232</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,56 +1199,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490119</v>
+        <v>490017</v>
       </c>
       <c r="R6" t="n">
-        <v>7004879</v>
+        <v>7004780</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1337,7 +1258,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1347,12 +1268,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:42</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1367,6 +1283,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1387,11 +1323,11 @@
         <v>129224447</v>
       </c>
       <c r="B7" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1516,58 +1452,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129223103</v>
+        <v>129225967</v>
       </c>
       <c r="B8" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489959</v>
+        <v>490095</v>
       </c>
       <c r="R8" t="n">
-        <v>7004819</v>
+        <v>7004830</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1596,7 +1522,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1606,12 +1532,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1640,12 +1561,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1663,10 +1584,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129226982</v>
+        <v>129227061</v>
       </c>
       <c r="B9" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1674,56 +1595,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>490196</v>
+        <v>490204</v>
       </c>
       <c r="R9" t="n">
-        <v>7004884</v>
+        <v>7004896</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1752,7 +1654,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1762,12 +1664,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1782,6 +1679,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1799,10 +1716,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129226861</v>
+        <v>129227087</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1810,53 +1727,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>490181</v>
+        <v>490187</v>
       </c>
       <c r="R10" t="n">
-        <v>7004884</v>
+        <v>7004903</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1888,7 +1786,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1898,12 +1796,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1918,6 +1811,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1935,14 +1848,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129231117</v>
+        <v>129227795</v>
       </c>
       <c r="B11" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1970,13 +1883,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>490037</v>
+        <v>490175</v>
       </c>
       <c r="R11" t="n">
-        <v>7004829</v>
+        <v>7004918</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2005,7 +1918,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2015,7 +1928,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2067,10 +1985,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129231914</v>
+        <v>129229015</v>
       </c>
       <c r="B12" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2078,53 +1996,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>489938</v>
+        <v>490105</v>
       </c>
       <c r="R12" t="n">
-        <v>7004758</v>
+        <v>7004966</v>
       </c>
       <c r="S12" t="n">
         <v>8</v>
@@ -2156,7 +2055,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:56</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2166,12 +2065,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:56</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2185,7 +2079,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2203,10 +2117,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129224667</v>
+        <v>129229156</v>
       </c>
       <c r="B13" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2214,51 +2128,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>490027</v>
+        <v>490069</v>
       </c>
       <c r="R13" t="n">
-        <v>7004700</v>
+        <v>7004928</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2287,7 +2187,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2297,12 +2197,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 250 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2317,6 +2212,26 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2334,58 +2249,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129231535</v>
+        <v>129230877</v>
       </c>
       <c r="B14" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>489991</v>
+        <v>490026</v>
       </c>
       <c r="R14" t="n">
-        <v>7004843</v>
+        <v>7004861</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2414,7 +2319,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2424,12 +2329,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:40</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2458,12 +2358,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2481,58 +2381,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129230279</v>
+        <v>129231117</v>
       </c>
       <c r="B15" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>490064</v>
+        <v>490037</v>
       </c>
       <c r="R15" t="n">
-        <v>7004903</v>
+        <v>7004829</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2561,7 +2451,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2571,12 +2461,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2605,12 +2490,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2628,10 +2513,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129230462</v>
+        <v>129230966</v>
       </c>
       <c r="B16" t="n">
-        <v>57740</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2639,32 +2524,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2673,13 +2553,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>490066</v>
+        <v>490020</v>
       </c>
       <c r="R16" t="n">
-        <v>7004896</v>
+        <v>7004857</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2708,7 +2588,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2718,12 +2598,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2742,22 +2617,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2775,43 +2650,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129230594</v>
+        <v>129223375</v>
       </c>
       <c r="B17" t="n">
-        <v>57740</v>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2820,13 +2690,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>490071</v>
+        <v>490028</v>
       </c>
       <c r="R17" t="n">
-        <v>7004887</v>
+        <v>7004796</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2855,7 +2725,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2865,12 +2735,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:53</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2889,22 +2754,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2922,38 +2787,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129225817</v>
+        <v>129225796</v>
       </c>
       <c r="B18" t="n">
-        <v>80176</v>
+        <v>80461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2962,10 +2827,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>490077</v>
+        <v>490072</v>
       </c>
       <c r="R18" t="n">
-        <v>7004807</v>
+        <v>7004799</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -2997,7 +2862,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3007,7 +2872,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3067,7 +2932,7 @@
         <v>129230997</v>
       </c>
       <c r="B19" t="n">
-        <v>80204</v>
+        <v>80461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3201,43 +3066,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129229350</v>
+        <v>129231240</v>
       </c>
       <c r="B20" t="n">
-        <v>57740</v>
+        <v>80461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3246,13 +3106,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>490080</v>
+        <v>490033</v>
       </c>
       <c r="R20" t="n">
-        <v>7004934</v>
+        <v>7004823</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3281,7 +3141,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3291,12 +3151,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, färska (2025), i riklig mängd längs flera meter på en gran vid en hyggeskant. Granen är gräns-snitslad för en planerad avverning.</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3315,22 +3170,22 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3348,10 +3203,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129225796</v>
+        <v>129226046</v>
       </c>
       <c r="B21" t="n">
-        <v>80204</v>
+        <v>80468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3359,21 +3214,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3388,13 +3243,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>490072</v>
+        <v>490078</v>
       </c>
       <c r="R21" t="n">
-        <v>7004799</v>
+        <v>7004812</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3423,7 +3278,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3433,12 +3288,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3467,12 +3322,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3490,47 +3345,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129225751</v>
+        <v>129222854</v>
       </c>
       <c r="B22" t="n">
-        <v>98756</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3544,13 +3390,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>490094</v>
+        <v>489942</v>
       </c>
       <c r="R22" t="n">
-        <v>7004803</v>
+        <v>7004813</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3579,7 +3425,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3589,12 +3435,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3609,6 +3455,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3626,47 +3492,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129230745</v>
+        <v>129222983</v>
       </c>
       <c r="B23" t="n">
-        <v>98756</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3680,13 +3537,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>490076</v>
+        <v>489960</v>
       </c>
       <c r="R23" t="n">
-        <v>7004871</v>
+        <v>7004821</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3715,7 +3572,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3725,12 +3582,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3745,6 +3602,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3762,10 +3639,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129230877</v>
+        <v>129223103</v>
       </c>
       <c r="B24" t="n">
-        <v>79070</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3773,37 +3650,47 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>490026</v>
+        <v>489959</v>
       </c>
       <c r="R24" t="n">
-        <v>7004861</v>
+        <v>7004819</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3832,7 +3719,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3842,7 +3729,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3871,12 +3763,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3894,10 +3786,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129225967</v>
+        <v>129229350</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3905,37 +3797,47 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>490095</v>
+        <v>490080</v>
       </c>
       <c r="R25" t="n">
-        <v>7004830</v>
+        <v>7004934</v>
       </c>
       <c r="S25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3964,7 +3866,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3974,7 +3876,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack, färska (2025), i riklig mängd längs flera meter på en gran vid en hyggeskant. Granen är gräns-snitslad för en planerad avverning.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4003,12 +3910,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -4026,10 +3933,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129230367</v>
+        <v>129229897</v>
       </c>
       <c r="B26" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4071,10 +3978,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>490063</v>
+        <v>490072</v>
       </c>
       <c r="R26" t="n">
-        <v>7004901</v>
+        <v>7004920</v>
       </c>
       <c r="S26" t="n">
         <v>9</v>
@@ -4106,7 +4013,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4116,12 +4023,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4173,10 +4080,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129230525</v>
+        <v>129230003</v>
       </c>
       <c r="B27" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4218,10 +4125,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>490071</v>
+        <v>490061</v>
       </c>
       <c r="R27" t="n">
-        <v>7004894</v>
+        <v>7004922</v>
       </c>
       <c r="S27" t="n">
         <v>8</v>
@@ -4253,7 +4160,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4263,12 +4170,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant. Särskilt tydligt några meter upp på stammen.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4320,10 +4227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129227087</v>
+        <v>129230142</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4331,34 +4238,44 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>490187</v>
+        <v>490056</v>
       </c>
       <c r="R28" t="n">
-        <v>7004903</v>
+        <v>7004912</v>
       </c>
       <c r="S28" t="n">
         <v>9</v>
@@ -4390,7 +4307,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4400,7 +4317,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4429,12 +4351,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4452,10 +4374,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129229156</v>
+        <v>129230183</v>
       </c>
       <c r="B29" t="n">
-        <v>79070</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4463,37 +4385,47 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>490069</v>
+        <v>490060</v>
       </c>
       <c r="R29" t="n">
-        <v>7004928</v>
+        <v>7004914</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4522,7 +4454,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4532,7 +4464,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4561,12 +4498,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4584,47 +4521,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129226592</v>
+        <v>129230279</v>
       </c>
       <c r="B30" t="n">
-        <v>98756</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4638,13 +4566,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>490132</v>
+        <v>490064</v>
       </c>
       <c r="R30" t="n">
-        <v>7004833</v>
+        <v>7004903</v>
       </c>
       <c r="S30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4673,7 +4601,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4683,12 +4611,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4703,6 +4631,26 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4720,47 +4668,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129225418</v>
+        <v>129230332</v>
       </c>
       <c r="B31" t="n">
-        <v>98756</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4774,13 +4713,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>490122</v>
+        <v>490052</v>
       </c>
       <c r="R31" t="n">
-        <v>7004771</v>
+        <v>7004901</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4809,7 +4748,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4819,12 +4758,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4839,6 +4778,26 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4856,47 +4815,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129225602</v>
+        <v>129230367</v>
       </c>
       <c r="B32" t="n">
-        <v>98756</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4910,13 +4860,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>490142</v>
+        <v>490063</v>
       </c>
       <c r="R32" t="n">
-        <v>7004806</v>
+        <v>7004901</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4945,7 +4895,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4955,12 +4905,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4975,6 +4925,26 @@
       <c r="AH32" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4992,47 +4962,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129225165</v>
+        <v>129230462</v>
       </c>
       <c r="B33" t="n">
-        <v>98756</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5046,13 +5007,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>490124</v>
+        <v>490066</v>
       </c>
       <c r="R33" t="n">
-        <v>7004767</v>
+        <v>7004896</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -5081,7 +5042,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5091,12 +5052,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5111,6 +5072,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5128,38 +5109,43 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129224808</v>
+        <v>129230525</v>
       </c>
       <c r="B34" t="n">
-        <v>92299</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5168,13 +5154,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>490107</v>
+        <v>490071</v>
       </c>
       <c r="R34" t="n">
-        <v>7004741</v>
+        <v>7004894</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5203,7 +5189,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5213,7 +5199,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5265,38 +5256,43 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129223375</v>
+        <v>129230577</v>
       </c>
       <c r="B35" t="n">
-        <v>80204</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5305,13 +5301,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>490028</v>
+        <v>490070</v>
       </c>
       <c r="R35" t="n">
-        <v>7004796</v>
+        <v>7004890</v>
       </c>
       <c r="S35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5340,7 +5336,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5350,7 +5346,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5369,22 +5370,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5402,10 +5403,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129227795</v>
+        <v>129230594</v>
       </c>
       <c r="B36" t="n">
-        <v>79070</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5413,34 +5414,44 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>490175</v>
+        <v>490071</v>
       </c>
       <c r="R36" t="n">
-        <v>7004918</v>
+        <v>7004887</v>
       </c>
       <c r="S36" t="n">
         <v>9</v>
@@ -5472,7 +5483,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5482,12 +5493,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5516,12 +5527,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5539,47 +5550,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129228038</v>
+        <v>129230622</v>
       </c>
       <c r="B37" t="n">
-        <v>98756</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5593,13 +5595,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>490161</v>
+        <v>490077</v>
       </c>
       <c r="R37" t="n">
-        <v>7004940</v>
+        <v>7004897</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5628,7 +5630,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5638,12 +5640,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
+          <t>Ringhack, äldre, i riklig mängd på en gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5657,7 +5659,27 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5675,47 +5697,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129223986</v>
+        <v>129230834</v>
       </c>
       <c r="B38" t="n">
-        <v>98756</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5729,10 +5742,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>490070</v>
+        <v>490020</v>
       </c>
       <c r="R38" t="n">
-        <v>7004763</v>
+        <v>7004888</v>
       </c>
       <c r="S38" t="n">
         <v>9</v>
@@ -5764,7 +5777,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5774,12 +5787,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Minst 22 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5794,6 +5807,26 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5811,38 +5844,43 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129231240</v>
+        <v>129231535</v>
       </c>
       <c r="B39" t="n">
-        <v>80204</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5851,13 +5889,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>490033</v>
+        <v>489991</v>
       </c>
       <c r="R39" t="n">
-        <v>7004823</v>
+        <v>7004843</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5886,7 +5924,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5896,7 +5934,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5915,22 +5958,22 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5948,47 +5991,47 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129223203</v>
+        <v>129223439</v>
       </c>
       <c r="B40" t="n">
-        <v>98756</v>
+        <v>58114</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -6002,13 +6045,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>489995</v>
+        <v>490044</v>
       </c>
       <c r="R40" t="n">
-        <v>7004788</v>
+        <v>7004789</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6037,7 +6080,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6047,12 +6090,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
+          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6084,47 +6127,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129227281</v>
+        <v>129225914</v>
       </c>
       <c r="B41" t="n">
-        <v>98756</v>
+        <v>58114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -6138,13 +6182,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>490162</v>
+        <v>490106</v>
       </c>
       <c r="R41" t="n">
-        <v>7004880</v>
+        <v>7004828</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6173,7 +6217,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6183,12 +6227,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Minst 16 plantor inom ca 2 m2 yta intill en tall.</t>
+          <t>Synobservation av minst 2 livliga talltitor i flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6220,38 +6264,43 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129230966</v>
+        <v>129231961</v>
       </c>
       <c r="B42" t="n">
-        <v>80175</v>
+        <v>99035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -6260,13 +6309,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>490020</v>
+        <v>489928</v>
       </c>
       <c r="R42" t="n">
-        <v>7004857</v>
+        <v>7004745</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6295,7 +6344,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6305,7 +6354,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6320,26 +6369,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6357,38 +6386,47 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129222983</v>
+        <v>129223203</v>
       </c>
       <c r="B43" t="n">
-        <v>57740</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6402,13 +6440,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>489960</v>
+        <v>489995</v>
       </c>
       <c r="R43" t="n">
-        <v>7004821</v>
+        <v>7004788</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6437,7 +6475,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6447,12 +6485,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 160 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6467,26 +6505,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6504,38 +6522,47 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129229897</v>
+        <v>129223831</v>
       </c>
       <c r="B44" t="n">
-        <v>57740</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6549,13 +6576,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>490072</v>
+        <v>490057</v>
       </c>
       <c r="R44" t="n">
-        <v>7004920</v>
+        <v>7004780</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6584,7 +6611,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6594,12 +6621,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6614,26 +6641,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6651,38 +6658,52 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129226789</v>
+        <v>129223986</v>
       </c>
       <c r="B45" t="n">
-        <v>92536</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6691,13 +6712,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>490174</v>
+        <v>490070</v>
       </c>
       <c r="R45" t="n">
-        <v>7004879</v>
+        <v>7004763</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6726,7 +6747,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6736,7 +6757,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 22 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6750,7 +6776,7 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6771,7 +6797,7 @@
         <v>129224339</v>
       </c>
       <c r="B46" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6900,43 +6926,47 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129230332</v>
+        <v>129224667</v>
       </c>
       <c r="B47" t="n">
-        <v>57740</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6945,13 +6975,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>490052</v>
+        <v>490027</v>
       </c>
       <c r="R47" t="n">
-        <v>7004901</v>
+        <v>7004700</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6980,7 +7010,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6990,12 +7020,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 250 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7010,26 +7040,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -7047,38 +7057,47 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129230142</v>
+        <v>129225165</v>
       </c>
       <c r="B48" t="n">
-        <v>57740</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -7092,10 +7111,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>490056</v>
+        <v>490124</v>
       </c>
       <c r="R48" t="n">
-        <v>7004912</v>
+        <v>7004767</v>
       </c>
       <c r="S48" t="n">
         <v>9</v>
@@ -7127,7 +7146,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -7137,12 +7156,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 31 plantor inom ca 3 x 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7157,26 +7176,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -7194,45 +7193,64 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129229015</v>
+        <v>129225418</v>
       </c>
       <c r="B49" t="n">
-        <v>79070</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>490105</v>
+        <v>490122</v>
       </c>
       <c r="R49" t="n">
-        <v>7004966</v>
+        <v>7004771</v>
       </c>
       <c r="S49" t="n">
         <v>8</v>
@@ -7264,7 +7282,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -7274,7 +7292,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 11 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7288,27 +7311,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7326,47 +7329,47 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129223439</v>
+        <v>129225550</v>
       </c>
       <c r="B50" t="n">
-        <v>57890</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7380,13 +7383,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>490044</v>
+        <v>490157</v>
       </c>
       <c r="R50" t="n">
-        <v>7004789</v>
+        <v>7004793</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7415,7 +7418,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7425,12 +7428,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Synobservation av en talltita i flerskiktad äldre granskog där det finns murkna björkhögstubbar för talltitans bobygge.</t>
+          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7462,10 +7465,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129223831</v>
+        <v>129225602</v>
       </c>
       <c r="B51" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7492,7 +7495,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7516,13 +7519,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>490057</v>
+        <v>490142</v>
       </c>
       <c r="R51" t="n">
-        <v>7004780</v>
+        <v>7004806</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7551,7 +7554,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7561,12 +7564,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 58 plantor och 1 fröställning inom ca 1 m2 yta intill en sälg med knäckt stam.</t>
+          <t>Minst 60 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7598,38 +7601,47 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129230834</v>
+        <v>129225751</v>
       </c>
       <c r="B52" t="n">
-        <v>57740</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7643,13 +7655,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>490020</v>
+        <v>490094</v>
       </c>
       <c r="R52" t="n">
-        <v>7004888</v>
+        <v>7004803</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7678,7 +7690,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7688,12 +7700,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en stor rotvälta.</t>
+          <t>Minst 90 plantor inom ca 2 m2 yta intill en grov gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7708,26 +7720,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7745,38 +7737,52 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129226046</v>
+        <v>129226468</v>
       </c>
       <c r="B53" t="n">
-        <v>80211</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7785,10 +7791,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>490078</v>
+        <v>490119</v>
       </c>
       <c r="R53" t="n">
-        <v>7004812</v>
+        <v>7004845</v>
       </c>
       <c r="S53" t="n">
         <v>11</v>
@@ -7820,7 +7826,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7830,12 +7836,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Växer här i riklig mängd på en gammal sälg med 47 cm i brösthöjdsdiameter.</t>
+          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7850,26 +7856,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7887,38 +7873,47 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129231961</v>
+        <v>129226592</v>
       </c>
       <c r="B54" t="n">
-        <v>98673</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7932,13 +7927,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>489928</v>
+        <v>490132</v>
       </c>
       <c r="R54" t="n">
-        <v>7004745</v>
+        <v>7004833</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7967,7 +7962,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7977,7 +7972,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Minst 42 plantor och 1 fröställning inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8009,10 +8009,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129226468</v>
+        <v>129226861</v>
       </c>
       <c r="B55" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -8063,13 +8063,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>490119</v>
+        <v>490181</v>
       </c>
       <c r="R55" t="n">
-        <v>7004845</v>
+        <v>7004884</v>
       </c>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -8108,12 +8108,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minst 110 plantor inom ca 3 m2 yta i äldre granskog på frisk-fuktig mark.</t>
+          <t>Minst 10 plantor och 1 fröställning inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -8145,10 +8145,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129225550</v>
+        <v>129226982</v>
       </c>
       <c r="B56" t="n">
-        <v>98756</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -8199,13 +8199,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>490157</v>
+        <v>490196</v>
       </c>
       <c r="R56" t="n">
-        <v>7004793</v>
+        <v>7004884</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Minst 18 plantor inom ca 0,5 m2 yta.</t>
+          <t>Minst 60 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -8281,48 +8281,67 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129223232</v>
+        <v>129227281</v>
       </c>
       <c r="B57" t="n">
-        <v>79070</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Storsved, Storsved, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>490017</v>
+        <v>490162</v>
       </c>
       <c r="R57" t="n">
-        <v>7004780</v>
+        <v>7004880</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8351,7 +8370,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8361,7 +8380,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Minst 16 plantor inom ca 2 m2 yta intill en tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8376,26 +8400,6 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8413,38 +8417,47 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129222854</v>
+        <v>129228038</v>
       </c>
       <c r="B58" t="n">
-        <v>57740</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8458,10 +8471,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>489942</v>
+        <v>490161</v>
       </c>
       <c r="R58" t="n">
-        <v>7004813</v>
+        <v>7004940</v>
       </c>
       <c r="S58" t="n">
         <v>8</v>
@@ -8493,7 +8506,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8503,12 +8516,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Minst 24 plantor inom ca 1 m2 yta innanför gränsen för en avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8522,27 +8535,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8560,38 +8553,47 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129230183</v>
+        <v>129228951</v>
       </c>
       <c r="B59" t="n">
-        <v>57740</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8605,10 +8607,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>490060</v>
+        <v>490119</v>
       </c>
       <c r="R59" t="n">
-        <v>7004914</v>
+        <v>7004879</v>
       </c>
       <c r="S59" t="n">
         <v>9</v>
@@ -8640,7 +8642,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8650,12 +8652,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), årsfärska, på en gran vid en hyggeskant.</t>
+          <t>Minst 47 plantor inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8670,26 +8672,6 @@
       <c r="AH59" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8707,48 +8689,47 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129225914</v>
+        <v>129230745</v>
       </c>
       <c r="B60" t="n">
-        <v>57896</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -8762,13 +8743,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>490106</v>
+        <v>490076</v>
       </c>
       <c r="R60" t="n">
-        <v>7004828</v>
+        <v>7004871</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8797,7 +8778,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8807,12 +8788,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Synobservation av minst 2 livliga talltitor i flerskiktad äldre granskog.</t>
+          <t>Minst 13 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8841,6 +8822,142 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129231914</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Storsved, Storsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>489938</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7004758</v>
+      </c>
+      <c r="S61" t="n">
+        <v>8</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Minst 38 plantor och 1 fröställning inom ca 1 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48030-2025 artfynd.xlsx
+++ b/artfynd/A 48030-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -814,6 +819,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129225817</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -951,6 +961,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224808</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1068,6 +1083,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129226715</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1185,6 +1205,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129226789</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1317,6 +1342,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129223232</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1449,6 +1479,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224447</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1581,6 +1616,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129225967</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1713,6 +1753,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129227061</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1845,6 +1890,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129227087</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1982,6 +2032,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129227795</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2114,6 +2169,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129229015</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2246,6 +2306,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129229156</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2378,6 +2443,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230877</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2510,6 +2580,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129231117</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2647,6 +2722,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230966</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2784,6 +2864,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129223375</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2926,6 +3011,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129225796</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3063,6 +3153,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230997</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3200,6 +3295,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129231240</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3342,6 +3442,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129226046</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3489,6 +3594,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129222854</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3636,6 +3746,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129222983</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3783,6 +3898,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129223103</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3930,6 +4050,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129229350</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4077,6 +4202,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129229897</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4224,6 +4354,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230003</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4371,6 +4506,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230142</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4518,6 +4658,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230183</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4665,6 +4810,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230279</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4812,6 +4962,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230332</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4959,6 +5114,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230367</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5106,6 +5266,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230462</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5253,6 +5418,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230525</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5400,6 +5570,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230577</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5547,6 +5722,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230594</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5694,6 +5874,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230622</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5841,6 +6026,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230834</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5988,6 +6178,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129231535</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6124,6 +6319,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129223439</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6261,6 +6461,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129225914</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6383,6 +6588,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129231961</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6519,6 +6729,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129223203</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6655,6 +6870,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129223831</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6791,6 +7011,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129223986</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6923,6 +7148,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224339</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -7054,6 +7284,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224667</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -7190,6 +7425,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129225165</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7326,6 +7566,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129225418</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7462,6 +7707,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129225550</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7598,6 +7848,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129225602</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7734,6 +7989,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129225751</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7870,6 +8130,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129226468</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -8006,6 +8271,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129226592</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -8142,6 +8412,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129226861</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8278,6 +8553,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129226982</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8414,6 +8694,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129227281</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8550,6 +8835,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129228038</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8686,6 +8976,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129228951</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8822,6 +9117,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230745</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8958,8 +9258,75 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129231914</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>